--- a/indicadores/ARG-ISS_out.xlsx
+++ b/indicadores/ARG-ISS_out.xlsx
@@ -110,7 +110,7 @@
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">arodriguez</t>
+    <t xml:space="preserve">pcohan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>

--- a/indicadores/ARG-ISS_out.xlsx
+++ b/indicadores/ARG-ISS_out.xlsx
@@ -110,7 +110,7 @@
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">arodriguez</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>

--- a/indicadores/ARG-ISS_out.xlsx
+++ b/indicadores/ARG-ISS_out.xlsx
@@ -104,13 +104,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">25/03/2026</t>
+    <t xml:space="preserve">26/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">arodriguez</t>
+    <t xml:space="preserve">pcohan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1235,7 +1235,7 @@
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.490433893860843</v>
+        <v>0.491300877502331</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1293,7 +1293,7 @@
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.240525404247509</v>
+        <v>0.24137655223456</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1363,7 +1363,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.271996000928396</v>
+        <v>0.263914338742567</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1393,7 +1393,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.0746493819108388</v>
+        <v>0.077707905837729</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -9786,7 +9786,7 @@
         <v>220</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.0194161135596886</v>
+        <v>0.0201897473373263</v>
       </c>
     </row>
     <row r="6">
@@ -9794,7 +9794,7 @@
         <v>221</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0995927061732437</v>
+        <v>0.0997056065288305</v>
       </c>
     </row>
     <row r="7">
@@ -9802,7 +9802,7 @@
         <v>222</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.233499879143102</v>
+        <v>0.232903782222348</v>
       </c>
     </row>
     <row r="8">
@@ -9810,7 +9810,7 @@
         <v>223</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.387414819686032</v>
+        <v>0.387566116632433</v>
       </c>
     </row>
     <row r="9">
@@ -9818,7 +9818,7 @@
         <v>224</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.490433893860843</v>
+        <v>0.491300877502331</v>
       </c>
     </row>
     <row r="10">
@@ -9826,7 +9826,7 @@
         <v>225</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.474198487548144</v>
+        <v>0.474817211964052</v>
       </c>
     </row>
     <row r="11">
@@ -9834,7 +9834,7 @@
         <v>226</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.324891307156536</v>
+        <v>0.325011287867504</v>
       </c>
     </row>
     <row r="12">
@@ -9842,7 +9842,7 @@
         <v>227</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.138626552105362</v>
+        <v>0.138611141073429</v>
       </c>
     </row>
     <row r="13">
@@ -9850,7 +9850,7 @@
         <v>228</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.0202564692530483</v>
+        <v>0.0204689317277212</v>
       </c>
     </row>
     <row r="14">

--- a/indicadores/ARG-ISS_out.xlsx
+++ b/indicadores/ARG-ISS_out.xlsx
@@ -104,13 +104,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">26/03/2026</t>
+    <t xml:space="preserve">30/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">arodriguez</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1235,7 +1235,7 @@
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.491300877502331</v>
+        <v>0.494964370307679</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1293,7 +1293,7 @@
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.24137655223456</v>
+        <v>0.244989727874077</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1363,7 +1363,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.263914338742567</v>
+        <v>0.213664886406701</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1393,7 +1393,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.077707905837729</v>
+        <v>0.0506467438502353</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1662,10 +1662,10 @@
         <v>787.328080192178</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>865.177573813071</v>
+        <v>865.177654549158</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>805.036332077161</v>
+        <v>805.036332075287</v>
       </c>
       <c r="K2" s="11" t="n">
         <v>786.96355327574</v>
@@ -1686,7 +1686,7 @@
         <v>1.01759504833838</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>0.926030886688734</v>
+        <v>0.926030800273984</v>
       </c>
     </row>
     <row r="3">
@@ -1715,10 +1715,10 @@
         <v>830.084542665156</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>887.244215395597</v>
+        <v>887.244267810002</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>835.542348194682</v>
+        <v>835.542348197256</v>
       </c>
       <c r="K3" s="11" t="n">
         <v>829.616360912496</v>
@@ -1743,7 +1743,7 @@
         <v>0.998837920155701</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>0.934488953280332</v>
+        <v>0.934488898074923</v>
       </c>
     </row>
     <row r="4">
@@ -1772,10 +1772,10 @@
         <v>863.981477130225</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>909.261973215287</v>
+        <v>909.26199725755</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>865.958000418196</v>
+        <v>865.958000425227</v>
       </c>
       <c r="K4" s="11" t="n">
         <v>870.283397495509</v>
@@ -1800,7 +1800,7 @@
         <v>1.00015644125182</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.950349475650468</v>
+        <v>0.95034945052179</v>
       </c>
     </row>
     <row r="5">
@@ -1829,10 +1829,10 @@
         <v>896.640668661376</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>931.145946100254</v>
+        <v>931.145941636695</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>896.163294917285</v>
+        <v>896.163294928778</v>
       </c>
       <c r="K5" s="11" t="n">
         <v>886.283401992717</v>
@@ -1857,7 +1857,7 @@
         <v>0.999177149121885</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>0.962150853850525</v>
+        <v>0.96215085846271</v>
       </c>
     </row>
     <row r="6">
@@ -1886,10 +1886,10 @@
         <v>933.341254450799</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>952.786871268784</v>
+        <v>952.78683806748</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>926.059864846917</v>
+        <v>926.059864862841</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>940.761266918315</v>
@@ -1916,7 +1916,7 @@
         <v>0.997387529720644</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.977031649190765</v>
+        <v>0.977031683236916</v>
       </c>
     </row>
     <row r="7">
@@ -1945,10 +1945,10 @@
         <v>954.723469186352</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>974.047446849098</v>
+        <v>974.047384582669</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>955.499943897439</v>
+        <v>955.499943917663</v>
       </c>
       <c r="K7" s="11" t="n">
         <v>955.805776822851</v>
@@ -1975,7 +1975,7 @@
         <v>0.996867722125416</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>0.977091016527163</v>
+        <v>0.977091078988158</v>
       </c>
     </row>
     <row r="8">
@@ -2004,10 +2004,10 @@
         <v>954.899709050321</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>994.782854966697</v>
+        <v>994.782763233057</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>984.409272769552</v>
+        <v>984.409272793773</v>
       </c>
       <c r="K8" s="11" t="n">
         <v>954.559219385876</v>
@@ -2034,7 +2034,7 @@
         <v>1.00529617422868</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>0.964991525022317</v>
+        <v>0.964991614008765</v>
       </c>
     </row>
     <row r="9">
@@ -2060,13 +2060,13 @@
         <v>1</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>985.343367101597</v>
+        <v>985.343367101596</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>1014.83687670332</v>
+        <v>1014.83675506459</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>1012.71512132859</v>
+        <v>1012.71512135622</v>
       </c>
       <c r="K9" s="11" t="n">
         <v>974.903881526865</v>
@@ -2093,7 +2093,7 @@
         <v>1.00331823902238</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>0.97415948770432</v>
+        <v>0.974159604467452</v>
       </c>
     </row>
     <row r="10">
@@ -2122,10 +2122,10 @@
         <v>1034.80641046859</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>1034.02815336845</v>
+        <v>1034.02800140831</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>1040.19550917295</v>
+        <v>1040.19550920303</v>
       </c>
       <c r="K10" s="11" t="n">
         <v>1050.08490521141</v>
@@ -2152,7 +2152,7 @@
         <v>1.00169588032332</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>1.00244980266915</v>
+        <v>1.00244994998858</v>
       </c>
     </row>
     <row r="11">
@@ -2181,10 +2181,10 @@
         <v>1085.56532501183</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>1052.15036814961</v>
+        <v>1052.1501855493</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1066.43939970206</v>
+        <v>1066.43939973305</v>
       </c>
       <c r="K11" s="11" t="n">
         <v>1071.17158124451</v>
@@ -2211,7 +2211,7 @@
         <v>0.997116367809164</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>1.02878351484971</v>
+        <v>1.02878369339474</v>
       </c>
     </row>
     <row r="12">
@@ -2240,10 +2240,10 @@
         <v>1129.95330183587</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>1069.00723970422</v>
+        <v>1069.00702633752</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1091.08520329549</v>
+        <v>1091.0852033252</v>
       </c>
       <c r="K12" s="11" t="n">
         <v>1137.31174788106</v>
@@ -2270,7 +2270,7 @@
         <v>0.995045377382422</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>1.05177473817753</v>
+        <v>1.05177494810478</v>
       </c>
     </row>
     <row r="13">
@@ -2299,10 +2299,10 @@
         <v>1146.69389986816</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>1084.41437494786</v>
+        <v>1084.41413099523</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>1113.79499124056</v>
+        <v>1113.79499126595</v>
       </c>
       <c r="K13" s="11" t="n">
         <v>1151.62416159253</v>
@@ -2329,7 +2329,7 @@
         <v>0.99372698274845</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>1.05079819631387</v>
+        <v>1.05079843270416</v>
       </c>
     </row>
     <row r="14">
@@ -2358,10 +2358,10 @@
         <v>1120.02758790004</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>1098.23007111375</v>
+        <v>1098.22979719567</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>1134.46196754751</v>
+        <v>1134.46196756453</v>
       </c>
       <c r="K14" s="11" t="n">
         <v>1117.44260594205</v>
@@ -2388,7 +2388,7 @@
         <v>1.00259934569772</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>1.02249879722668</v>
+        <v>1.02249905225609</v>
       </c>
     </row>
     <row r="15">
@@ -2417,10 +2417,10 @@
         <v>1110.73830140417</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>1110.35463155175</v>
+        <v>1110.35432888119</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>1153.16848207832</v>
+        <v>1153.16848208184</v>
       </c>
       <c r="K15" s="11" t="n">
         <v>1105.24633369128</v>
@@ -2447,7 +2447,7 @@
         <v>1.00794329161176</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>1.00829157444226</v>
+        <v>1.00829184929162</v>
       </c>
     </row>
     <row r="16">
@@ -2476,10 +2476,10 @@
         <v>1154.7317803985</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>1120.70036744598</v>
+        <v>1120.70003799961</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>1169.91178788697</v>
+        <v>1169.91178787062</v>
       </c>
       <c r="K16" s="11" t="n">
         <v>1150.30960522167</v>
@@ -2506,7 +2506,7 @@
         <v>0.999892308216567</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>1.03025523932411</v>
+        <v>1.03025554218289</v>
       </c>
     </row>
     <row r="17">
@@ -2535,10 +2535,10 @@
         <v>1193.30186694772</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>1129.17639729442</v>
+        <v>1129.17604400176</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>1184.44952728549</v>
+        <v>1184.44952724171</v>
       </c>
       <c r="K17" s="11" t="n">
         <v>1222.5915744926</v>
@@ -2565,7 +2565,7 @@
         <v>0.99916866313837</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>1.05591104629491</v>
+        <v>1.05591137666467</v>
       </c>
     </row>
     <row r="18">
@@ -2594,10 +2594,10 @@
         <v>1221.09939587363</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>1135.71034536864</v>
+        <v>1135.70997231799</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>1196.44133167258</v>
+        <v>1196.44133159265</v>
       </c>
       <c r="K18" s="11" t="n">
         <v>1189.57359278706</v>
@@ -2624,7 +2624,7 @@
         <v>0.99559771269258</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>1.07045231247538</v>
+        <v>1.07045266409062</v>
       </c>
     </row>
     <row r="19">
@@ -2653,10 +2653,10 @@
         <v>1239.17609899248</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>1140.28195329</v>
+        <v>1140.28156594922</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>1205.68740559533</v>
+        <v>1205.68740546962</v>
       </c>
       <c r="K19" s="11" t="n">
         <v>1262.72809438255</v>
@@ -2683,7 +2683,7 @@
         <v>0.996329384383439</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>1.08273884041543</v>
+        <v>1.08273920820959</v>
       </c>
     </row>
     <row r="20">
@@ -2712,10 +2712,10 @@
         <v>1224.46749876136</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>1142.90726959235</v>
+        <v>1142.90687504205</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>1211.9747539691</v>
+        <v>1211.97475378748</v>
       </c>
       <c r="K20" s="11" t="n">
         <v>1219.25264530946</v>
@@ -2742,7 +2742,7 @@
         <v>0.997400492664322</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>1.06857705695724</v>
+        <v>1.06857742584766</v>
       </c>
     </row>
     <row r="21">
@@ -2771,10 +2771,10 @@
         <v>1193.01539789214</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>1143.67887164772</v>
+        <v>1143.67847882331</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1215.37558515323</v>
+        <v>1215.37558490565</v>
       </c>
       <c r="K21" s="11" t="n">
         <v>1183.90456106264</v>
@@ -2801,7 +2801,7 @@
         <v>1.00441927671623</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.0477483608102</v>
+        <v>1.04774872068506</v>
       </c>
     </row>
     <row r="22">
@@ -2830,10 +2830,10 @@
         <v>1201.26749695839</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>1142.73705268796</v>
+        <v>1142.73667262626</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>1215.99849696373</v>
+        <v>1215.99849664116</v>
       </c>
       <c r="K22" s="11" t="n">
         <v>1206.08888481386</v>
@@ -2848,19 +2848,19 @@
         <v>1201.80301744872</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>0.00292935340228345</v>
+        <v>0.00292935340228323</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>-0.0114505847860983</v>
+        <v>-0.0114505847860985</v>
       </c>
       <c r="Q22" s="17" t="n">
-        <v>0.00293364815054908</v>
+        <v>0.00293364815054886</v>
       </c>
       <c r="R22" s="18" t="n">
         <v>1.00044579620416</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>1.05168815049956</v>
+        <v>1.05168850027952</v>
       </c>
     </row>
     <row r="23">
@@ -2880,25 +2880,25 @@
         <v>1087.93885305562</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.898284319118459</v>
+        <v>0.89828431911846</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>1208.18083055083</v>
+        <v>1208.18083055082</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>1140.2472470008</v>
+        <v>1140.24689308558</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>1213.79473209615</v>
+        <v>1213.79473169184</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>1211.12973910452</v>
+        <v>1211.12973910451</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>1211.12973910452</v>
+        <v>1211.12973910451</v>
       </c>
       <c r="M23" s="13" t="n">
         <v>1204.59058007312</v>
@@ -2907,19 +2907,19 @@
         <v>1204.59058007312</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>0.00231679794538642</v>
+        <v>0.0023167979453862</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>-0.0243287779695553</v>
+        <v>-0.0243287779695559</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>0.00231948379553648</v>
+        <v>0.00231948379553626</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>0.997028383179964</v>
+        <v>0.997028383179972</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>1.05642928166814</v>
+        <v>1.05642960956765</v>
       </c>
     </row>
     <row r="24">
@@ -2948,10 +2948,10 @@
         <v>1186.16846425595</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>1136.41448376905</v>
+        <v>1136.41417196853</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>1208.66598518533</v>
+        <v>1208.66598469637</v>
       </c>
       <c r="K24" s="11" t="n">
         <v>1190.01395726959</v>
@@ -2966,19 +2966,19 @@
         <v>1195.96405946775</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>-0.00718713716970447</v>
+        <v>-0.00718713716970424</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>-0.0207326198996565</v>
+        <v>-0.0207326198996569</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>-0.00716137146353035</v>
+        <v>-0.00716137146353013</v>
       </c>
       <c r="R24" s="18" t="n">
         <v>1.00825818212756</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>1.05240128188194</v>
+        <v>1.05240157063165</v>
       </c>
     </row>
     <row r="25">
@@ -3007,10 +3007,10 @@
         <v>1192.6985842273</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>1131.4880937331</v>
+        <v>1131.48784282116</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>1200.50062590111</v>
+        <v>1200.5006253305</v>
       </c>
       <c r="K25" s="11" t="n">
         <v>1101.49479167434</v>
@@ -3025,19 +3025,19 @@
         <v>1205.78556989278</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>0.00817867528924491</v>
+        <v>0.00817867528924469</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>0.0062571843654502</v>
+        <v>0.00625718436544953</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>0.00821221202031852</v>
+        <v>0.0082122120203183</v>
       </c>
       <c r="R25" s="18" t="n">
         <v>1.01097258422081</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>1.06566350682008</v>
+        <v>1.0656637431352</v>
       </c>
     </row>
     <row r="26">
@@ -3060,16 +3060,16 @@
         <v>1.14252300854203</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>0.933234916956912</v>
+        <v>0.933234916956807</v>
       </c>
       <c r="H26" s="8" t="n">
         <v>1226.88797227137</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>1125.75090730425</v>
+        <v>1125.75073905533</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>1189.09376377378</v>
+        <v>1189.09376313284</v>
       </c>
       <c r="K26" s="11" t="n">
         <v>1249.22230759984</v>
@@ -3087,7 +3087,7 @@
         <v>0.0204311096859823</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>0.0240234694617485</v>
+        <v>0.024023469461748</v>
       </c>
       <c r="Q26" s="17" t="n">
         <v>0.0206412535247651</v>
@@ -3096,7 +3096,7 @@
         <v>1.00308628281607</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>1.09320320112772</v>
+        <v>1.09320336451225</v>
       </c>
     </row>
     <row r="27">
@@ -3116,19 +3116,19 @@
         <v>1111.28111175113</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.900160165739004</v>
+        <v>0.900160165739003</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>1243.43392363156</v>
+        <v>1243.43392363155</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>1119.52401145039</v>
+        <v>1119.52395079627</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>1174.20149812525</v>
+        <v>1174.20149743649</v>
       </c>
       <c r="K27" s="11" t="n">
         <v>1234.53709022861</v>
@@ -3137,25 +3137,25 @@
         <v>1234.53709022861</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>1236.72429918106</v>
+        <v>1236.72429918105</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>1236.72429918106</v>
+        <v>1236.72429918105</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>0.00490380053682172</v>
+        <v>0.00490380053681951</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>0.0266760504685213</v>
+        <v>0.0266760504685191</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.00491584384461996</v>
+        <v>0.00491584384461774</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>0.994603955768789</v>
+        <v>0.994603955768794</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>1.10468760520717</v>
+        <v>1.10468766505748</v>
       </c>
     </row>
     <row r="28">
@@ -3175,46 +3175,46 @@
         <v>1143.39024827993</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.929516146892008</v>
+        <v>0.929516146892019</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>1217.8569780938</v>
+        <v>1217.85697809378</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>1113.20473079347</v>
+        <v>1113.20480592845</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>1155.87311522778</v>
+        <v>1155.87311452812</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>1230.09186242009</v>
+        <v>1230.09186242007</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>1230.09186242009</v>
+        <v>1230.09186242007</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>1224.47948183802</v>
+        <v>1224.47948183801</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>1224.47948183802</v>
+        <v>1224.47948183801</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>-0.00995034906632556</v>
+        <v>-0.00995034906633318</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>0.0238430428945875</v>
+        <v>0.0238430428945773</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>-0.00990100813183892</v>
+        <v>-0.00990100813184647</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>1.00543783372214</v>
+        <v>1.00543783372215</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>1.09995892755974</v>
+        <v>1.09995885331878</v>
       </c>
     </row>
     <row r="29">
@@ -3234,7 +3234,7 @@
         <v>1253.57935444932</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>1.04187363953227</v>
+        <v>1.04187363953229</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>1</v>
@@ -3243,37 +3243,37 @@
         <v>1235.27197745011</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>1107.26227312971</v>
+        <v>1107.2625155485</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>1134.45957931418</v>
+        <v>1134.45957865835</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>1203.1971122833</v>
+        <v>1203.19711228328</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>1203.1971122833</v>
+        <v>1203.19711228328</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>1231.80552991618</v>
+        <v>1231.80552991619</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>1231.80552991618</v>
+        <v>1231.80552991619</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>0.00596516264745369</v>
+        <v>0.00596516264747267</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>0.0215792597565372</v>
+        <v>0.0215792597565467</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>0.00598298965954025</v>
+        <v>0.00598298965955935</v>
       </c>
       <c r="R29" s="18" t="n">
-        <v>0.997193777890851</v>
+        <v>0.99719377789086</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>1.11247855165737</v>
+        <v>1.1124783080966</v>
       </c>
     </row>
     <row r="30">
@@ -3293,46 +3293,46 @@
         <v>1449.81126794023</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1.12324381688808</v>
+        <v>1.12324381688799</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>1256.1764669859</v>
+        <v>1256.17646698602</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>1102.23890071255</v>
+        <v>1102.23934516335</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1110.6829483532</v>
+        <v>1110.68294781728</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>1290.73603267802</v>
+        <v>1290.73603267812</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>1290.73603267802</v>
+        <v>1290.73603267812</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>1244.3579695055</v>
+        <v>1244.35796950558</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>1244.3579695055</v>
+        <v>1244.35796950558</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>0.0101387062023118</v>
+        <v>0.010138706202367</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>0.011118678430146</v>
+        <v>0.0111186784302111</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>0.0101902770238229</v>
+        <v>0.0101902770238786</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>0.990591690108033</v>
+        <v>0.990591690108002</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>1.12893672025282</v>
+        <v>1.12893626503703</v>
       </c>
     </row>
     <row r="31">
@@ -3352,46 +3352,46 @@
         <v>1073.94141993997</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.900381458604821</v>
+        <v>0.90038145860472</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>1201.36291431615</v>
+        <v>1201.36291431613</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>1098.73683506995</v>
+        <v>1098.7375194029</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>1085.60896797843</v>
+        <v>1085.60896766311</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>1192.76270038266</v>
+        <v>1192.7627003828</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>1192.76270038266</v>
+        <v>1192.7627003828</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>1189.06524911839</v>
+        <v>1189.06524911837</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>1189.06524911839</v>
+        <v>1189.06524911837</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>-0.0454522162498976</v>
+        <v>-0.0454522162499804</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>-0.0385365194928431</v>
+        <v>-0.0385365194928589</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>-0.0444347380272583</v>
+        <v>-0.0444347380273374</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>0.989763571813969</v>
+        <v>0.989763571813967</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>1.08221114571324</v>
+        <v>1.08221047167349</v>
       </c>
     </row>
     <row r="32">
@@ -3411,46 +3411,46 @@
         <v>1006.17899473794</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.931647594296094</v>
+        <v>0.931647594296492</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>1092.52573848083</v>
+        <v>1092.52573848053</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>1097.47610843732</v>
+        <v>1097.47707332672</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>1061.2036492451</v>
+        <v>1061.20364927836</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>1079.99956303022</v>
+        <v>1079.99956302976</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>1079.99956303022</v>
+        <v>1079.99956302976</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>1089.09872865335</v>
+        <v>1089.09872865313</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>1089.09872865335</v>
+        <v>1089.09872865313</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>-0.0878169937483608</v>
+        <v>-0.0878169937485426</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>-0.110561879715174</v>
+        <v>-0.110561879715344</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>-0.0840715179752862</v>
+        <v>-0.0840715179754528</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>0.996863222799448</v>
+        <v>0.996863222799522</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>0.992366685962846</v>
+        <v>0.992365813485111</v>
       </c>
     </row>
     <row r="33">
@@ -3470,46 +3470,46 @@
         <v>1097.12674299929</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>1.05926121942517</v>
+        <v>1.05926121942526</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>0.402706876665903</v>
+        <v>0.402706876665518</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>981.98117976002</v>
+        <v>981.981179759969</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>1099.23551921591</v>
+        <v>1099.23680773252</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>1039.96877187046</v>
+        <v>1039.96877240915</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>1035.74710645469</v>
+        <v>1035.7471064546</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>1003.63308817028</v>
+        <v>1003.63308817019</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>984.81944589828</v>
+        <v>984.819445898267</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>984.81944589828</v>
+        <v>984.819445898267</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>-0.100647458030675</v>
+        <v>-0.100647458030487</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>-0.20050736745329</v>
+        <v>-0.200507367453307</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>-0.0957482366029447</v>
+        <v>-0.0957482366027748</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>1.00289034677727</v>
+        <v>1.00289034677731</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.895913049280613</v>
+        <v>0.895911999098472</v>
       </c>
     </row>
     <row r="34">
@@ -3529,46 +3529,46 @@
         <v>925.043759968322</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1.10386259851249</v>
+        <v>1.10386259851174</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>0.596425102270288</v>
+        <v>0.596425102269621</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>872.710570145708</v>
+        <v>872.710570146253</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>1104.78294296605</v>
+        <v>1104.78459997407</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1024.50009514068</v>
+        <v>1024.50009637035</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>838.0062529656</v>
+        <v>838.006252966169</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>852.012044222341</v>
+        <v>852.012044222924</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>885.474395048665</v>
+        <v>885.474395049009</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>885.474395048665</v>
+        <v>885.474395049009</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>-0.106334779720318</v>
+        <v>-0.106334779719917</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>-0.288408627783734</v>
+        <v>-0.288408627783503</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>-0.100876410659215</v>
+        <v>-0.100876410658854</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>1.01462549594286</v>
+        <v>1.01462549594262</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.8014917325492</v>
+        <v>0.801490530434433</v>
       </c>
     </row>
     <row r="35">
@@ -3588,46 +3588,46 @@
         <v>751.640121231456</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.900987434804394</v>
+        <v>0.900987434804073</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>841.773184953458</v>
+        <v>841.773184953336</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1114.82650372872</v>
+        <v>1114.82857508039</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>1017.21169992342</v>
+        <v>1017.21170205565</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>834.240403579699</v>
+        <v>834.240403579996</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>834.240403579699</v>
+        <v>834.240403579996</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>855.495684594223</v>
+        <v>855.495684594114</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>855.495684594223</v>
+        <v>855.495684594114</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>-0.0344424919818386</v>
+        <v>-0.0344424919823548</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.280530916845385</v>
+        <v>-0.280530916845463</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>-0.0338561008901833</v>
+        <v>-0.033856100890682</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>1.01630189686017</v>
+        <v>1.01630189686018</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.767380109580171</v>
+        <v>0.767378683787706</v>
       </c>
     </row>
     <row r="36">
@@ -3647,46 +3647,46 @@
         <v>839.434712132987</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.931163759286297</v>
+        <v>0.931163759287965</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>883.713693481832</v>
+        <v>883.713693480859</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>1129.91634373315</v>
+        <v>1129.91887523318</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1019.65522683176</v>
+        <v>1019.65523009797</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>901.489886995154</v>
+        <v>901.489886993539</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>901.489886995154</v>
+        <v>901.489886993539</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>886.168604033112</v>
+        <v>886.168604032376</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>886.168604033112</v>
+        <v>886.168604032376</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>0.0352261814952865</v>
+        <v>0.0352261814945845</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>-0.186328492799873</v>
+        <v>-0.186328492800384</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>0.0358539733060572</v>
+        <v>0.03585397330533</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>1.00277794784599</v>
+        <v>1.00277794784626</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>0.784278065317019</v>
+        <v>0.784276308199115</v>
       </c>
     </row>
     <row r="37">
@@ -3706,46 +3706,46 @@
         <v>979.295252197054</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>1.07916764348186</v>
+        <v>1.07916764348187</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>907.529823709129</v>
+        <v>907.52982370898</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>1150.42723889598</v>
+        <v>1150.43027500696</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1032.46745999707</v>
+        <v>1032.46746463788</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>907.45423856244</v>
+        <v>907.454238562431</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>907.45423856244</v>
+        <v>907.454238562431</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>915.610061324458</v>
+        <v>915.610061324423</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>915.610061324458</v>
+        <v>915.610061324423</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>0.032683346288812</v>
+        <v>0.0326833462896037</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>-0.070276216480164</v>
+        <v>-0.0702762164801872</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>0.033223313438721</v>
+        <v>0.033223313439539</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>1.00890355049965</v>
+        <v>1.00890355049977</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>0.795886980390982</v>
+        <v>0.795884879958402</v>
       </c>
     </row>
     <row r="38">
@@ -3765,46 +3765,46 @@
         <v>1025.67860484186</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1.08417885640001</v>
+        <v>1.0841788563983</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>970.103942586831</v>
+        <v>970.103942588299</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>1176.59119859841</v>
+        <v>1176.59478085856</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>1055.69435685152</v>
+        <v>1055.69436310042</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>946.041881177797</v>
+        <v>946.041881179289</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>946.041881177797</v>
+        <v>946.041881179289</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>977.417460235857</v>
+        <v>977.417460236894</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>977.417460235857</v>
+        <v>977.417460236894</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>0.065323271842587</v>
+        <v>0.065323271843685</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>0.103834809567971</v>
+        <v>0.103834809568712</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>0.0675040626159062</v>
+        <v>0.0675040626170784</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>1.00753890106819</v>
+        <v>1.00753890106774</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>0.830719676808892</v>
+        <v>0.83071714760087</v>
       </c>
     </row>
     <row r="39">
@@ -3824,46 +3824,46 @@
         <v>1000.69836644118</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.901422993523258</v>
+        <v>0.901422993522309</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>1081.07321788891</v>
+        <v>1081.07321788967</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>1208.4883740964</v>
+        <v>1208.49253922207</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1088.75680872011</v>
+        <v>1088.75681678026</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>1110.1318400254</v>
+        <v>1110.13184002656</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>1110.1318400254</v>
+        <v>1110.13184002656</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>1082.80158534398</v>
+        <v>1082.80158534435</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>1082.80158534398</v>
+        <v>1082.80158534435</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>0.102393173216433</v>
+        <v>0.102393173215709</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.26570081514505</v>
+        <v>0.265700815145637</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>0.107818950853091</v>
+        <v>0.10781895085229</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>1.00159875152438</v>
+        <v>1.00159875152402</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>0.895996691861936</v>
+        <v>0.895993603768018</v>
       </c>
     </row>
     <row r="40">
@@ -3883,46 +3883,46 @@
         <v>1086.52423367125</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.932718264240354</v>
+        <v>0.932718264242253</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>1189.56260180463</v>
+        <v>1189.56260180146</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>1246.05482332255</v>
+        <v>1246.05960096927</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>1130.52744454947</v>
+        <v>1130.52745456245</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>1164.90078014733</v>
+        <v>1164.90078014496</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>1164.90078014733</v>
+        <v>1164.90078014496</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>1177.80238138162</v>
+        <v>1177.80238137948</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>1177.80238138162</v>
+        <v>1177.80238137948</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>0.084098570543757</v>
+        <v>0.084098570541603</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>0.329095136096261</v>
+        <v>0.329095136094948</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>0.0877361072642522</v>
+        <v>0.0877361072619092</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>0.990113828053129</v>
+        <v>0.990113828053968</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>0.945225169339713</v>
+        <v>0.945221545151856</v>
       </c>
     </row>
     <row r="41">
@@ -3942,46 +3942,46 @@
         <v>1387.01112527143</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1.09103844378908</v>
+        <v>1.09103844379336</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>1246.60401004275</v>
+        <v>1246.60401004189</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>1289.16513137565</v>
+        <v>1289.17054153494</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>1179.98576844277</v>
+        <v>1179.98578044828</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>1271.27612520643</v>
+        <v>1271.27612520144</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>1271.27612520643</v>
+        <v>1271.27612520144</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>1240.44195147563</v>
+        <v>1240.44195147463</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>1240.44195147563</v>
+        <v>1240.44195147463</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>0.0518174151815162</v>
+        <v>0.0518174151825267</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.354770992447691</v>
+        <v>0.354770992446649</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>0.0531834296518614</v>
+        <v>0.0531834296529257</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>0.995056923836695</v>
+        <v>0.995056923836578</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>0.962205633154203</v>
+        <v>0.962201595141711</v>
       </c>
     </row>
     <row r="42">
@@ -4001,46 +4001,46 @@
         <v>1344.70366909301</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1.07206236865545</v>
+        <v>1.07206236864832</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>1265.64713671446</v>
+        <v>1265.64713671646</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>1337.64316207751</v>
+        <v>1337.64921209084</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>1236.28315118116</v>
+        <v>1236.28316506695</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>1254.31477534232</v>
+        <v>1254.31477535066</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>1254.31477534232</v>
+        <v>1254.31477535066</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>1263.74750446561</v>
+        <v>1263.74750446761</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>1263.74750446561</v>
+        <v>1263.74750446761</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>0.0186137880473975</v>
+        <v>0.0186137880497854</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0.292945497577525</v>
+        <v>0.292945497578198</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>0.0187881044834548</v>
+        <v>0.0187881044858875</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>0.998499082253068</v>
+        <v>0.998499082253069</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>0.94475682326434</v>
+        <v>0.94475255025365</v>
       </c>
     </row>
     <row r="43">
@@ -4060,46 +4060,46 @@
         <v>1151.18082419785</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.902827198409504</v>
+        <v>0.902827198412127</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>1278.88937793055</v>
+        <v>1278.88937793292</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>1391.30159862107</v>
+        <v>1391.30827979853</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>1299.02741532961</v>
+        <v>1299.02743077143</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>1275.08434197138</v>
+        <v>1275.08434196768</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>1275.08434197138</v>
+        <v>1275.08434196768</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>1286.19998165792</v>
+        <v>1286.19998165909</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>1286.19998165792</v>
+        <v>1286.19998165909</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>0.0176106038131033</v>
+        <v>0.0176106038124353</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.187844568263468</v>
+        <v>0.187844568264152</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>0.0177665847908455</v>
+        <v>0.0177665847901656</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>1.00571636910395</v>
+        <v>1.005716369103</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>0.924458063537538</v>
+        <v>0.924453624214283</v>
       </c>
     </row>
     <row r="44">
@@ -4119,46 +4119,46 @@
         <v>1247.82293557512</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.9309912740574</v>
+        <v>0.930991274054785</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>1332.79147643428</v>
+        <v>1332.79147643215</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>1449.9010439576</v>
+        <v>1449.9083277966</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>1367.91654157388</v>
+        <v>1367.9165579661</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>1340.31646734659</v>
+        <v>1340.31646735036</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>1340.31646734659</v>
+        <v>1340.31646735036</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>1340.15977611636</v>
+        <v>1340.15977611552</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>1340.15977611636</v>
+        <v>1340.15977611552</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>0.0410967223045683</v>
+        <v>0.0410967223030267</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.137847738552106</v>
+        <v>0.137847738553458</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>0.0419528807556739</v>
+        <v>0.0419528807540677</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>1.00552847149188</v>
+        <v>1.00552847149285</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>0.924311201582636</v>
+        <v>0.924306558161601</v>
       </c>
     </row>
     <row r="45">
@@ -4178,46 +4178,46 @@
         <v>1544.43982105477</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>1.09930658809129</v>
+        <v>1.09930658809692</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>1414.479524396</v>
+        <v>1414.47952439662</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>1513.12946525291</v>
+        <v>1513.13729926251</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>1442.52879523297</v>
+        <v>1442.52881161133</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>1404.92182780088</v>
+        <v>1404.92182779369</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>1404.92182780088</v>
+        <v>1404.92182779369</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>1419.1136080458</v>
+        <v>1419.11360804459</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>1419.1136080458</v>
+        <v>1419.11360804459</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>0.0572436142583732</v>
+        <v>0.0572436142581482</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.144038708427772</v>
+        <v>0.144038708427718</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>0.0589137454626765</v>
+        <v>0.0589137454624382</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>1.0032761758441</v>
+        <v>1.0032761758428</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>0.93786661395071</v>
+        <v>0.937861758305909</v>
       </c>
     </row>
     <row r="46">
@@ -4237,46 +4237,46 @@
         <v>1628.14312336858</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1.06672947249918</v>
+        <v>1.06672947249514</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>1523.12820100905</v>
+        <v>1523.12820100023</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>1580.60633931249</v>
+        <v>1580.61464246091</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>1522.30444125472</v>
+        <v>1522.30445621441</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>1526.29430923484</v>
+        <v>1526.29430924062</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>1526.29430923484</v>
+        <v>1526.29430924062</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>1522.29287969058</v>
+        <v>1522.29287968633</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>1522.29287969058</v>
+        <v>1522.29287968633</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0.0701852147146948</v>
+        <v>0.070185214712759</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0.204586259764203</v>
+        <v>0.204586259758938</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>0.0727068439480745</v>
+        <v>0.0727068439459979</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>0.999451575174092</v>
+        <v>0.999451575177091</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>0.963106905134092</v>
+        <v>0.96310184582133</v>
       </c>
     </row>
     <row r="47">
@@ -4296,46 +4296,46 @@
         <v>1470.67718086851</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.901337419677859</v>
+        <v>0.901337419689653</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>1623.940714316</v>
+        <v>1623.94071432103</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>1651.88351316836</v>
+        <v>1651.89217098684</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>1606.49570974981</v>
+        <v>1606.49572136354</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>1631.66107249174</v>
+        <v>1631.66107247039</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>1631.66107249174</v>
+        <v>1631.66107247039</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>1620.2462778318</v>
+        <v>1620.24627783415</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>1620.2462778318</v>
+        <v>1620.24627783415</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>0.062360489307292</v>
+        <v>0.0623604893115308</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>0.259715674807658</v>
+        <v>0.259715674808334</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>0.0643459609172823</v>
+        <v>0.0643459609217938</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>0.997725017636648</v>
+        <v>0.997725017635004</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>0.980847780679234</v>
+        <v>0.980842639908038</v>
       </c>
     </row>
     <row r="48">
@@ -4355,46 +4355,46 @@
         <v>1577.11367430347</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.932448208540931</v>
+        <v>0.932448208515398</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>1702.59001323425</v>
+        <v>1702.59001324888</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>1726.47888883378</v>
+        <v>1726.48774822701</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>1694.37478016883</v>
+        <v>1694.37478591205</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>1691.36865710889</v>
+        <v>1691.3686571552</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>1691.36865710889</v>
+        <v>1691.3686571552</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>1698.82647874115</v>
+        <v>1698.82647875509</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>1698.82647874115</v>
+        <v>1698.82647875509</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>0.0473595450251145</v>
+        <v>0.0473595450318714</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>0.267629807293694</v>
+        <v>0.267629807304894</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>0.0484989238885951</v>
+        <v>0.0484989238956797</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>0.997789523923053</v>
+        <v>0.997789523922667</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>0.983983348842848</v>
+        <v>0.983978299585194</v>
       </c>
     </row>
     <row r="49">
@@ -4414,46 +4414,46 @@
         <v>1958.50082068495</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1.09972067028314</v>
+        <v>1.09972067029272</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>1769.14027916881</v>
+        <v>1769.14027918263</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>1803.89772929659</v>
+        <v>1803.90659313161</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>1785.33965877609</v>
+        <v>1785.3396554688</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>1780.90752825507</v>
+        <v>1780.90752823955</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>1780.90752825507</v>
+        <v>1780.90752823955</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>1769.03192032413</v>
+        <v>1769.03192032806</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>1769.03192032413</v>
+        <v>1769.03192032806</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>0.0404947532227977</v>
+        <v>0.0404947532168095</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.246575263808647</v>
+        <v>0.246575263812476</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>0.0413258460834749</v>
+        <v>0.0413258460772392</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>0.99993875056379</v>
+        <v>0.999938750558197</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>0.98067195916586</v>
+        <v>0.980667140451543</v>
       </c>
     </row>
     <row r="50">
@@ -4473,46 +4473,46 @@
         <v>1945.13754028478</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1.0670308987955</v>
+        <v>1.06703089879526</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>1826.98871225255</v>
+        <v>1826.98871220342</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>1883.62335364977</v>
+        <v>1883.63197521886</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>1878.77332122057</v>
+        <v>1878.77330499888</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>1822.94396767752</v>
+        <v>1822.94396767793</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>1822.94396767752</v>
+        <v>1822.94396767793</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>1831.79961159612</v>
+        <v>1831.79961156794</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>1831.79961159612</v>
+        <v>1831.79961156794</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>0.0348664186619401</v>
+        <v>0.0348664186443345</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>0.203316152913006</v>
+        <v>0.203316152897846</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>0.0354813785725747</v>
+        <v>0.0354813785543444</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>1.0026332397739</v>
+        <v>1.00263323978544</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>0.97248720560125</v>
+        <v>0.972482754416555</v>
       </c>
     </row>
     <row r="51">
@@ -4532,46 +4532,46 @@
         <v>1712.91881357271</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0.901345045813399</v>
+        <v>0.901345045859905</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>1910.54382484879</v>
+        <v>1910.54382485871</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>1965.12471211068</v>
+        <v>1965.13278959148</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>1974.03658249866</v>
+        <v>1974.03654883122</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>1900.40298277439</v>
+        <v>1900.40298267634</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>1900.40298277439</v>
+        <v>1900.40298267634</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>1916.21848629897</v>
+        <v>1916.21848629299</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>1916.21848629897</v>
+        <v>1916.21848629299</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>0.0450548276098476</v>
+        <v>0.0450548276221128</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>0.182671123838803</v>
+        <v>0.182671123833396</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>0.0460852126883533</v>
+        <v>0.0460852127011837</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>1.00297018125226</v>
+        <v>1.00297018124392</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>0.97511291496651</v>
+        <v>0.97510890685985</v>
       </c>
     </row>
     <row r="52">
@@ -4591,46 +4591,46 @@
         <v>1898.85436922996</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.930298383682062</v>
+        <v>0.930298383603775</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>2021.33452895548</v>
+        <v>2021.33452898574</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>2047.83283028044</v>
+        <v>2047.84000134742</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>2070.21111083905</v>
+        <v>2070.21105460816</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>2041.12401196959</v>
+        <v>2041.12401214136</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>2041.12401196959</v>
+        <v>2041.12401214136</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>2029.37222232304</v>
+        <v>2029.37222233992</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>2029.37222232304</v>
+        <v>2029.37222233992</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>0.0573727895762769</v>
+        <v>0.057372789587717</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>0.194572987717282</v>
+        <v>0.194572987717415</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>0.0590505398174161</v>
+        <v>0.0590505398295318</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>1.00397642906329</v>
+        <v>1.00397642905661</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.990985295437974</v>
+        <v>0.990981825242526</v>
       </c>
     </row>
     <row r="53">
@@ -4650,46 +4650,46 @@
         <v>2354.10436983294</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1.10270872980271</v>
+        <v>1.10270872989463</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>2166.58784122052</v>
+        <v>2166.58784114105</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>2131.13828267931</v>
+        <v>2131.14411945535</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>2166.01040647179</v>
+        <v>2166.01032214123</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>2134.83788257859</v>
+        <v>2134.83788240063</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>2134.83788257859</v>
+        <v>2134.83788240063</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>2155.07297510159</v>
+        <v>2155.07297482541</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>2155.07297510159</v>
+        <v>2155.07297482541</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>0.0600980909997007</v>
+        <v>0.0600980908632322</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>0.218221644472485</v>
+        <v>0.218221644313667</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>0.0619407082623089</v>
+        <v>0.0619407081173875</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>0.994685253050969</v>
+        <v>0.994685252959985</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>1.01123094292698</v>
+        <v>1.01122817323879</v>
       </c>
     </row>
     <row r="54">
@@ -4709,46 +4709,46 @@
         <v>2600.12971883191</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>1.06458671078362</v>
+        <v>1.06458671063023</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>0.0387982256014614</v>
+        <v>0.0387982204834509</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>2304.1280308078</v>
+        <v>2304.12803057205</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>2214.42745081615</v>
+        <v>2214.43145539067</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>2260.00253413258</v>
+        <v>2260.00241602968</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>2442.3841594998</v>
+        <v>2442.38415985171</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>2309.49212327958</v>
+        <v>2309.49212235903</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>2284.91025847308</v>
+        <v>2284.91025788842</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>2284.91025847308</v>
+        <v>2284.91025788842</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>0.0585021632451484</v>
+        <v>0.0585021631174207</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>0.247358195737437</v>
+        <v>0.247358195437459</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>0.0602472792668995</v>
+        <v>0.0602472791314765</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>0.991659416457</v>
+        <v>0.991659416304719</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>1.03182890802359</v>
+        <v>1.03182704180171</v>
       </c>
     </row>
     <row r="55">
@@ -4768,46 +4768,46 @@
         <v>2154.1851770688</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.902912275854565</v>
+        <v>0.902912275975512</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>2401.05607792804</v>
+        <v>2401.05607751034</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>2297.08902844972</v>
+        <v>2297.09062923062</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>2350.59969593767</v>
+        <v>2350.59953867401</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>2385.81890475458</v>
+        <v>2385.81890443499</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>2385.81890475458</v>
+        <v>2385.81890443499</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>2394.29727396351</v>
+        <v>2394.29727343993</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>2394.29727396351</v>
+        <v>2394.29727343993</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>0.0467630246309839</v>
+        <v>0.0467630246681838</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>0.249490750184708</v>
+        <v>0.249490749915373</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>0.0478736594073199</v>
+        <v>0.0478736594463007</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>0.997185070341897</v>
+        <v>0.997185070297309</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>1.0423180139341</v>
+        <v>1.04231728734267</v>
       </c>
     </row>
     <row r="56">
@@ -4827,46 +4827,46 @@
         <v>2321.41186175029</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.930030784566603</v>
+        <v>0.930030784765797</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>2511.24096847412</v>
+        <v>2511.24096798117</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>2378.57112475909</v>
+        <v>2378.56967396931</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>2436.46154194904</v>
+        <v>2436.46134100639</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>2496.05916306531</v>
+        <v>2496.05916253071</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>2496.05916306531</v>
+        <v>2496.05916253071</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>2517.01602969518</v>
+        <v>2517.01602946351</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>2517.01602969518</v>
+        <v>2517.01602946351</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>0.0499843106899972</v>
+        <v>0.0499843108166302</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>0.240292934932328</v>
+        <v>0.240292934807848</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>0.0512546027872829</v>
+        <v>0.0512546029204064</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>1.00229968421731</v>
+        <v>1.0022996843218</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>1.05820507257277</v>
+        <v>1.05820571791919</v>
       </c>
     </row>
     <row r="57">
@@ -4886,46 +4886,46 @@
         <v>2970.00973852471</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1.10404076175311</v>
+        <v>1.10404076156347</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>2671.11548266478</v>
+        <v>2671.1154842476</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>2458.377305096</v>
+        <v>2458.37207777282</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>2516.42381827274</v>
+        <v>2516.42357078779</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>2690.12688789553</v>
+        <v>2690.12688835761</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>2690.12688789553</v>
+        <v>2690.12688835761</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>2664.04751670422</v>
+        <v>2664.04751765615</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>2664.04751670422</v>
+        <v>2664.04751765615</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>0.0567725044150701</v>
+        <v>0.0567725048644387</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>0.23617508431641</v>
+        <v>0.236175084916541</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>0.0584149982655615</v>
+        <v>0.0584149987411799</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>0.997353927223877</v>
+        <v>0.997353926989254</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>1.0836609625308</v>
+        <v>1.08366326714452</v>
       </c>
     </row>
     <row r="58">
@@ -4945,46 +4945,46 @@
         <v>2943.99757674031</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>1.0590387420829</v>
+        <v>1.0590387407807</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>2773.86896383624</v>
+        <v>2773.86896446549</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>2536.08456483617</v>
+        <v>2536.07475973761</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>2589.62025912042</v>
+        <v>2589.61996488681</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>2779.8771279605</v>
+        <v>2779.87713137865</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>2779.8771279605</v>
+        <v>2779.87713137865</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>2771.49082723364</v>
+        <v>2771.49082751269</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>2771.49082723364</v>
+        <v>2771.49082751269</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0.0395387910767331</v>
+        <v>0.0395387908200955</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>0.212953907907842</v>
+        <v>0.212953908340338</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>0.0403308536562224</v>
+        <v>0.0403308533892344</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>0.999142664403544</v>
+        <v>0.999142664277489</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>1.09282271800455</v>
+        <v>1.09282694324021</v>
       </c>
     </row>
     <row r="59">
@@ -5004,46 +5004,46 @@
         <v>2579.42813442157</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0.909504021479654</v>
+        <v>0.909504023462221</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>2887.05647488818</v>
+        <v>2887.05647042638</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>2611.41474284452</v>
+        <v>2611.39948571675</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>2656.05311405184</v>
+        <v>2656.05277675988</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>2836.08216511803</v>
+        <v>2836.08215893585</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>2836.08216511803</v>
+        <v>2836.08215893585</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2863.46681568099</v>
+        <v>2863.46681228152</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>2863.46681568099</v>
+        <v>2863.46681228152</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>0.0326476838614019</v>
+        <v>0.0326476825735274</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>0.195952919806329</v>
+        <v>0.195952918648036</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>0.0331864668443305</v>
+        <v>0.033186465513716</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>0.991829165999221</v>
+        <v>0.991829166354555</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.09651935738171</v>
+        <v>1.09652576250531</v>
       </c>
     </row>
     <row r="60">
@@ -5063,46 +5063,46 @@
         <v>2838.16101860859</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>0.926665436144795</v>
+        <v>0.926665437336485</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.531286024823208</v>
+        <v>0.531286017005079</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>2932.74826691724</v>
+        <v>2932.74826362613</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>2684.24204833796</v>
+        <v>2684.22039804558</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>2716.67591697094</v>
+        <v>2716.67554569591</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>3062.76775619924</v>
+        <v>3062.76775226053</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>3001.82580452742</v>
+        <v>3001.82579987574</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>2900.93996836305</v>
+        <v>2900.93996633742</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>2900.93996836305</v>
+        <v>2900.93996633742</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>0.0130017474384644</v>
+        <v>0.0130017479273876</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0.152531384043017</v>
+        <v>0.152531383344329</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>0.0130866376648209</v>
+        <v>0.0130866381601424</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>0.989154098593118</v>
+        <v>0.989154099012447</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.08072964960789</v>
+        <v>1.08073836576521</v>
       </c>
     </row>
     <row r="61">
@@ -5122,46 +5122,46 @@
         <v>3062.56234200586</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>1.10800775101377</v>
+        <v>1.10800774805415</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>2804.85501895972</v>
+        <v>2804.85502615529</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>2754.5811076723</v>
+        <v>2754.5520657302</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>2773.34234703703</v>
+        <v>2773.34195789467</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>2764.02609927933</v>
+        <v>2764.02610666238</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>2764.02609927933</v>
+        <v>2764.02610666238</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>2788.18415446001</v>
+        <v>2788.18415925912</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>2788.18415446001</v>
+        <v>2788.18415925912</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>-0.0396442682471649</v>
+        <v>-0.0396442658276678</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.0465970058632306</v>
+        <v>0.0465970072906925</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>-0.0388687167375843</v>
+        <v>-0.03886871441213</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>0.994056425595255</v>
+        <v>0.994056424756105</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>1.01219896800066</v>
+        <v>1.01220964161373</v>
       </c>
     </row>
     <row r="62">
@@ -5181,46 +5181,46 @@
         <v>2755.1961460775</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>1.05045545748411</v>
+        <v>1.05045545384675</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>2624.79751929735</v>
+        <v>2624.79752296184</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>2822.64503705099</v>
+        <v>2822.60756115286</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>2829.33183284717</v>
+        <v>2829.33145082684</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>2622.85861475395</v>
+        <v>2622.85862383599</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>2622.85861475395</v>
+        <v>2622.85862383599</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>2642.56176094911</v>
+        <v>2642.56176265453</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>2642.56176094911</v>
+        <v>2642.56176265453</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>-0.0536417325938885</v>
+        <v>-0.0536417336697503</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>-0.0465197521195567</v>
+        <v>-0.0465197516002114</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>-0.0522283986435994</v>
+        <v>-0.0522283996632706</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>1.00676785219475</v>
+        <v>1.00676785143894</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>0.936200523360872</v>
+        <v>0.936212953945044</v>
       </c>
     </row>
     <row r="63">
@@ -5240,46 +5240,46 @@
         <v>2346.01620451565</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0.916232298654267</v>
+        <v>0.916232305354833</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>2533.47973393037</v>
+        <v>2533.47971696673</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>2888.65285579721</v>
+        <v>2888.60587797139</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>2887.87722175964</v>
+        <v>2887.87688270695</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>2560.50371500918</v>
+        <v>2560.50369628377</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>2560.50371500918</v>
+        <v>2560.50369628377</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>2566.55798655187</v>
+        <v>2566.5579748969</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>2566.55798655187</v>
+        <v>2566.5579748969</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>-0.0291831142621293</v>
+        <v>-0.0291831194485888</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>-0.10368858738058</v>
+        <v>-0.103688590386719</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>-0.0287613994572986</v>
+        <v>-0.0287614044945883</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>1.01305645045369</v>
+        <v>1.01305645263652</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>0.888496511929796</v>
+        <v>0.888510957645539</v>
       </c>
     </row>
     <row r="64">
@@ -5299,46 +5299,46 @@
         <v>2313.68685692728</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>0.927837000316897</v>
+        <v>0.927837006402059</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>0.658289832679701</v>
+        <v>0.658289879807384</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>2577.71465804575</v>
+        <v>2577.71464773665</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>2952.69871672022</v>
+        <v>2952.64116675781</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>2951.17899504226</v>
+        <v>2951.17874761456</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>2493.63504164746</v>
+        <v>2493.63502529311</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>2522.36590143515</v>
+        <v>2522.36588318404</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>2607.63739897013</v>
+        <v>2607.63739328193</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>2607.63739897013</v>
+        <v>2607.63739328193</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>0.0158789038678709</v>
+        <v>0.0158789062275997</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>-0.101106045830528</v>
+        <v>-0.101106047163674</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>0.0160056436026403</v>
+        <v>0.0160056460001381</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>1.01160824408201</v>
+        <v>1.01160824592107</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>0.883136970326123</v>
+        <v>0.883154181632333</v>
       </c>
     </row>
     <row r="65">
@@ -5358,46 +5358,46 @@
         <v>3129.72211611434</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.10774307907342</v>
+        <v>1.10774306634076</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>2789.05101999878</v>
+        <v>2789.05104443279</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>3014.67167941628</v>
+        <v>3014.60251422055</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>3019.80076642909</v>
+        <v>3019.8006736971</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>2825.31407800103</v>
+        <v>2825.31411047585</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>2825.31407800103</v>
+        <v>2825.31411047585</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>2802.98370993049</v>
+        <v>2802.9837277893</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>2802.98370993049</v>
+        <v>2802.9837277893</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>0.0722398602495252</v>
+        <v>0.0722398688022427</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>0.00530795480162394</v>
+        <v>0.00530795947643159</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>0.0749131420793065</v>
+        <v>0.074913151272735</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>1.00499549482308</v>
+        <v>1.00499549242181</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>0.92978075492228</v>
+        <v>0.929802093167174</v>
       </c>
     </row>
     <row r="66">
@@ -5417,46 +5417,46 @@
         <v>3164.98577161261</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>1.04147661911105</v>
+        <v>1.04147661063353</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>3058.61952391388</v>
+        <v>3058.61954194895</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>3074.19184547211</v>
+        <v>3074.11008501585</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>3092.16208418616</v>
+        <v>3092.16222477988</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>3038.94078228475</v>
+        <v>3038.94080702144</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>3038.94078228475</v>
+        <v>3038.94080702144</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>3033.33150639749</v>
+        <v>3033.33151376016</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>3033.33150639749</v>
+        <v>3033.33151376016</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>0.0789770620574046</v>
+        <v>0.0789770581133029</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>0.147875350057302</v>
+        <v>0.147875352102683</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>0.0821794988143969</v>
+        <v>0.0821794945461709</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>0.991732212091543</v>
+        <v>0.991732208651007</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.98670859167921</v>
+        <v>0.986734837033177</v>
       </c>
     </row>
     <row r="67">
@@ -5476,46 +5476,46 @@
         <v>2987.75245463425</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>0.924963422634777</v>
+        <v>0.924963437667698</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>3186.01444582474</v>
+        <v>3186.01437251162</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>3130.76096797352</v>
+        <v>3130.66573854758</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>3165.71006313735</v>
+        <v>3165.71053187209</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>3230.13038301945</v>
+        <v>3230.13033052192</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>3230.13038301945</v>
+        <v>3230.13033052192</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>3174.02679964481</v>
+        <v>3174.02675057168</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>3174.02679964481</v>
+        <v>3174.02675057168</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>0.0453395429929773</v>
+        <v>0.0453395251048791</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>0.236686182925121</v>
+        <v>0.236686169420812</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>0.0463830916438184</v>
+        <v>0.0463830729260151</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>0.996237416250376</v>
+        <v>0.996237423772043</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>1.01381958958665</v>
+        <v>1.01385041254651</v>
       </c>
     </row>
     <row r="68">
@@ -5535,46 +5535,46 @@
         <v>2968.07680589468</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>0.928421771114008</v>
+        <v>0.928421804811794</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>3244.08406064927</v>
+        <v>3244.08404039134</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>3183.85876809186</v>
+        <v>3183.74935342088</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>3237.62571159706</v>
+        <v>3237.62661889411</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>3196.9056502556</v>
+        <v>3196.90553422144</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>3196.9056502556</v>
+        <v>3196.90553422144</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>3240.51202174698</v>
+        <v>3240.51200080778</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>3240.51202174698</v>
+        <v>3240.51200080778</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.0207302831610304</v>
+        <v>0.0207302921601798</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>0.242700393477562</v>
+        <v>0.242700388158391</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.0209466479960443</v>
+        <v>0.0209466571836958</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>0.998898906799113</v>
+        <v>0.998898906582234</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>1.01779389658326</v>
+        <v>1.01782886813182</v>
       </c>
     </row>
     <row r="69">
@@ -5594,46 +5594,46 @@
         <v>3696.32832846722</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1.10731291388403</v>
+        <v>1.10731284727188</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>3306.91257772163</v>
+        <v>3306.91265515426</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>3233.02707288285</v>
+        <v>3232.90297361086</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>3305.41213947906</v>
+        <v>3305.41360875961</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>3338.10640345728</v>
+        <v>3338.10660426634</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>3338.10640345728</v>
+        <v>3338.10660426634</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>3320.79147537905</v>
+        <v>3320.79153685842</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>3320.79147537905</v>
+        <v>3320.79153685842</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>0.0244718019930672</v>
+        <v>0.0244718269682295</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>0.184734489756062</v>
+        <v>0.18473450414124</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>0.0247736941240504</v>
+        <v>0.0247737197179401</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>1.00419693515665</v>
+        <v>1.00419693023416</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>1.02714620091874</v>
+        <v>1.02718564830586</v>
       </c>
     </row>
     <row r="70">
@@ -5653,46 +5653,46 @@
         <v>3523.50222767909</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>1.03327073455273</v>
+        <v>1.03327074657198</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>3437.22753060391</v>
+        <v>3437.22756504671</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>3277.81586370359</v>
+        <v>3277.67686570563</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>3366.36885639044</v>
+        <v>3366.37101895886</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>3410.04744434604</v>
+        <v>3410.04740467956</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>3410.04744434604</v>
+        <v>3410.04740467956</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>3438.01876622669</v>
+        <v>3438.01877287324</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>3438.01876622669</v>
+        <v>3438.01877287324</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>0.0346922147026979</v>
+        <v>0.0346921981224809</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0.133413462714405</v>
+        <v>0.133413462154495</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>0.0353010093276802</v>
+        <v>0.035300992162165</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>1.00023019588192</v>
+        <v>1.00023018779279</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>1.04887489388805</v>
+        <v>1.04891937605115</v>
       </c>
     </row>
     <row r="71">
@@ -5712,46 +5712,46 @@
         <v>3347.59534135146</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>0.931472709678121</v>
+        <v>0.931472734272011</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>3575.99254979868</v>
+        <v>3575.99237133013</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>3317.84079649278</v>
+        <v>3317.68704856248</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>3417.95884325818</v>
+        <v>3417.96183195967</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>3593.87377275739</v>
+        <v>3593.87367786751</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>3593.87377275739</v>
+        <v>3593.87367786751</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>3574.58962233801</v>
+        <v>3574.5895070794</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>3574.58962233801</v>
+        <v>3574.5895070794</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>0.0389550131848365</v>
+        <v>0.0389549790077133</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>0.126200201818719</v>
+        <v>0.12620018291767</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>0.0397237087397324</v>
+        <v>0.0397236732049677</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>0.999607681660089</v>
+        <v>0.999607699316705</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>1.07738431154281</v>
+        <v>1.07743420484106</v>
       </c>
     </row>
     <row r="72">
@@ -5771,46 +5771,46 @@
         <v>3450.41139520334</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>0.932401618206992</v>
+        <v>0.932401676558435</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>3712.71083218678</v>
+        <v>3712.71081053977</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>3352.80017192701</v>
+        <v>3352.63227262553</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>3457.86347394903</v>
+        <v>3457.86741215847</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>3700.56349949122</v>
+        <v>3700.56326790303</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>3700.56349949122</v>
+        <v>3700.56326790303</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>3694.90518351219</v>
+        <v>3694.90514943896</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>3694.90518351219</v>
+        <v>3694.90514943896</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>0.033104514713859</v>
+        <v>0.0331045377360504</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>0.140222643432825</v>
+        <v>0.140222640285826</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>0.0336585661252742</v>
+        <v>0.0336585899223598</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>0.995204138032991</v>
+        <v>0.995204134658087</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>1.1020356102489</v>
+        <v>1.1020907898573</v>
       </c>
     </row>
     <row r="73">
@@ -5830,46 +5830,46 @@
         <v>4175.47231114959</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>1.10327386969713</v>
+        <v>1.10327374674385</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>3773.83838605993</v>
+        <v>3773.83853519508</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>3382.56481129304</v>
+        <v>3382.38390498223</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>3484.64369697724</v>
+        <v>3484.64868318122</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>3784.61996230894</v>
+        <v>3784.62038408227</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>3784.61996230894</v>
+        <v>3784.62038408227</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>3751.22870516396</v>
+        <v>3751.22882753617</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>3751.22870516396</v>
+        <v>3751.22882753617</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>0.0151285477091849</v>
+        <v>0.0151285895527656</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>0.129618867362268</v>
+        <v>0.12961888329942</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>0.0152435634622232</v>
+        <v>0.01524360594365</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>0.994008837002801</v>
+        <v>0.994008830147858</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>1.10898945458195</v>
+        <v>1.10904880490078</v>
       </c>
     </row>
     <row r="74">
@@ -5889,46 +5889,46 @@
         <v>3842.8691195722</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>1.0288499355401</v>
+        <v>1.0288499692748</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>3722.99339371286</v>
+        <v>3722.993420475</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>3407.22288795738</v>
+        <v>3407.03076959209</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>3498.07396098476</v>
+        <v>3498.08004793258</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>3735.11139654673</v>
+        <v>3735.11127407711</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>3735.11139654673</v>
+        <v>3735.11127407711</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>3710.6958983217</v>
+        <v>3710.69590780298</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>3710.6958983217</v>
+        <v>3710.69590780298</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>-0.010864008324407</v>
+        <v>-0.0108640383911853</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0.0793122872898926</v>
+        <v>0.0793122879610852</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>-0.0108052081139338</v>
+        <v>-0.0108052378558339</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>0.996696879609852</v>
+        <v>0.996696874991938</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>1.08906755452863</v>
+        <v>1.08912896852037</v>
       </c>
     </row>
     <row r="75">
@@ -5948,46 +5948,46 @@
         <v>3354.26213069839</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>0.934871081284665</v>
+        <v>0.93487111747868</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>3623.64146986333</v>
+        <v>3623.64130562075</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>3427.11385975589</v>
+        <v>3426.91308821404</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>3499.42859594023</v>
+        <v>3499.43576782176</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>3587.94083788439</v>
+        <v>3587.94069897542</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>3587.94083788439</v>
+        <v>3587.94069897542</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>3612.6891858821</v>
+        <v>3612.68918229064</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>3612.6891858821</v>
+        <v>3612.68918229064</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>-0.0267670108395643</v>
+        <v>-0.0267670143888114</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>0.0106584440647415</v>
+        <v>0.0106584756475623</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>-0.026411949436202</v>
+        <v>-0.0264119528917065</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>0.996977547565809</v>
+        <v>0.996977591762981</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.05414915690587</v>
+        <v>1.05421091498221</v>
       </c>
     </row>
     <row r="76">
@@ -6007,46 +6007,46 @@
         <v>3413.57383659744</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>0.937755295089687</v>
+        <v>0.937755373126117</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>0.309497391833462</v>
+        <v>0.30949986429986</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>3494.76660175249</v>
+        <v>3494.76677584293</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>3442.78211484233</v>
+        <v>3442.57613292233</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>3491.16711899005</v>
+        <v>3491.17526038866</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>3640.15415798955</v>
+        <v>3640.15385506979</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>3539.7636712129</v>
+        <v>3539.7640571346</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>3496.40702212657</v>
+        <v>3496.40731253467</v>
       </c>
       <c r="N76" s="14" t="n">
-        <v>3496.40702212657</v>
+        <v>3496.40731253467</v>
       </c>
       <c r="O76" s="15" t="n">
-        <v>-0.0327165457518297</v>
+        <v>-0.0327164616986975</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>-0.0537221258806279</v>
+        <v>-0.0537220385574509</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>-0.0321871486232342</v>
+        <v>-0.0321870672755292</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>1.00046939339905</v>
+        <v>1.00046942665905</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.01557603864998</v>
+        <v>1.01563688863626</v>
       </c>
     </row>
     <row r="77">
@@ -6066,46 +6066,46 @@
         <v>3636.39564268968</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>1.09590729298716</v>
+        <v>1.09590711837113</v>
       </c>
       <c r="G77" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>3347.9086963182</v>
+        <v>3347.90897779938</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>3454.87255823177</v>
+        <v>3454.66581804791</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>3476.19160849039</v>
+        <v>3476.20046782897</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>3318.15990819607</v>
+        <v>3318.16043689408</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>3318.15990819607</v>
+        <v>3318.16043689408</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>3368.06125267616</v>
+        <v>3368.06156587855</v>
       </c>
       <c r="N77" s="14" t="n">
-        <v>3368.06125267616</v>
+        <v>3368.06156587855</v>
       </c>
       <c r="O77" s="15" t="n">
-        <v>-0.0373985932335526</v>
+        <v>-0.0373985833006721</v>
       </c>
       <c r="P77" s="16" t="n">
-        <v>-0.102144519197224</v>
+        <v>-0.102144464993699</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>-0.0367079028952254</v>
+        <v>-0.0367078933269601</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>1.00601944622329</v>
+        <v>1.00601945519212</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>0.974872790792595</v>
+        <v>0.974931221504285</v>
       </c>
     </row>
     <row r="78">
@@ -6125,46 +6125,46 @@
         <v>3401.60556878379</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>1.03198995102189</v>
+        <v>1.03199001066779</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>3327.05323572863</v>
+        <v>3327.05324721695</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>3464.09070841203</v>
+        <v>3463.8888003744</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>3457.64712555851</v>
+        <v>3457.65627632207</v>
       </c>
       <c r="K78" s="11" t="n">
-        <v>3296.1615230996</v>
+        <v>3296.16133259143</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>3296.1615230996</v>
+        <v>3296.16133259143</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>3342.31662906604</v>
+        <v>3342.31662434204</v>
       </c>
       <c r="N78" s="14" t="n">
-        <v>3342.31662906604</v>
+        <v>3342.31662434204</v>
       </c>
       <c r="O78" s="15" t="n">
-        <v>-0.0076731148012491</v>
+        <v>-0.00767320920652527</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>-0.0992749822000436</v>
+        <v>-0.0992749857745805</v>
       </c>
       <c r="Q78" s="17" t="n">
-        <v>-0.00764375160625907</v>
+        <v>-0.00764384528992035</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>1.00458766128942</v>
+        <v>1.00458765640071</v>
       </c>
       <c r="S78" s="19" t="n">
-        <v>0.964846740574581</v>
+        <v>0.964902979558925</v>
       </c>
     </row>
     <row r="79">
@@ -6184,46 +6184,46 @@
         <v>3222.50375079941</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>0.931687020351802</v>
+        <v>0.931687065222562</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>3397.44367019113</v>
+        <v>3397.44365096179</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>3471.05663846463</v>
+        <v>3470.86642082216</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>3437.8885728102</v>
+        <v>3437.89737189272</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>3458.78356186889</v>
+        <v>3458.78339529123</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>3458.78356186889</v>
+        <v>3458.78339529123</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>3394.94267588173</v>
+        <v>3394.94248873126</v>
       </c>
       <c r="N79" s="14" t="n">
-        <v>3394.94267588173</v>
+        <v>3394.94248873126</v>
       </c>
       <c r="O79" s="15" t="n">
-        <v>0.0156227079276156</v>
+        <v>0.0156226542147502</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>-0.0602726940505419</v>
+        <v>-0.0602727449199801</v>
       </c>
       <c r="Q79" s="17" t="n">
-        <v>0.0157453804220815</v>
+        <v>0.0157453258634881</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>0.999263859962906</v>
+        <v>0.999263810533011</v>
       </c>
       <c r="S79" s="19" t="n">
-        <v>0.9780718177458</v>
+        <v>0.978125366151974</v>
       </c>
     </row>
     <row r="80">
@@ -6243,46 +6243,46 @@
         <v>3185.85231014052</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>0.946468361501624</v>
+        <v>0.946468424750118</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>3418.69640861602</v>
+        <v>3418.69534254549</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>3476.2854657303</v>
+        <v>3476.1151906442</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>3418.46342484896</v>
+        <v>3418.47096584699</v>
       </c>
       <c r="K80" s="11" t="n">
-        <v>3366.04205668956</v>
+        <v>3366.04183175116</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>3366.04205668956</v>
+        <v>3366.04183175116</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>3389.42537521054</v>
+        <v>3389.42350510521</v>
       </c>
       <c r="N80" s="14" t="n">
-        <v>3389.42537521054</v>
+        <v>3389.42350510521</v>
       </c>
       <c r="O80" s="15" t="n">
-        <v>-0.0016264748156182</v>
+        <v>-0.00162697143652829</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>-0.0305975952567907</v>
+        <v>-0.0305982106392244</v>
       </c>
       <c r="Q80" s="17" t="n">
-        <v>-0.00162515282228204</v>
+        <v>-0.00162564863598413</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>0.991437954732771</v>
+        <v>0.99143771687521</v>
       </c>
       <c r="S80" s="19" t="n">
-        <v>0.975013533446536</v>
+        <v>0.975060755819509</v>
       </c>
     </row>
     <row r="81">
@@ -6302,46 +6302,46 @@
         <v>3869.93013865163</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1.08365462110772</v>
+        <v>1.08365440476456</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>0.0222090337844789</v>
+        <v>0.0221851017823451</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>3362.19232038989</v>
+        <v>3362.19039958411</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>3480.28463687688</v>
+        <v>3480.1440692026</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>3401.02363122357</v>
+        <v>3401.02869960795</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>3571.18408695176</v>
+        <v>3571.18479991084</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>3366.83382559414</v>
+        <v>3366.8269616273</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>3344.67593692362</v>
+        <v>3344.67233325523</v>
       </c>
       <c r="N81" s="14" t="n">
-        <v>3344.67593692362</v>
+        <v>3344.67233325523</v>
       </c>
       <c r="O81" s="15" t="n">
-        <v>-0.013290592143445</v>
+        <v>-0.0132911178311058</v>
       </c>
       <c r="P81" s="16" t="n">
-        <v>-0.00694325726230627</v>
+        <v>-0.00694441956176473</v>
       </c>
       <c r="Q81" s="17" t="n">
-        <v>-0.0132026622017406</v>
+        <v>-0.0132031809487885</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>0.994790189912683</v>
+        <v>0.994789686410667</v>
       </c>
       <c r="S81" s="19" t="n">
-        <v>0.961035169791473</v>
+        <v>0.961072951793514</v>
       </c>
     </row>
     <row r="82">
@@ -6361,46 +6361,46 @@
         <v>3413.56946580066</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>1.04104168057333</v>
+        <v>1.04104182718984</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>3322.86761579529</v>
+        <v>3322.86609770666</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>3483.49269644155</v>
+        <v>3483.39322001008</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>3386.95903464203</v>
+        <v>3386.96006892819</v>
       </c>
       <c r="K82" s="11" t="n">
-        <v>3278.99403981666</v>
+        <v>3278.99357801517</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>3278.99403981666</v>
+        <v>3278.99357801517</v>
       </c>
       <c r="M82" s="13" t="n">
-        <v>3315.68886854918</v>
+        <v>3315.68672547236</v>
       </c>
       <c r="N82" s="14" t="n">
-        <v>3315.68886854918</v>
+        <v>3315.68672547236</v>
       </c>
       <c r="O82" s="15" t="n">
-        <v>-0.00870440350998933</v>
+        <v>-0.00870397241973668</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>-0.00796685756379201</v>
+        <v>-0.00796749735669433</v>
       </c>
       <c r="Q82" s="17" t="n">
-        <v>-0.00866662986821698</v>
+        <v>-0.00866620251397188</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>0.997839592762591</v>
+        <v>0.997839403688505</v>
       </c>
       <c r="S82" s="19" t="n">
-        <v>0.951828856117946</v>
+        <v>0.951855422587855</v>
       </c>
     </row>
     <row r="83">
@@ -6420,46 +6420,46 @@
         <v>3098.85650879477</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>0.928375728505495</v>
+        <v>0.92837594676369</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>3316.37832946521</v>
+        <v>3316.37818758131</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>3486.27728220446</v>
+        <v>3486.23198338717</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>3377.48852878419</v>
+        <v>3377.48356087041</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>3337.93356896925</v>
+        <v>3337.93278423182</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>3337.93356896925</v>
+        <v>3337.93278423182</v>
       </c>
       <c r="M83" s="13" t="n">
-        <v>3330.61215484658</v>
+        <v>3330.61200987115</v>
       </c>
       <c r="N83" s="14" t="n">
-        <v>3330.61215484658</v>
+        <v>3330.61200987115</v>
       </c>
       <c r="O83" s="15" t="n">
-        <v>0.00449071184830805</v>
+        <v>0.00449131466471476</v>
       </c>
       <c r="P83" s="16" t="n">
-        <v>-0.0189489270296569</v>
+        <v>-0.0189489156513396</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>0.0045008102053723</v>
+        <v>0.00450141573512375</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>1.0042919787694</v>
+        <v>1.00429197802082</v>
       </c>
       <c r="S83" s="19" t="n">
-        <v>0.955349183453519</v>
+        <v>0.955361555324605</v>
       </c>
     </row>
     <row r="84">
@@ -6479,46 +6479,46 @@
         <v>3199.75362495821</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>0.950162001853865</v>
+        <v>0.9501615923499</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>3392.20068757613</v>
+        <v>3392.20269081218</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>3488.87822028535</v>
+        <v>3488.90194987812</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>3373.29118235577</v>
+        <v>3373.27783004273</v>
       </c>
       <c r="K84" s="11" t="n">
-        <v>3367.58744163117</v>
+        <v>3367.58889300578</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>3367.58744163117</v>
+        <v>3367.58889300578</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>3378.01271299979</v>
+        <v>3378.01401985931</v>
       </c>
       <c r="N84" s="14" t="n">
-        <v>3378.01271299979</v>
+        <v>3378.01401985931</v>
       </c>
       <c r="O84" s="15" t="n">
-        <v>0.0141314644660775</v>
+        <v>0.0141318948664604</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>-0.00336713777332842</v>
+        <v>-0.00336620231396878</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>0.0142317856146148</v>
+        <v>0.0142322221404576</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>0.995817471935459</v>
+        <v>0.995817269117998</v>
       </c>
       <c r="S84" s="19" t="n">
-        <v>0.968223165073243</v>
+        <v>0.968216954327797</v>
       </c>
     </row>
     <row r="85">
@@ -6538,46 +6538,46 @@
         <v>3684.19222817274</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1.07131548013766</v>
+        <v>1.07131451147546</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>3391.14395881609</v>
+        <v>3391.14491732455</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>3491.44262198322</v>
+        <v>3491.55202302774</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>3374.84828926341</v>
+        <v>3374.82377717008</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>3438.94239976756</v>
+        <v>3438.94550919385</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>3438.94239976756</v>
+        <v>3438.94550919385</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>3383.31211448152</v>
+        <v>3383.31241615884</v>
       </c>
       <c r="N85" s="14" t="n">
-        <v>3383.31211448152</v>
+        <v>3383.31241615884</v>
       </c>
       <c r="O85" s="15" t="n">
-        <v>0.0015675633702304</v>
+        <v>0.00156726566427836</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>0.0115515458856172</v>
+        <v>0.0115527259634418</v>
       </c>
       <c r="Q85" s="17" t="n">
-        <v>0.00156879263992571</v>
+        <v>0.00156849446697915</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>0.997690500778001</v>
+        <v>0.997690307740698</v>
       </c>
       <c r="S85" s="19" t="n">
-        <v>0.969029848343811</v>
+        <v>0.96899957206565</v>
       </c>
     </row>
     <row r="86">
@@ -6597,46 +6597,46 @@
         <v>3473.96328435329</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>1.05663009138043</v>
+        <v>1.05663216863889</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>3321.51565847708</v>
+        <v>3321.50849358518</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>3494.04179186037</v>
+        <v>3494.25528572027</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>3382.61262471013</v>
+        <v>3382.5738582922</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>3287.77621675978</v>
+        <v>3287.76975324186</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>3287.77621675978</v>
+        <v>3287.76975324186</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>3328.83268567763</v>
+        <v>3328.82807453996</v>
       </c>
       <c r="N86" s="14" t="n">
-        <v>3328.83268567763</v>
+        <v>3328.82807453996</v>
       </c>
       <c r="O86" s="15" t="n">
-        <v>-0.0162334475226069</v>
+        <v>-0.0162349219014396</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>0.00396412861687145</v>
+        <v>0.00396338682018271</v>
       </c>
       <c r="Q86" s="17" t="n">
-        <v>-0.0161023952152379</v>
+        <v>-0.0161038458519706</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>1.00220291817137</v>
+        <v>1.00220369177707</v>
       </c>
       <c r="S86" s="19" t="n">
-        <v>0.952716906086354</v>
+        <v>0.952657376850411</v>
       </c>
     </row>
     <row r="87">
@@ -6656,46 +6656,46 @@
         <v>3047.37400305265</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>0.92321281235242</v>
+        <v>0.92321522523317</v>
       </c>
       <c r="G87" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>3320.95742826627</v>
+        <v>3320.95694275611</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>3496.71422184024</v>
+        <v>3497.05194176882</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>3397.35743445148</v>
+        <v>3397.30113810897</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>3300.83590942342</v>
+        <v>3300.82728248226</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>3300.83590942342</v>
+        <v>3300.82728248226</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>3323.70436669813</v>
+        <v>3323.70464027785</v>
       </c>
       <c r="N87" s="14" t="n">
-        <v>3323.70436669813</v>
+        <v>3323.70464027785</v>
       </c>
       <c r="O87" s="15" t="n">
-        <v>-0.00154176367752043</v>
+        <v>-0.00154029615326543</v>
       </c>
       <c r="P87" s="16" t="n">
-        <v>-0.00207402958594316</v>
+        <v>-0.00207390400707774</v>
       </c>
       <c r="Q87" s="17" t="n">
-        <v>-0.00154057577047084</v>
+        <v>-0.001539110505973</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>1.00082715255802</v>
+        <v>1.00082738125459</v>
       </c>
       <c r="S87" s="19" t="n">
-        <v>0.95052216333222</v>
+        <v>0.950430447022962</v>
       </c>
     </row>
     <row r="88">
@@ -6715,46 +6715,46 @@
         <v>3228.33181776595</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>0.948012215121607</v>
+        <v>0.948005307899961</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>3341.63466417141</v>
+        <v>3341.65290941161</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>3499.36948786183</v>
+        <v>3499.85314152869</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>3419.38178220324</v>
+        <v>3419.304660795</v>
       </c>
       <c r="K88" s="11" t="n">
-        <v>3405.3694311859</v>
+        <v>3405.39424290504</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>3405.3694311859</v>
+        <v>3405.39424290504</v>
       </c>
       <c r="M88" s="13" t="n">
-        <v>3341.54089599534</v>
+        <v>3341.55393674192</v>
       </c>
       <c r="N88" s="14" t="n">
-        <v>3341.54089599534</v>
+        <v>3341.55393674192</v>
       </c>
       <c r="O88" s="15" t="n">
-        <v>0.0053521126895272</v>
+        <v>0.00535593298491406</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>-0.0107968264489038</v>
+        <v>-0.0107933486667121</v>
       </c>
       <c r="Q88" s="17" t="n">
-        <v>0.00536646083085013</v>
+        <v>0.00537030163503904</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>0.999971939429203</v>
+        <v>0.999970382121552</v>
       </c>
       <c r="S88" s="19" t="n">
-        <v>0.95489799164851</v>
+        <v>0.954769757934009</v>
       </c>
     </row>
     <row r="89">
@@ -6774,46 +6774,46 @@
         <v>3463.84324480454</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>1.06429519816294</v>
+        <v>1.06429154658028</v>
       </c>
       <c r="G89" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>3332.12828171643</v>
+        <v>3332.13201839874</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>3501.79474191888</v>
+        <v>3502.44739494312</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>3448.50212405607</v>
+        <v>3448.40110124676</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>3254.58881218615</v>
+        <v>3254.59997867536</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>3254.58881218615</v>
+        <v>3254.59997867536</v>
       </c>
       <c r="M89" s="13" t="n">
-        <v>3321.06499127012</v>
+        <v>3321.0660725907</v>
       </c>
       <c r="N89" s="14" t="n">
-        <v>3321.06499127012</v>
+        <v>3321.0660725907</v>
       </c>
       <c r="O89" s="15" t="n">
-        <v>-0.00614653471522205</v>
+        <v>-0.00615011172782469</v>
       </c>
       <c r="P89" s="16" t="n">
-        <v>-0.0183982798822965</v>
+        <v>-0.0183980478039348</v>
       </c>
       <c r="Q89" s="17" t="n">
-        <v>-0.00612768341388725</v>
+        <v>-0.00613123850133079</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>0.996679812566937</v>
+        <v>0.996679019394508</v>
       </c>
       <c r="S89" s="19" t="n">
-        <v>0.948389393448651</v>
+        <v>0.948212977412793</v>
       </c>
     </row>
     <row r="90">
@@ -6833,46 +6833,46 @@
         <v>3610.11150456841</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>1.07134097221362</v>
+        <v>1.07135458606683</v>
       </c>
       <c r="G90" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>3284.27914311729</v>
+        <v>3284.24060255633</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>3503.71838596969</v>
+        <v>3504.56417514374</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>3484.46485434552</v>
+        <v>3484.33758227129</v>
       </c>
       <c r="K90" s="11" t="n">
-        <v>3369.7129095223</v>
+        <v>3369.67009010704</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>3369.7129095223</v>
+        <v>3369.67009010704</v>
       </c>
       <c r="M90" s="13" t="n">
-        <v>3302.49037090869</v>
+        <v>3302.4644488522</v>
       </c>
       <c r="N90" s="14" t="n">
-        <v>3302.49037090869</v>
+        <v>3302.4644488522</v>
       </c>
       <c r="O90" s="15" t="n">
-        <v>-0.00560867027988221</v>
+        <v>-0.00561684515030083</v>
       </c>
       <c r="P90" s="16" t="n">
-        <v>-0.00791337902991551</v>
+        <v>-0.00791979191998471</v>
       </c>
       <c r="Q90" s="17" t="n">
-        <v>-0.00559297105303669</v>
+        <v>-0.00560110016841442</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>1.00554496953451</v>
+        <v>1.00554887674237</v>
       </c>
       <c r="S90" s="19" t="n">
-        <v>0.942567297683856</v>
+        <v>0.942332422466409</v>
       </c>
     </row>
     <row r="91">
@@ -6892,46 +6892,46 @@
         <v>2954.63346329572</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>0.918744493892063</v>
+        <v>0.918752840478085</v>
       </c>
       <c r="G91" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>3303.66563402869</v>
+        <v>3303.66221518779</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>3504.71431826651</v>
+        <v>3505.77805062699</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v>3526.04680084783</v>
+        <v>3525.89222106276</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>3215.94685240404</v>
+        <v>3215.91763651935</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>3215.94685240404</v>
+        <v>3215.91763651935</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>3305.90722932901</v>
+        <v>3305.90732485032</v>
       </c>
       <c r="N91" s="14" t="n">
-        <v>3305.90722932901</v>
+        <v>3305.90732485032</v>
       </c>
       <c r="O91" s="15" t="n">
-        <v>0.00103409598861745</v>
+        <v>0.00104197415869556</v>
       </c>
       <c r="P91" s="16" t="n">
-        <v>-0.00535460901620488</v>
+        <v>-0.00535466214772962</v>
       </c>
       <c r="Q91" s="17" t="n">
-        <v>0.00103463085022448</v>
+        <v>0.00104251720236537</v>
       </c>
       <c r="R91" s="18" t="n">
-        <v>1.000678517607</v>
+        <v>1.00067958208688</v>
       </c>
       <c r="S91" s="19" t="n">
-        <v>0.943274381052595</v>
+        <v>0.942988197515551</v>
       </c>
     </row>
     <row r="92">
@@ -6951,46 +6951,46 @@
         <v>3221.79961592558</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>0.941489952626731</v>
+        <v>0.941461991423614</v>
       </c>
       <c r="G92" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>3343.05359343945</v>
+        <v>3343.13084423546</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>3504.27268363877</v>
+        <v>3505.57928108614</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v>3571.45103161507</v>
+        <v>3571.26979735453</v>
       </c>
       <c r="K92" s="11" t="n">
-        <v>3422.02230298565</v>
+        <v>3422.12393625556</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>3422.02230298565</v>
+        <v>3422.12393625556</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>3370.50402944148</v>
+        <v>3370.55955537268</v>
       </c>
       <c r="N92" s="14" t="n">
-        <v>3370.50402944148</v>
+        <v>3370.55955537268</v>
       </c>
       <c r="O92" s="15" t="n">
-        <v>0.0193513591121152</v>
+        <v>0.0193678041558144</v>
       </c>
       <c r="P92" s="16" t="n">
-        <v>0.00866759807753636</v>
+        <v>0.00868027845123898</v>
       </c>
       <c r="Q92" s="17" t="n">
-        <v>0.0195398102945501</v>
+        <v>0.0195565768091461</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>1.0082111863405</v>
+        <v>1.00820449824287</v>
       </c>
       <c r="S92" s="19" t="n">
-        <v>0.961826984862836</v>
+        <v>0.961484332577515</v>
       </c>
     </row>
     <row r="93">
@@ -7010,46 +7010,46 @@
         <v>3638.1623004355</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1.06316074913482</v>
+        <v>1.06314582013072</v>
       </c>
       <c r="G93" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>3486.19264850826</v>
+        <v>3486.21379474576</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>3501.70314724977</v>
+        <v>3503.2769634557</v>
       </c>
       <c r="J93" s="10" t="n">
-        <v>3617.33011495714</v>
+        <v>3617.12521795723</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>3422.02465939057</v>
+        <v>3422.07271246024</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>3422.02465939057</v>
+        <v>3422.07271246024</v>
       </c>
       <c r="M93" s="13" t="n">
-        <v>3497.89738930834</v>
+        <v>3497.90693281288</v>
       </c>
       <c r="N93" s="14" t="n">
-        <v>3497.89738930834</v>
+        <v>3497.90693281288</v>
       </c>
       <c r="O93" s="15" t="n">
-        <v>0.037099745250106</v>
+        <v>0.037085999663186</v>
       </c>
       <c r="P93" s="16" t="n">
-        <v>0.0532456903141136</v>
+        <v>0.0532482210100178</v>
       </c>
       <c r="Q93" s="17" t="n">
-        <v>0.037796530950289</v>
+        <v>0.0377822659259084</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>1.00335745668131</v>
+        <v>1.00335410814011</v>
       </c>
       <c r="S93" s="19" t="n">
-        <v>0.998913169454576</v>
+        <v>0.998467140708874</v>
       </c>
     </row>
     <row r="94">
@@ -7069,46 +7069,46 @@
         <v>4037.4781476365</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>1.08373606504484</v>
+        <v>1.08378248387274</v>
       </c>
       <c r="G94" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>3715.50190366204</v>
+        <v>3715.3642805585</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>3496.26396777489</v>
+        <v>3498.12803507961</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v>3659.58947554077</v>
+        <v>3659.367660376</v>
       </c>
       <c r="K94" s="11" t="n">
-        <v>3725.51793546656</v>
+        <v>3725.35837007548</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>3725.51793546656</v>
+        <v>3725.35837007548</v>
       </c>
       <c r="M94" s="13" t="n">
-        <v>3710.30494399315</v>
+        <v>3710.20607816769</v>
       </c>
       <c r="N94" s="14" t="n">
-        <v>3710.30494399315</v>
+        <v>3710.20607816769</v>
       </c>
       <c r="O94" s="15" t="n">
-        <v>0.0589520263245713</v>
+        <v>0.058922651338363</v>
       </c>
       <c r="P94" s="16" t="n">
-        <v>0.123486983240541</v>
+        <v>0.123465864850477</v>
       </c>
       <c r="Q94" s="17" t="n">
-        <v>0.0607243526737105</v>
+        <v>0.0606931943681195</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>0.998601276542539</v>
+        <v>0.998611656354182</v>
       </c>
       <c r="S94" s="19" t="n">
-        <v>1.06121991308181</v>
+        <v>1.06062615231956</v>
       </c>
     </row>
     <row r="95">
@@ -7128,46 +7128,46 @@
         <v>3625.34060687029</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>0.913607640833843</v>
+        <v>0.913636279600601</v>
       </c>
       <c r="G95" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H95" s="8" t="n">
-        <v>3928.04346173475</v>
+        <v>3927.96523573611</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>3487.16360483459</v>
+        <v>3489.33868064497</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v>3693.15801075484</v>
+        <v>3692.9310395885</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>3968.1592456489</v>
+        <v>3968.03486005954</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>3968.1592456489</v>
+        <v>3968.03486005954</v>
       </c>
       <c r="M95" s="13" t="n">
-        <v>3895.96273630917</v>
+        <v>3895.92355115147</v>
       </c>
       <c r="N95" s="14" t="n">
-        <v>3895.96273630917</v>
+        <v>3895.92355115147</v>
       </c>
       <c r="O95" s="15" t="n">
-        <v>0.0488267527442698</v>
+        <v>0.0488433414407701</v>
       </c>
       <c r="P95" s="16" t="n">
-        <v>0.178485198176576</v>
+        <v>0.178473311053225</v>
       </c>
       <c r="Q95" s="17" t="n">
-        <v>0.0500384187064182</v>
+        <v>0.0500558376195379</v>
       </c>
       <c r="R95" s="18" t="n">
-        <v>0.991832899575044</v>
+        <v>0.99184267612831</v>
       </c>
       <c r="S95" s="19" t="n">
-        <v>1.11722969662445</v>
+        <v>1.11652204263283</v>
       </c>
     </row>
     <row r="96">
@@ -7187,46 +7187,46 @@
         <v>3659.99110295258</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>0.933191625302347</v>
+        <v>0.93313176520709</v>
       </c>
       <c r="G96" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>3929.54898721448</v>
+        <v>3929.85900583045</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>3473.75380177915</v>
+        <v>3476.25710379821</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>3713.2942602879</v>
+        <v>3713.07922412087</v>
       </c>
       <c r="K96" s="11" t="n">
-        <v>3922.01451847232</v>
+        <v>3922.26611441131</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>3922.01451847232</v>
+        <v>3922.26611441131</v>
       </c>
       <c r="M96" s="13" t="n">
-        <v>3929.41918411681</v>
+        <v>3929.6233189375</v>
       </c>
       <c r="N96" s="14" t="n">
-        <v>3929.41918411681</v>
+        <v>3929.6233189375</v>
       </c>
       <c r="O96" s="15" t="n">
-        <v>0.00855080352586276</v>
+        <v>0.00861281049551458</v>
       </c>
       <c r="P96" s="16" t="n">
-        <v>0.165825392817569</v>
+        <v>0.165866751315423</v>
       </c>
       <c r="Q96" s="17" t="n">
-        <v>0.00858746606989769</v>
+        <v>0.00865000746127853</v>
       </c>
       <c r="R96" s="18" t="n">
-        <v>0.999966967431099</v>
+        <v>0.999940026628793</v>
       </c>
       <c r="S96" s="19" t="n">
-        <v>1.13117377003065</v>
+        <v>1.1304179183536</v>
       </c>
     </row>
     <row r="97">
@@ -7246,46 +7246,46 @@
         <v>4183.39210452291</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>1.07115720707702</v>
+        <v>1.07103716362791</v>
       </c>
       <c r="G97" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H97" s="8" t="n">
-        <v>3977.80771611824</v>
+        <v>3977.8671107608</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>3455.68692423434</v>
+        <v>3458.53069329795</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>3716.63177000293</v>
+        <v>3716.45160160164</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>3905.4884538737</v>
+        <v>3905.92618686784</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>3905.4884538737</v>
+        <v>3905.92618686784</v>
       </c>
       <c r="M97" s="13" t="n">
-        <v>3966.8412223565</v>
+        <v>3966.89991737741</v>
       </c>
       <c r="N97" s="14" t="n">
-        <v>3966.8412223565</v>
+        <v>3966.89991737741</v>
       </c>
       <c r="O97" s="15" t="n">
-        <v>0.00947849145920487</v>
+        <v>0.00944133873185516</v>
       </c>
       <c r="P97" s="16" t="n">
-        <v>0.134064490994371</v>
+        <v>0.134078176913467</v>
       </c>
       <c r="Q97" s="17" t="n">
-        <v>0.00952355462378529</v>
+        <v>0.00948604876713399</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>0.997243080977165</v>
+        <v>0.997242946262905</v>
       </c>
       <c r="S97" s="19" t="n">
-        <v>1.14791684239029</v>
+        <v>1.14698994144091</v>
       </c>
     </row>
     <row r="98">
@@ -7305,46 +7305,46 @@
         <v>4473.66539441506</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>1.08206610608072</v>
+        <v>1.08229968835621</v>
       </c>
       <c r="G98" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>4033.46909336605</v>
+        <v>4033.07148730938</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>3432.8955007739</v>
+        <v>3436.08559353441</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>3700.84768705386</v>
+        <v>3700.73349411075</v>
       </c>
       <c r="K98" s="11" t="n">
-        <v>4134.37346320626</v>
+        <v>4133.48118136265</v>
       </c>
       <c r="L98" s="12" t="n">
-        <v>4134.37346320626</v>
+        <v>4133.48118136265</v>
       </c>
       <c r="M98" s="13" t="n">
-        <v>4003.44446545673</v>
+        <v>4003.1297207915</v>
       </c>
       <c r="N98" s="14" t="n">
-        <v>4003.44446545673</v>
+        <v>4003.1297207915</v>
       </c>
       <c r="O98" s="15" t="n">
-        <v>0.00918499081883901</v>
+        <v>0.00909157295808076</v>
       </c>
       <c r="P98" s="16" t="n">
-        <v>0.0790068541234508</v>
+        <v>0.0789507742838031</v>
       </c>
       <c r="Q98" s="17" t="n">
-        <v>0.0092273022912901</v>
+        <v>0.00913302683926531</v>
       </c>
       <c r="R98" s="18" t="n">
-        <v>0.992556127934958</v>
+        <v>0.992575939550762</v>
       </c>
       <c r="S98" s="19" t="n">
-        <v>1.16620050466267</v>
+        <v>1.16502619385387</v>
       </c>
     </row>
     <row r="99">
@@ -7364,46 +7364,46 @@
         <v>3517.77670169052</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>0.916196843400711</v>
+        <v>0.916175880509091</v>
       </c>
       <c r="G99" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H99" s="8" t="n">
-        <v>3869.41379405501</v>
+        <v>3869.24644741629</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>3405.59318592755</v>
+        <v>3409.12757108129</v>
       </c>
       <c r="J99" s="10" t="n">
-        <v>3664.56344201397</v>
+        <v>3664.5575966545</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>3839.5424815407</v>
+        <v>3839.63033357285</v>
       </c>
       <c r="L99" s="12" t="n">
-        <v>3839.5424815407</v>
+        <v>3839.63033357285</v>
       </c>
       <c r="M99" s="13" t="n">
-        <v>3859.88707201486</v>
+        <v>3859.82478310238</v>
       </c>
       <c r="N99" s="14" t="n">
-        <v>3859.88707201486</v>
+        <v>3859.82478310238</v>
       </c>
       <c r="O99" s="15" t="n">
-        <v>-0.0365171798420086</v>
+        <v>-0.0364546959110425</v>
       </c>
       <c r="P99" s="16" t="n">
-        <v>-0.00925975599255457</v>
+        <v>-0.0092657793653117</v>
       </c>
       <c r="Q99" s="17" t="n">
-        <v>-0.0358584700451171</v>
+        <v>-0.0357982248101579</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>0.997537941779505</v>
+        <v>0.997564987280611</v>
       </c>
       <c r="S99" s="19" t="n">
-        <v>1.13339640446913</v>
+        <v>1.13220309378981</v>
       </c>
     </row>
     <row r="100">
@@ -7423,46 +7423,46 @@
         <v>3357.72554729946</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>0.925990715977129</v>
+        <v>0.925871366269303</v>
       </c>
       <c r="G100" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>3667.02632696472</v>
+        <v>3667.74812196973</v>
       </c>
       <c r="I100" s="9" t="n">
-        <v>3374.43205795156</v>
+        <v>3378.29826475469</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>3608.56809433729</v>
+        <v>3608.72034267545</v>
       </c>
       <c r="K100" s="11" t="n">
-        <v>3626.08986177179</v>
+        <v>3626.55728390117</v>
       </c>
       <c r="L100" s="12" t="n">
-        <v>3626.08986177179</v>
+        <v>3626.55728390117</v>
       </c>
       <c r="M100" s="13" t="n">
-        <v>3696.00333357567</v>
+        <v>3696.46182735014</v>
       </c>
       <c r="N100" s="14" t="n">
-        <v>3696.00333357567</v>
+        <v>3696.46182735014</v>
       </c>
       <c r="O100" s="15" t="n">
-        <v>-0.0433858713735767</v>
+        <v>-0.0432456902069874</v>
       </c>
       <c r="P100" s="16" t="n">
-        <v>-0.0594021252516495</v>
+        <v>-0.0593343108647891</v>
       </c>
       <c r="Q100" s="17" t="n">
-        <v>-0.0424581692110606</v>
+        <v>-0.0423239304715108</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>1.00790204487976</v>
+        <v>1.00782870154262</v>
       </c>
       <c r="S100" s="19" t="n">
-        <v>1.09529641435997</v>
+        <v>1.09417864784611</v>
       </c>
     </row>
     <row r="101">
@@ -7482,46 +7482,46 @@
         <v>3992.99553442729</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>1.0814411417424</v>
+        <v>1.08120357717409</v>
       </c>
       <c r="G101" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H101" s="8" t="n">
-        <v>3660.56031198653</v>
+        <v>3660.601032298</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>3340.33541341196</v>
+        <v>3344.50837759728</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v>3534.52559867549</v>
+        <v>3534.89352930072</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>3692.2911292184</v>
+        <v>3693.10240802538</v>
       </c>
       <c r="L101" s="12" t="n">
-        <v>3692.2911292184</v>
+        <v>3693.10240802538</v>
       </c>
       <c r="M101" s="13" t="n">
-        <v>3672.39456514748</v>
+        <v>3672.47204911272</v>
       </c>
       <c r="N101" s="14" t="n">
-        <v>3672.39456514748</v>
+        <v>3672.47204911272</v>
       </c>
       <c r="O101" s="15" t="n">
-        <v>-0.00640813635263928</v>
+        <v>-0.00651108108493959</v>
       </c>
       <c r="P101" s="16" t="n">
-        <v>-0.074226983310944</v>
+        <v>-0.0742211486039567</v>
       </c>
       <c r="Q101" s="17" t="n">
-        <v>-0.00638764803422209</v>
+        <v>-0.00648992992702413</v>
       </c>
       <c r="R101" s="18" t="n">
-        <v>1.00323290757489</v>
+        <v>1.00324291467712</v>
       </c>
       <c r="S101" s="19" t="n">
-        <v>1.09940892474518</v>
+        <v>1.09806035281964</v>
       </c>
     </row>
     <row r="102">
@@ -7541,46 +7541,46 @@
         <v>3941.5912142825</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>1.07140303771761</v>
+        <v>1.07192168852609</v>
       </c>
       <c r="G102" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>3675.37819483866</v>
+        <v>3674.58176927484</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>3304.38383500214</v>
+        <v>3308.82377453867</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v>3444.1875185174</v>
+        <v>3444.83813836361</v>
       </c>
       <c r="K102" s="11" t="n">
-        <v>3678.90614038131</v>
+        <v>3677.12609649895</v>
       </c>
       <c r="L102" s="12" t="n">
-        <v>3678.90614038131</v>
+        <v>3677.12609649895</v>
       </c>
       <c r="M102" s="13" t="n">
-        <v>3677.23541815362</v>
+        <v>3676.62028115357</v>
       </c>
       <c r="N102" s="14" t="n">
-        <v>3677.23541815362</v>
+        <v>3676.62028115357</v>
       </c>
       <c r="O102" s="15" t="n">
-        <v>0.0013173054200461</v>
+        <v>0.00112891015515632</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>-0.0814820962593013</v>
+        <v>-0.0815635421310725</v>
       </c>
       <c r="Q102" s="17" t="n">
-        <v>0.00131817344794172</v>
+        <v>0.00112954761408091</v>
       </c>
       <c r="R102" s="18" t="n">
-        <v>1.00050531488639</v>
+        <v>1.00055476024395</v>
       </c>
       <c r="S102" s="19" t="n">
-        <v>1.11283543370537</v>
+        <v>1.11115626931996</v>
       </c>
     </row>
     <row r="103">
@@ -7600,46 +7600,46 @@
         <v>3374.51907473218</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>0.922292496280874</v>
+        <v>0.922219839345833</v>
       </c>
       <c r="G103" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H103" s="8" t="n">
-        <v>3688.02120756882</v>
+        <v>3687.85354894499</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>3267.87787773789</v>
+        <v>3272.52819177751</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>3340.0942450046</v>
+        <v>3341.10619609099</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>3658.83826263345</v>
+        <v>3659.12652359102</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>3658.83826263345</v>
+        <v>3659.12652359102</v>
       </c>
       <c r="M103" s="13" t="n">
-        <v>3687.40519683467</v>
+        <v>3687.40808021881</v>
       </c>
       <c r="N103" s="14" t="n">
-        <v>3687.40519683467</v>
+        <v>3687.40808021881</v>
       </c>
       <c r="O103" s="15" t="n">
-        <v>0.00276178721456926</v>
+        <v>0.00292986562593904</v>
       </c>
       <c r="P103" s="16" t="n">
-        <v>-0.0446857309455323</v>
+        <v>-0.0446695672918564</v>
       </c>
       <c r="Q103" s="17" t="n">
-        <v>0.00276560446221152</v>
+        <v>0.00293416187702022</v>
       </c>
       <c r="R103" s="18" t="n">
-        <v>0.999832969850366</v>
+        <v>0.999879206503115</v>
       </c>
       <c r="S103" s="19" t="n">
-        <v>1.1283791300632</v>
+        <v>1.12677656665685</v>
       </c>
     </row>
     <row r="104">
@@ -7659,46 +7659,46 @@
         <v>3469.76766476378</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>0.924522360886898</v>
+        <v>0.924223141327113</v>
       </c>
       <c r="G104" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>3756.22943295129</v>
+        <v>3757.69336524073</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>3232.35217307587</v>
+        <v>3237.13555446365</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v>3225.95976238795</v>
+        <v>3227.41116850045</v>
       </c>
       <c r="K104" s="11" t="n">
-        <v>3753.03812169045</v>
+        <v>3754.25317719427</v>
       </c>
       <c r="L104" s="12" t="n">
-        <v>3753.03812169045</v>
+        <v>3754.25317719427</v>
       </c>
       <c r="M104" s="13" t="n">
-        <v>3712.48173313584</v>
+        <v>3713.5134242329</v>
       </c>
       <c r="N104" s="14" t="n">
-        <v>3712.48173313584</v>
+        <v>3713.5134242329</v>
       </c>
       <c r="O104" s="15" t="n">
-        <v>0.00677757174678684</v>
+        <v>0.00705464914497969</v>
       </c>
       <c r="P104" s="16" t="n">
-        <v>0.00445843741819107</v>
+        <v>0.00461295089174008</v>
       </c>
       <c r="Q104" s="17" t="n">
-        <v>0.00680059146271761</v>
+        <v>0.00707959180165818</v>
       </c>
       <c r="R104" s="18" t="n">
-        <v>0.988353294015622</v>
+        <v>0.988242803040689</v>
       </c>
       <c r="S104" s="19" t="n">
-        <v>1.1485387526951</v>
+        <v>1.14716030940143</v>
       </c>
     </row>
     <row r="105">
@@ -7718,46 +7718,46 @@
         <v>4016.542850834</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1.08996724730648</v>
+        <v>1.08955082669477</v>
       </c>
       <c r="G105" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H105" s="8" t="n">
-        <v>3640.50779842188</v>
+        <v>3640.96250904559</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>3199.58570271327</v>
+        <v>3204.40141170435</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>3107.09177500649</v>
+        <v>3109.05662324705</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>3685.01242652901</v>
+        <v>3686.42081895203</v>
       </c>
       <c r="L105" s="12" t="n">
-        <v>3685.01242652901</v>
+        <v>3686.42081895203</v>
       </c>
       <c r="M105" s="13" t="n">
-        <v>3560.71011407669</v>
+        <v>3561.52795782527</v>
       </c>
       <c r="N105" s="14" t="n">
-        <v>3560.71011407669</v>
+        <v>3561.52795782527</v>
       </c>
       <c r="O105" s="15" t="n">
-        <v>-0.0417405885306054</v>
+        <v>-0.0417887886823625</v>
       </c>
       <c r="P105" s="16" t="n">
-        <v>-0.0304118876905852</v>
+        <v>-0.0302096489241503</v>
       </c>
       <c r="Q105" s="17" t="n">
-        <v>-0.0408814453427487</v>
+        <v>-0.0409276738885158</v>
       </c>
       <c r="R105" s="18" t="n">
-        <v>0.978080617110674</v>
+        <v>0.978183090041994</v>
       </c>
       <c r="S105" s="19" t="n">
-        <v>1.11286599107415</v>
+        <v>1.11144875445894</v>
       </c>
     </row>
     <row r="106">
@@ -7777,46 +7777,46 @@
         <v>3685.04709961106</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>1.05317687315511</v>
+        <v>1.05417424529402</v>
       </c>
       <c r="G106" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>3119.77748155831</v>
+        <v>3119.01701620274</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>3171.6828770652</v>
+        <v>3176.40451112108</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>2991.43337899573</v>
+        <v>2993.98033802933</v>
       </c>
       <c r="K106" s="11" t="n">
-        <v>3498.98216865643</v>
+        <v>3495.67172226188</v>
       </c>
       <c r="L106" s="12" t="n">
-        <v>3119.77748155831</v>
+        <v>3119.01701620274</v>
       </c>
       <c r="M106" s="13" t="n">
-        <v>3084.23756175549</v>
+        <v>3084.19139300264</v>
       </c>
       <c r="N106" s="14" t="n">
-        <v>3084.23756175549</v>
+        <v>3084.19139300264</v>
       </c>
       <c r="O106" s="15" t="n">
-        <v>-0.14365551208365</v>
+        <v>-0.143900140656246</v>
       </c>
       <c r="P106" s="16" t="n">
-        <v>-0.161261869030914</v>
+        <v>-0.161134096764828</v>
       </c>
       <c r="Q106" s="17" t="n">
-        <v>-0.13381391269049</v>
+        <v>-0.134025780641097</v>
       </c>
       <c r="R106" s="18" t="n">
-        <v>0.988608187598986</v>
+        <v>0.988834423467655</v>
       </c>
       <c r="S106" s="19" t="n">
-        <v>0.972429363622057</v>
+        <v>0.970969340398686</v>
       </c>
     </row>
     <row r="107">
@@ -7836,46 +7836,46 @@
         <v>1880.07334156122</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>0.931427821975475</v>
+        <v>0.931357242143957</v>
       </c>
       <c r="G107" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="8" t="n">
-        <v>2412.38285737633</v>
+        <v>2412.31072065306</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>3151.05149824913</v>
+        <v>3155.52486246481</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>2889.81727374883</v>
+        <v>2893.00691152436</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>2018.48527304429</v>
+        <v>2018.63823728191</v>
       </c>
       <c r="L107" s="12" t="n">
-        <v>2412.38285737633</v>
+        <v>2412.31072065306</v>
       </c>
       <c r="M107" s="13" t="n">
-        <v>2470.41820315091</v>
+        <v>2470.518103819</v>
       </c>
       <c r="N107" s="14" t="n">
-        <v>2470.41820315091</v>
+        <v>2470.518103819</v>
       </c>
       <c r="O107" s="15" t="n">
-        <v>-0.22191703381039</v>
+        <v>-0.221861626488533</v>
       </c>
       <c r="P107" s="16" t="n">
-        <v>-0.330038856247326</v>
+        <v>-0.330012287744295</v>
       </c>
       <c r="Q107" s="17" t="n">
-        <v>-0.19901818401278</v>
+        <v>-0.198973802525981</v>
       </c>
       <c r="R107" s="18" t="n">
-        <v>1.02405727001298</v>
+        <v>1.02412930584257</v>
       </c>
       <c r="S107" s="19" t="n">
-        <v>0.783998041454919</v>
+        <v>0.782918281901685</v>
       </c>
     </row>
     <row r="108">
@@ -7895,46 +7895,46 @@
         <v>1803.44547006555</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>0.930988538349357</v>
+        <v>0.930362090923597</v>
       </c>
       <c r="G108" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>1984.06454996</v>
+        <v>1985.14039905338</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>3140.06692751034</v>
+        <v>3144.10660830222</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>2813.71787917174</v>
+        <v>2817.58612580007</v>
       </c>
       <c r="K108" s="11" t="n">
-        <v>1937.12961629266</v>
+        <v>1938.43395776715</v>
       </c>
       <c r="L108" s="12" t="n">
-        <v>1937.12961629266</v>
+        <v>1938.43395776715</v>
       </c>
       <c r="M108" s="13" t="n">
-        <v>2058.41281489844</v>
+        <v>2059.38362983858</v>
       </c>
       <c r="N108" s="14" t="n">
-        <v>2058.41281489844</v>
+        <v>2059.38362983858</v>
       </c>
       <c r="O108" s="15" t="n">
-        <v>-0.182452241698647</v>
+        <v>-0.18202115806142</v>
       </c>
       <c r="P108" s="16" t="n">
-        <v>-0.445542641590386</v>
+        <v>-0.445435253741143</v>
       </c>
       <c r="Q108" s="17" t="n">
-        <v>-0.16677556363816</v>
+        <v>-0.16641629678604</v>
       </c>
       <c r="R108" s="18" t="n">
-        <v>1.03747270467583</v>
+        <v>1.03739948611222</v>
       </c>
       <c r="S108" s="19" t="n">
-        <v>0.655531510129465</v>
+        <v>0.654998028502162</v>
       </c>
     </row>
     <row r="109">
@@ -7954,46 +7954,46 @@
         <v>2123.17169555586</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>1.09047852915712</v>
+        <v>1.08972478482975</v>
       </c>
       <c r="G109" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H109" s="8" t="n">
-        <v>1878.20899198226</v>
+        <v>1881.10674569218</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>3140.6428581936</v>
+        <v>3144.02938236133</v>
       </c>
       <c r="J109" s="10" t="n">
-        <v>2772.22244308857</v>
+        <v>2776.76428197004</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>1947.00916963212</v>
+        <v>1948.35588316693</v>
       </c>
       <c r="L109" s="12" t="n">
-        <v>1947.00916963212</v>
+        <v>1948.35588316693</v>
       </c>
       <c r="M109" s="13" t="n">
-        <v>1943.80916875773</v>
+        <v>1946.21401693398</v>
       </c>
       <c r="N109" s="14" t="n">
-        <v>1943.80916875773</v>
+        <v>1946.21401693398</v>
       </c>
       <c r="O109" s="15" t="n">
-        <v>-0.0572856706254207</v>
+        <v>-0.0565207736272218</v>
       </c>
       <c r="P109" s="16" t="n">
-        <v>-0.454095080339961</v>
+        <v>-0.453545208691169</v>
       </c>
       <c r="Q109" s="17" t="n">
-        <v>-0.0556757348726336</v>
+        <v>-0.0549531477597847</v>
       </c>
       <c r="R109" s="18" t="n">
-        <v>1.03492698472614</v>
+        <v>1.03461115186094</v>
       </c>
       <c r="S109" s="19" t="n">
-        <v>0.61892079313843</v>
+        <v>0.619019029482564</v>
       </c>
     </row>
     <row r="110">
@@ -8013,46 +8013,46 @@
         <v>1981.82749195669</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>1.03806509557455</v>
+        <v>1.03943534361272</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>0.720625149554306</v>
+        <v>0.667347090440055</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>2034.19665714709</v>
+        <v>2036.11824257747</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>3153.94114782407</v>
+        <v>3156.41927296357</v>
       </c>
       <c r="J110" s="10" t="n">
-        <v>2770.035272009</v>
+        <v>2775.19192030767</v>
       </c>
       <c r="K110" s="11" t="n">
-        <v>1909.15531251899</v>
+        <v>1906.63854575941</v>
       </c>
       <c r="L110" s="12" t="n">
-        <v>1944.088719474</v>
+        <v>1949.71034363488</v>
       </c>
       <c r="M110" s="13" t="n">
-        <v>2058.04802646193</v>
+        <v>2060.44947007172</v>
       </c>
       <c r="N110" s="14" t="n">
-        <v>2058.04802646193</v>
+        <v>2060.44947007172</v>
       </c>
       <c r="O110" s="15" t="n">
-        <v>0.0571084366122597</v>
+        <v>0.0570381927707018</v>
       </c>
       <c r="P110" s="16" t="n">
-        <v>-0.332720652915423</v>
+        <v>-0.331932034196572</v>
       </c>
       <c r="Q110" s="17" t="n">
-        <v>0.058770613669455</v>
+        <v>0.0586962441662526</v>
       </c>
       <c r="R110" s="18" t="n">
-        <v>1.01172520327916</v>
+        <v>1.01194981066691</v>
       </c>
       <c r="S110" s="19" t="n">
-        <v>0.652532158972527</v>
+        <v>0.652780664381496</v>
       </c>
     </row>
     <row r="111">
@@ -8072,46 +8072,46 @@
         <v>2244.76524089118</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>0.93648731446383</v>
+        <v>0.937654661491575</v>
       </c>
       <c r="G111" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H111" s="8" t="n">
-        <v>2321.36061612805</v>
+        <v>2323.25847300991</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>3180.37763287167</v>
+        <v>3181.65507249338</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>2807.73460607546</v>
+        <v>2813.37753909236</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>2397.00549726761</v>
+        <v>2394.02130985017</v>
       </c>
       <c r="L111" s="12" t="n">
-        <v>2397.00549726761</v>
+        <v>2394.02130985017</v>
       </c>
       <c r="M111" s="13" t="n">
-        <v>2324.07358869903</v>
+        <v>2325.79494405394</v>
       </c>
       <c r="N111" s="14" t="n">
-        <v>2324.07358869903</v>
+        <v>2325.79494405394</v>
       </c>
       <c r="O111" s="15" t="n">
-        <v>0.121563529548102</v>
+        <v>0.121137743665123</v>
       </c>
       <c r="P111" s="16" t="n">
-        <v>-0.0592388018616526</v>
+        <v>-0.0585800846961405</v>
       </c>
       <c r="Q111" s="17" t="n">
-        <v>0.129261105094051</v>
+        <v>0.128780384006693</v>
       </c>
       <c r="R111" s="18" t="n">
-        <v>1.0011686993189</v>
+        <v>1.00109177307368</v>
       </c>
       <c r="S111" s="19" t="n">
-        <v>0.730753972320119</v>
+        <v>0.731001598558347</v>
       </c>
     </row>
     <row r="112">
@@ -8131,46 +8131,46 @@
         <v>2416.28398981369</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>0.944527031403065</v>
+        <v>0.941864323582329</v>
       </c>
       <c r="G112" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>2565.24571542475</v>
+        <v>2568.54222444784</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>3219.61199203855</v>
+        <v>3219.36138025441</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>2881.7689526677</v>
+        <v>2887.70222872016</v>
       </c>
       <c r="K112" s="11" t="n">
-        <v>2558.19464078691</v>
+        <v>2565.42681288053</v>
       </c>
       <c r="L112" s="12" t="n">
-        <v>2558.19464078691</v>
+        <v>2565.42681288053</v>
       </c>
       <c r="M112" s="13" t="n">
-        <v>2557.36574005181</v>
+        <v>2560.40028078374</v>
       </c>
       <c r="N112" s="14" t="n">
-        <v>2557.36574005181</v>
+        <v>2560.40028078374</v>
       </c>
       <c r="O112" s="15" t="n">
-        <v>0.0956562177463085</v>
+        <v>0.0961017139277385</v>
       </c>
       <c r="P112" s="16" t="n">
-        <v>0.242396919384696</v>
+        <v>0.243284759423105</v>
       </c>
       <c r="Q112" s="17" t="n">
-        <v>0.100380707602021</v>
+        <v>0.100871032216139</v>
       </c>
       <c r="R112" s="18" t="n">
-        <v>0.996928179111435</v>
+        <v>0.996830130497132</v>
       </c>
       <c r="S112" s="19" t="n">
-        <v>0.794308676441649</v>
+        <v>0.79531310044522</v>
       </c>
     </row>
     <row r="113">
@@ -8190,46 +8190,46 @@
         <v>2945.85895499108</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>1.08460419926194</v>
+        <v>1.08434150210634</v>
       </c>
       <c r="G113" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H113" s="8" t="n">
-        <v>2730.61315499454</v>
+        <v>2732.73459126095</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>3270.81429644214</v>
+        <v>3268.67052444861</v>
       </c>
       <c r="J113" s="10" t="n">
-        <v>2986.53317362143</v>
+        <v>2992.45029844088</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>2716.0681813658</v>
+        <v>2716.7261875237</v>
       </c>
       <c r="L113" s="12" t="n">
-        <v>2716.0681813658</v>
+        <v>2716.7261875237</v>
       </c>
       <c r="M113" s="13" t="n">
-        <v>2762.97470470067</v>
+        <v>2763.98357580784</v>
       </c>
       <c r="N113" s="14" t="n">
-        <v>2762.97470470067</v>
+        <v>2763.98357580784</v>
       </c>
       <c r="O113" s="15" t="n">
-        <v>0.0773301699797288</v>
+        <v>0.076509357755649</v>
       </c>
       <c r="P113" s="16" t="n">
-        <v>0.421422817172154</v>
+        <v>0.420184805863314</v>
       </c>
       <c r="Q113" s="17" t="n">
-        <v>0.0803987327384383</v>
+        <v>0.0795122921021501</v>
       </c>
       <c r="R113" s="18" t="n">
-        <v>1.01185138570322</v>
+        <v>1.01143506019458</v>
       </c>
       <c r="S113" s="19" t="n">
-        <v>0.844736036437813</v>
+        <v>0.845598709057436</v>
       </c>
     </row>
     <row r="114">
@@ -8249,46 +8249,46 @@
         <v>3141.23369626134</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>1.02602126942263</v>
+        <v>1.02753584014123</v>
       </c>
       <c r="G114" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>3090.38711251879</v>
+        <v>3083.33816008347</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>3332.7412313553</v>
+        <v>3328.30612417336</v>
       </c>
       <c r="J114" s="10" t="n">
-        <v>3114.80425921293</v>
+        <v>3120.29468042513</v>
       </c>
       <c r="K114" s="11" t="n">
-        <v>3061.56781528417</v>
+        <v>3057.05511530341</v>
       </c>
       <c r="L114" s="12" t="n">
-        <v>3061.56781528417</v>
+        <v>3057.05511530341</v>
       </c>
       <c r="M114" s="13" t="n">
-        <v>3106.68759057215</v>
+        <v>3102.09162076786</v>
       </c>
       <c r="N114" s="14" t="n">
-        <v>3106.68759057215</v>
+        <v>3102.09162076786</v>
       </c>
       <c r="O114" s="15" t="n">
-        <v>0.117249184282471</v>
+        <v>0.115403636643705</v>
       </c>
       <c r="P114" s="16" t="n">
-        <v>0.509531143407267</v>
+        <v>0.505541225750075</v>
       </c>
       <c r="Q114" s="17" t="n">
-        <v>0.1243995774868</v>
+        <v>0.122326358202474</v>
       </c>
       <c r="R114" s="18" t="n">
-        <v>1.00527457482182</v>
+        <v>1.00608219394394</v>
       </c>
       <c r="S114" s="19" t="n">
-        <v>0.932171859412192</v>
+        <v>0.932033143897879</v>
       </c>
     </row>
     <row r="115">
@@ -8308,46 +8308,46 @@
         <v>3374.61116034377</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>0.940645957614225</v>
+        <v>0.943279608860394</v>
       </c>
       <c r="G115" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>3565.99370852769</v>
+        <v>3563.77099972505</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>3403.80276572898</v>
+        <v>3396.64683331542</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>3258.00687475723</v>
+        <v>3262.52968628896</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>3587.54655035445</v>
+        <v>3577.53006494092</v>
       </c>
       <c r="L115" s="12" t="n">
-        <v>3587.54655035445</v>
+        <v>3577.53006494092</v>
       </c>
       <c r="M115" s="13" t="n">
-        <v>3532.75673224913</v>
+        <v>3530.85817797741</v>
       </c>
       <c r="N115" s="14" t="n">
-        <v>3532.75673224913</v>
+        <v>3530.85817797741</v>
       </c>
       <c r="O115" s="15" t="n">
-        <v>0.128521434977626</v>
+        <v>0.129464350958326</v>
       </c>
       <c r="P115" s="16" t="n">
-        <v>0.520070943290007</v>
+        <v>0.518129612846699</v>
       </c>
       <c r="Q115" s="17" t="n">
-        <v>0.137145795724671</v>
+        <v>0.138218534339556</v>
       </c>
       <c r="R115" s="18" t="n">
-        <v>0.9906794630066</v>
+        <v>0.990764608121516</v>
       </c>
       <c r="S115" s="19" t="n">
-        <v>1.03788526404013</v>
+        <v>1.03951289352358</v>
       </c>
     </row>
     <row r="116">
@@ -8367,46 +8367,46 @@
         <v>3733.26985008941</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>0.958633533063888</v>
+        <v>0.954478863413738</v>
       </c>
       <c r="G116" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>3841.87664714042</v>
+        <v>3850.24228817767</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>3482.23938512908</v>
+        <v>3471.90177388102</v>
       </c>
       <c r="J116" s="10" t="n">
-        <v>3407.29950334971</v>
+        <v>3410.1334298228</v>
       </c>
       <c r="K116" s="11" t="n">
-        <v>3894.36601300344</v>
+        <v>3911.31746672441</v>
       </c>
       <c r="L116" s="12" t="n">
-        <v>3894.36601300344</v>
+        <v>3911.31746672441</v>
       </c>
       <c r="M116" s="13" t="n">
-        <v>3813.04889629596</v>
+        <v>3819.7835284251</v>
       </c>
       <c r="N116" s="14" t="n">
-        <v>3813.04889629596</v>
+        <v>3819.7835284251</v>
       </c>
       <c r="O116" s="15" t="n">
-        <v>0.076350594222336</v>
+        <v>0.0786528017538535</v>
       </c>
       <c r="P116" s="16" t="n">
-        <v>0.491006482404316</v>
+        <v>0.491869672524746</v>
       </c>
       <c r="Q116" s="17" t="n">
-        <v>0.0793409185206988</v>
+        <v>0.0818286478482091</v>
       </c>
       <c r="R116" s="18" t="n">
-        <v>0.992496440283703</v>
+        <v>0.99208913167722</v>
       </c>
       <c r="S116" s="19" t="n">
-        <v>1.09499907231524</v>
+        <v>1.10019919260423</v>
       </c>
     </row>
     <row r="117">
@@ -8426,46 +8426,46 @@
         <v>4166.74891556592</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1.07503563829706</v>
+        <v>1.07418976323358</v>
       </c>
       <c r="G117" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H117" s="8" t="n">
-        <v>3959.12717663405</v>
+        <v>3965.66517602769</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>3566.40641498691</v>
+        <v>3552.39311989618</v>
       </c>
       <c r="J117" s="10" t="n">
-        <v>3555.48832646374</v>
+        <v>3555.65902671033</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>3875.9170088225</v>
+        <v>3878.96911531066</v>
       </c>
       <c r="L117" s="12" t="n">
-        <v>3875.9170088225</v>
+        <v>3878.96911531066</v>
       </c>
       <c r="M117" s="13" t="n">
-        <v>3946.78638680834</v>
+        <v>3950.51956691797</v>
       </c>
       <c r="N117" s="14" t="n">
-        <v>3946.78638680834</v>
+        <v>3950.51956691797</v>
       </c>
       <c r="O117" s="15" t="n">
-        <v>0.0344725704536452</v>
+        <v>0.0336533531302897</v>
       </c>
       <c r="P117" s="16" t="n">
-        <v>0.428455490415328</v>
+        <v>0.429284747382531</v>
       </c>
       <c r="Q117" s="17" t="n">
-        <v>0.0350736363864366</v>
+        <v>0.0342260333655027</v>
       </c>
       <c r="R117" s="18" t="n">
-        <v>0.996882951904516</v>
+        <v>0.996180814961063</v>
       </c>
       <c r="S117" s="19" t="n">
-        <v>1.10665637270699</v>
+        <v>1.11207274464979</v>
       </c>
     </row>
     <row r="118">
@@ -8485,46 +8485,46 @@
         <v>4233.78150541524</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>1.02241903170628</v>
+        <v>1.02442856749137</v>
       </c>
       <c r="G118" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>4092.75845167939</v>
+        <v>4079.73788972205</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>3654.91675987618</v>
+        <v>3636.71768019492</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>3697.81485812095</v>
+        <v>3694.16551281975</v>
       </c>
       <c r="K118" s="11" t="n">
-        <v>4140.94551658494</v>
+        <v>4132.82257032617</v>
       </c>
       <c r="L118" s="12" t="n">
-        <v>4140.94551658494</v>
+        <v>4132.82257032617</v>
       </c>
       <c r="M118" s="13" t="n">
-        <v>4080.69057981046</v>
+        <v>4072.27796701784</v>
       </c>
       <c r="N118" s="14" t="n">
-        <v>4080.69057981046</v>
+        <v>4072.27796701784</v>
       </c>
       <c r="O118" s="15" t="n">
-        <v>0.0333645590276947</v>
+        <v>0.0303554337469663</v>
       </c>
       <c r="P118" s="16" t="n">
-        <v>0.313518163910049</v>
+        <v>0.312752318388915</v>
       </c>
       <c r="Q118" s="17" t="n">
-        <v>0.0339273981104422</v>
+        <v>0.0308208573675937</v>
       </c>
       <c r="R118" s="18" t="n">
-        <v>0.997051408723138</v>
+        <v>0.998171470102772</v>
       </c>
       <c r="S118" s="19" t="n">
-        <v>1.11649343826608</v>
+        <v>1.11976741807452</v>
       </c>
     </row>
     <row r="119">
@@ -8544,46 +8544,46 @@
         <v>3910.97166063794</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>0.939019110486066</v>
+        <v>0.943653978521264</v>
       </c>
       <c r="G119" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H119" s="8" t="n">
-        <v>4155.12424904742</v>
+        <v>4149.46179489071</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>3746.57676849177</v>
+        <v>3723.6763736084</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>3831.12275575476</v>
+        <v>3822.32847446226</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>4164.95427724947</v>
+        <v>4144.49761210837</v>
       </c>
       <c r="L119" s="12" t="n">
-        <v>4164.95427724947</v>
+        <v>4144.49761210837</v>
       </c>
       <c r="M119" s="13" t="n">
-        <v>4137.64050860738</v>
+        <v>4132.59865213177</v>
       </c>
       <c r="N119" s="14" t="n">
-        <v>4137.64050860738</v>
+        <v>4132.59865213177</v>
       </c>
       <c r="O119" s="15" t="n">
-        <v>0.0138594660601021</v>
+        <v>0.0147038827537903</v>
       </c>
       <c r="P119" s="16" t="n">
-        <v>0.171221463067783</v>
+        <v>0.17042329196554</v>
       </c>
       <c r="Q119" s="17" t="n">
-        <v>0.0139559537002591</v>
+        <v>0.0148125166313504</v>
       </c>
       <c r="R119" s="18" t="n">
-        <v>0.995792246057613</v>
+        <v>0.995936065062775</v>
       </c>
       <c r="S119" s="19" t="n">
-        <v>1.10437894757807</v>
+        <v>1.10981681475372</v>
       </c>
     </row>
     <row r="120">
@@ -8603,46 +8603,46 @@
         <v>3961.64730583922</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>0.971061492987454</v>
+        <v>0.964238344614886</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>4120.99417861366</v>
+        <v>4132.77669493217</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>3840.49655750146</v>
+        <v>3812.38018452413</v>
       </c>
       <c r="J120" s="10" t="n">
-        <v>3954.47133009092</v>
+        <v>3939.01678323659</v>
       </c>
       <c r="K120" s="11" t="n">
-        <v>4079.70796334564</v>
+        <v>4108.57681398419</v>
       </c>
       <c r="L120" s="12" t="n">
-        <v>4079.70796334564</v>
+        <v>4108.57681398419</v>
       </c>
       <c r="M120" s="13" t="n">
-        <v>4118.80426838103</v>
+        <v>4128.42163691375</v>
       </c>
       <c r="N120" s="14" t="n">
-        <v>4118.80426838103</v>
+        <v>4128.42163691375</v>
       </c>
       <c r="O120" s="15" t="n">
-        <v>-0.00456280479424822</v>
+        <v>-0.0010112590038134</v>
       </c>
       <c r="P120" s="16" t="n">
-        <v>0.08018658569579</v>
+        <v>0.0807998951228273</v>
       </c>
       <c r="Q120" s="17" t="n">
-        <v>-0.00455241101472437</v>
+        <v>-0.00101074785374322</v>
       </c>
       <c r="R120" s="18" t="n">
-        <v>0.99946859662069</v>
+        <v>0.998946215017191</v>
       </c>
       <c r="S120" s="19" t="n">
-        <v>1.0724665955854</v>
+        <v>1.0828987239186</v>
       </c>
     </row>
     <row r="121">
@@ -8662,46 +8662,46 @@
         <v>4425.94559335052</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>1.06627532462906</v>
+        <v>1.06597012440437</v>
       </c>
       <c r="G121" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>4109.11881698196</v>
+        <v>4118.86179972859</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>3936.04772951606</v>
+        <v>3902.20311060365</v>
       </c>
       <c r="J121" s="10" t="n">
-        <v>4068.58904946265</v>
+        <v>4044.71015642969</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>4150.84686958336</v>
+        <v>4152.03530757824</v>
       </c>
       <c r="L121" s="12" t="n">
-        <v>4150.84686958336</v>
+        <v>4152.03530757824</v>
       </c>
       <c r="M121" s="13" t="n">
-        <v>4115.78351535986</v>
+        <v>4121.22908066251</v>
       </c>
       <c r="N121" s="14" t="n">
-        <v>4115.78351535986</v>
+        <v>4121.22908066251</v>
       </c>
       <c r="O121" s="15" t="n">
-        <v>-0.000733674407512188</v>
+        <v>-0.00174372426662301</v>
       </c>
       <c r="P121" s="16" t="n">
-        <v>0.0428189194926705</v>
+        <v>0.0432119144970378</v>
       </c>
       <c r="Q121" s="17" t="n">
-        <v>-0.000733405334252146</v>
+        <v>-0.0017422048627328</v>
       </c>
       <c r="R121" s="18" t="n">
-        <v>1.001621928855</v>
+        <v>1.00057474153031</v>
       </c>
       <c r="S121" s="19" t="n">
-        <v>1.04566402599643</v>
+        <v>1.05612879797663</v>
       </c>
     </row>
     <row r="122">
@@ -8721,46 +8721,46 @@
         <v>4179.49876291989</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>1.0239521838758</v>
+        <v>1.02633172617394</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>4087.46880839296</v>
+        <v>4086.48423115742</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>4032.751394275</v>
+        <v>3992.70427240193</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>4174.83056536945</v>
+        <v>4140.73611148227</v>
       </c>
       <c r="K122" s="11" t="n">
-        <v>4081.73235892706</v>
+        <v>4072.26889350935</v>
       </c>
       <c r="L122" s="12" t="n">
-        <v>4081.73235892706</v>
+        <v>4072.26889350935</v>
       </c>
       <c r="M122" s="13" t="n">
-        <v>4114.58342930184</v>
+        <v>4103.75951252214</v>
       </c>
       <c r="N122" s="14" t="n">
-        <v>4114.58342930184</v>
+        <v>4103.75951252214</v>
       </c>
       <c r="O122" s="15" t="n">
-        <v>-0.000291623951785912</v>
+        <v>-0.00424793158365897</v>
       </c>
       <c r="P122" s="16" t="n">
-        <v>0.00830566513890107</v>
+        <v>0.00773069661729209</v>
       </c>
       <c r="Q122" s="17" t="n">
-        <v>-0.000291581433654486</v>
+        <v>-0.00423892188433284</v>
       </c>
       <c r="R122" s="18" t="n">
-        <v>1.00663359702053</v>
+        <v>1.00422741906918</v>
       </c>
       <c r="S122" s="19" t="n">
-        <v>1.02029186206296</v>
+        <v>1.02781454186022</v>
       </c>
     </row>
     <row r="123">
@@ -8780,46 +8780,46 @@
         <v>3874.20337444698</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>0.93488964419747</v>
+        <v>0.940691110963825</v>
       </c>
       <c r="G123" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>4219.75447451043</v>
+        <v>4148.17122213313</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>4130.26291098025</v>
+        <v>4083.59893559706</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>4274.96181841141</v>
+        <v>4228.95879159077</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>4144.02212976986</v>
+        <v>4118.46495549161</v>
       </c>
       <c r="L123" s="12" t="n">
-        <v>4144.02212976986</v>
+        <v>4118.46495549161</v>
       </c>
       <c r="M123" s="13" t="n">
-        <v>4225.25638013283</v>
+        <v>4153.6105842369</v>
       </c>
       <c r="N123" s="14" t="n">
-        <v>4225.25638013283</v>
+        <v>4153.6105842369</v>
       </c>
       <c r="O123" s="15" t="n">
-        <v>0.0265423438990462</v>
+        <v>0.0120744684541691</v>
       </c>
       <c r="P123" s="16" t="n">
-        <v>0.0211753223469238</v>
+        <v>0.00508443569623984</v>
       </c>
       <c r="Q123" s="17" t="n">
-        <v>0.0268977291948542</v>
+        <v>0.0121476591312557</v>
       </c>
       <c r="R123" s="18" t="n">
-        <v>1.00130384496435</v>
+        <v>1.00131126749898</v>
       </c>
       <c r="S123" s="19" t="n">
-        <v>1.02299937587509</v>
+        <v>1.01714459469307</v>
       </c>
     </row>
     <row r="124">
@@ -8839,46 +8839,46 @@
         <v>4430.14508587482</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>0.977687428262069</v>
+        <v>0.96927998880952</v>
       </c>
       <c r="G124" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>4414.39063615061</v>
+        <v>4305.24353245505</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>4228.2682519367</v>
+        <v>4174.65209375531</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>4370.28325815642</v>
+        <v>4310.90000386176</v>
       </c>
       <c r="K124" s="11" t="n">
-        <v>4531.24890206455</v>
+        <v>4570.55251013277</v>
       </c>
       <c r="L124" s="12" t="n">
-        <v>4531.24890206455</v>
+        <v>4305.24353245505</v>
       </c>
       <c r="M124" s="13" t="n">
-        <v>4403.01573008471</v>
+        <v>4283.86939037307</v>
       </c>
       <c r="N124" s="14" t="n">
-        <v>4403.01573008471</v>
+        <v>4283.86939037307</v>
       </c>
       <c r="O124" s="15" t="n">
-        <v>0.0412097586943126</v>
+        <v>0.0308786880536441</v>
       </c>
       <c r="P124" s="16" t="n">
-        <v>0.0690033910777208</v>
+        <v>0.0376530711081946</v>
       </c>
       <c r="Q124" s="17" t="n">
-        <v>0.0420706660044825</v>
+        <v>0.0313603799620752</v>
       </c>
       <c r="R124" s="18" t="n">
-        <v>0.997423221684835</v>
+        <v>0.995035323339818</v>
       </c>
       <c r="S124" s="19" t="n">
-        <v>1.0413283802578</v>
+        <v>1.02616201162754</v>
       </c>
     </row>
     <row r="125">
@@ -8898,46 +8898,46 @@
         <v>4683.00158498928</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>1.06297943281984</v>
+        <v>1.06274241266063</v>
       </c>
       <c r="G125" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>4485.89489350355</v>
+        <v>4432.961825219</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>4326.46198896098</v>
+        <v>4265.65053170538</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v>4461.44063572916</v>
+        <v>4387.52908622133</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>4405.54298643988</v>
+        <v>4406.52554109057</v>
       </c>
       <c r="L125" s="12" t="n">
-        <v>4405.54298643988</v>
+        <v>4406.52554109057</v>
       </c>
       <c r="M125" s="13" t="n">
-        <v>4465.71696415756</v>
+        <v>4406.66588424604</v>
       </c>
       <c r="N125" s="14" t="n">
-        <v>4465.71696415756</v>
+        <v>4406.66588424604</v>
       </c>
       <c r="O125" s="15" t="n">
-        <v>0.0141400763665659</v>
+        <v>0.0282617038555527</v>
       </c>
       <c r="P125" s="16" t="n">
-        <v>0.0850223165265542</v>
+        <v>0.0692601158530239</v>
       </c>
       <c r="Q125" s="17" t="n">
-        <v>0.014240520115435</v>
+        <v>0.028664854756993</v>
       </c>
       <c r="R125" s="18" t="n">
-        <v>0.995501916601922</v>
+        <v>0.994068087655671</v>
       </c>
       <c r="S125" s="19" t="n">
-        <v>1.03218680195316</v>
+        <v>1.03305834631612</v>
       </c>
     </row>
     <row r="126">
@@ -8957,46 +8957,46 @@
         <v>4643.87571398214</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>1.02728499776374</v>
+        <v>1.03005672205805</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>4483.10683328925</v>
+        <v>4484.94879567994</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>4424.72805677605</v>
+        <v>4356.46265392516</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v>4549.88453047385</v>
+        <v>4459.78709423853</v>
       </c>
       <c r="K126" s="11" t="n">
-        <v>4520.53298168592</v>
+        <v>4508.36892234797</v>
       </c>
       <c r="L126" s="12" t="n">
-        <v>4520.53298168592</v>
+        <v>4508.36892234797</v>
       </c>
       <c r="M126" s="13" t="n">
-        <v>4495.53499695577</v>
+        <v>4480.98248207096</v>
       </c>
       <c r="N126" s="14" t="n">
-        <v>4495.53499695577</v>
+        <v>4480.98248207096</v>
       </c>
       <c r="O126" s="15" t="n">
-        <v>0.00665490558135583</v>
+        <v>0.0167239582154094</v>
       </c>
       <c r="P126" s="16" t="n">
-        <v>0.092585695295665</v>
+        <v>0.0919213146866362</v>
       </c>
       <c r="Q126" s="17" t="n">
-        <v>0.00667709866915778</v>
+        <v>0.0168645864644748</v>
       </c>
       <c r="R126" s="18" t="n">
-        <v>1.00277222116909</v>
+        <v>0.999115639043014</v>
       </c>
       <c r="S126" s="19" t="n">
-        <v>1.01600255185656</v>
+        <v>1.02858278333538</v>
       </c>
     </row>
     <row r="127">
@@ -9016,46 +9016,46 @@
         <v>4212.04006084719</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>0.928676273086205</v>
+        <v>0.935870280785125</v>
       </c>
       <c r="G127" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>4538.61187814316</v>
+        <v>4526.37383700262</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>4522.99981572829</v>
+        <v>4447.04491177342</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>4636.78603348826</v>
+        <v>4528.71006575674</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>4535.53103801135</v>
+        <v>4500.66654249732</v>
       </c>
       <c r="L127" s="12" t="n">
-        <v>4535.53103801135</v>
+        <v>4500.66654249732</v>
       </c>
       <c r="M127" s="13" t="n">
-        <v>4552.7882151363</v>
+        <v>4515.25127776335</v>
       </c>
       <c r="N127" s="14" t="n">
-        <v>4552.7882151363</v>
+        <v>4515.25127776335</v>
       </c>
       <c r="O127" s="15" t="n">
-        <v>0.012655158517852</v>
+        <v>0.00761851289301565</v>
       </c>
       <c r="P127" s="16" t="n">
-        <v>0.0775176239111848</v>
+        <v>0.0870665860923239</v>
       </c>
       <c r="Q127" s="17" t="n">
-        <v>0.0127355739015054</v>
+        <v>0.00764760760157124</v>
       </c>
       <c r="R127" s="18" t="n">
-        <v>1.00312349620848</v>
+        <v>0.997542721913877</v>
       </c>
       <c r="S127" s="19" t="n">
-        <v>1.00658598289225</v>
+        <v>1.0153374583219</v>
       </c>
     </row>
     <row r="128">
@@ -9063,92 +9063,118 @@
         <v>177</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>4532.94531294541</v>
+        <v>4416.92558923214</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>4532.94531294541</v>
+        <v>4416.92558923214</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>4532.94531294541</v>
+        <v>4416.92558923214</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>4532.94531294541</v>
+        <v>4416.92558923214</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>0.981250913271831</v>
+        <v>0.97047493620693</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>4659.29684257012</v>
+        <v>4519.95821482252</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>4621.27050424214</v>
+        <v>4537.44869802667</v>
       </c>
       <c r="J128" s="10" t="n">
-        <v>4723.16947812621</v>
+        <v>4595.57694775991</v>
       </c>
       <c r="K128" s="11" t="n">
-        <v>4619.55780283658</v>
+        <v>4551.3031037108</v>
       </c>
       <c r="L128" s="12" t="n">
-        <v>4619.55780283658</v>
+        <v>4551.3031037108</v>
       </c>
       <c r="M128" s="13" t="n">
-        <v>4591.54888122817</v>
+        <v>4520.33179751374</v>
       </c>
       <c r="N128" s="14" t="n">
-        <v>4591.54888122817</v>
+        <v>4520.33179751374</v>
       </c>
       <c r="O128" s="15" t="n">
-        <v>0.00847757422431776</v>
+        <v>0.00112455836960924</v>
       </c>
       <c r="P128" s="16" t="n">
-        <v>0.0428190955247476</v>
+        <v>0.055198323196328</v>
       </c>
       <c r="Q128" s="17" t="n">
-        <v>0.00851361061843492</v>
+        <v>0.00112519092246455</v>
       </c>
       <c r="R128" s="18" t="n">
-        <v>0.985459616841116</v>
+        <v>1.00008265180196</v>
       </c>
       <c r="S128" s="19" t="n">
-        <v>0.993568516929124</v>
+        <v>0.99622763767657</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
         <v>178</v>
       </c>
-      <c r="B129" s="2"/>
+      <c r="B129" s="2" t="n">
+        <v>4766.00149933856</v>
+      </c>
       <c r="C129" s="3" t="n">
-        <v>5211.23550695706</v>
+        <v>4766.00149933856</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>6340.62198509027</v>
+        <v>4766.00149933856</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>4283.01443814639</v>
+        <v>4766.00149933856</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>1.06358781756039</v>
-      </c>
-      <c r="G129" s="7"/>
-      <c r="H129" s="8"/>
-      <c r="I129" s="9"/>
-      <c r="J129" s="10"/>
-      <c r="K129" s="11"/>
-      <c r="L129" s="12"/>
-      <c r="M129" s="13"/>
+        <v>1.06430182193001</v>
+      </c>
+      <c r="G129" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" s="8" t="n">
+        <v>4516.10839293417</v>
+      </c>
+      <c r="I129" s="9" t="n">
+        <v>4627.75891898065</v>
+      </c>
+      <c r="J129" s="10" t="n">
+        <v>4661.52646961568</v>
+      </c>
+      <c r="K129" s="11" t="n">
+        <v>4478.05444013604</v>
+      </c>
+      <c r="L129" s="12" t="n">
+        <v>4478.05444013604</v>
+      </c>
+      <c r="M129" s="13" t="n">
+        <v>4502.47066132763</v>
+      </c>
       <c r="N129" s="14" t="n">
-        <v>4899.67581512015</v>
-      </c>
-      <c r="O129" s="15"/>
-      <c r="P129" s="16"/>
-      <c r="Q129" s="17"/>
-      <c r="R129" s="18"/>
-      <c r="S129" s="19"/>
+        <v>4502.47066132763</v>
+      </c>
+      <c r="O129" s="15" t="n">
+        <v>-0.00395911571778157</v>
+      </c>
+      <c r="P129" s="16" t="n">
+        <v>0.0217408761177216</v>
+      </c>
+      <c r="Q129" s="17" t="n">
+        <v>-0.00395128875184314</v>
+      </c>
+      <c r="R129" s="18" t="n">
+        <v>0.996980202771953</v>
+      </c>
+      <c r="S129" s="19" t="n">
+        <v>0.972926796782961</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
@@ -9156,16 +9182,16 @@
       </c>
       <c r="B130" s="2"/>
       <c r="C130" s="3" t="n">
-        <v>5100.29507672339</v>
+        <v>4664.53953058182</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>6730.91024533282</v>
+        <v>5668.23010814561</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>3864.70906928021</v>
+        <v>3838.57546663339</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>1.02792474910971</v>
+        <v>1.03070445996027</v>
       </c>
       <c r="G130" s="7"/>
       <c r="H130" s="8"/>
@@ -9175,7 +9201,7 @@
       <c r="L130" s="12"/>
       <c r="M130" s="13"/>
       <c r="N130" s="14" t="n">
-        <v>4961.73973935424</v>
+        <v>4525.583920304</v>
       </c>
       <c r="O130" s="15"/>
       <c r="P130" s="16"/>
@@ -9189,16 +9215,16 @@
       </c>
       <c r="B131" s="2"/>
       <c r="C131" s="3" t="n">
-        <v>4512.29128510906</v>
+        <v>4126.77321452653</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>6338.00456937515</v>
+        <v>5436.3547999046</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>3212.48942294128</v>
+        <v>3132.66109203037</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>0.925834308753845</v>
+        <v>0.933596509852354</v>
       </c>
       <c r="G131" s="7"/>
       <c r="H131" s="8"/>
@@ -9208,7 +9234,7 @@
       <c r="L131" s="12"/>
       <c r="M131" s="13"/>
       <c r="N131" s="14" t="n">
-        <v>4873.75682932135</v>
+        <v>4420.29631749498</v>
       </c>
       <c r="O131" s="15"/>
       <c r="P131" s="16"/>
@@ -9222,16 +9248,16 @@
       </c>
       <c r="B132" s="2"/>
       <c r="C132" s="3" t="n">
-        <v>4670.16274406819</v>
+        <v>4264.24070320446</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>6913.76062271779</v>
+        <v>5976.40789412975</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>3154.63916763564</v>
+        <v>3042.58830671957</v>
       </c>
       <c r="F132" s="6" t="n">
-        <v>0.982998898630276</v>
+        <v>0.97088695864908</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="8"/>
@@ -9241,7 +9267,7 @@
       <c r="L132" s="12"/>
       <c r="M132" s="13"/>
       <c r="N132" s="14" t="n">
-        <v>4750.9338520884</v>
+        <v>4392.10833477241</v>
       </c>
       <c r="O132" s="15"/>
       <c r="P132" s="16"/>
@@ -9254,10 +9280,18 @@
         <v>182</v>
       </c>
       <c r="B133" s="2"/>
-      <c r="C133" s="3"/>
-      <c r="D133" s="4"/>
-      <c r="E133" s="5"/>
-      <c r="F133" s="6"/>
+      <c r="C133" s="3" t="n">
+        <v>4882.94163916669</v>
+      </c>
+      <c r="D133" s="4" t="n">
+        <v>7210.39277618192</v>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>3306.77118315508</v>
+      </c>
+      <c r="F133" s="6" t="n">
+        <v>1.06553787255376</v>
+      </c>
       <c r="G133" s="7"/>
       <c r="H133" s="8"/>
       <c r="I133" s="9"/>
@@ -9265,7 +9299,9 @@
       <c r="K133" s="11"/>
       <c r="L133" s="12"/>
       <c r="M133" s="13"/>
-      <c r="N133" s="14"/>
+      <c r="N133" s="14" t="n">
+        <v>4582.60730560783</v>
+      </c>
       <c r="O133" s="15"/>
       <c r="P133" s="16"/>
       <c r="Q133" s="17"/>
@@ -9786,7 +9822,7 @@
         <v>220</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.0201897473373263</v>
+        <v>0.0231806818279697</v>
       </c>
     </row>
     <row r="6">
@@ -9794,7 +9830,7 @@
         <v>221</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0997056065288305</v>
+        <v>0.0994231037845042</v>
       </c>
     </row>
     <row r="7">
@@ -9802,7 +9838,7 @@
         <v>222</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.232903782222348</v>
+        <v>0.226926164741323</v>
       </c>
     </row>
     <row r="8">
@@ -9810,7 +9846,7 @@
         <v>223</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.387566116632433</v>
+        <v>0.384246171454591</v>
       </c>
     </row>
     <row r="9">
@@ -9818,7 +9854,7 @@
         <v>224</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.491300877502331</v>
+        <v>0.494964370307679</v>
       </c>
     </row>
     <row r="10">
@@ -9826,7 +9862,7 @@
         <v>225</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.474817211964052</v>
+        <v>0.484650037189408</v>
       </c>
     </row>
     <row r="11">
@@ -9834,7 +9870,7 @@
         <v>226</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.325011287867504</v>
+        <v>0.336029418365472</v>
       </c>
     </row>
     <row r="12">
@@ -9842,7 +9878,7 @@
         <v>227</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.138611141073429</v>
+        <v>0.13627273846482</v>
       </c>
     </row>
     <row r="13">
@@ -9850,7 +9886,7 @@
         <v>228</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.0204689317277212</v>
+        <v>0.0100434008054514</v>
       </c>
     </row>
     <row r="14">
@@ -9908,4 +9944,237 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
+    <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
+    <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5dd4176-d247-4204-85b8-921214f3ccea" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="01529062-7a8b-4d76-943d-e0db5644ee6d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="359b39ce-e1f9-4933-8424-33b611e6fdcd" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c9b73259-0823-4f05-8927-4a40ee49fbe1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="359b39ce-e1f9-4933-8424-33b611e6fdcd">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF0F39F1-988E-493E-BFB2-2B722DAE028C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BBD8B5E-BD90-4590-A864-BF0DF3E53D05}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51FC1727-50FD-4849-A2DC-85E002F4E194}"/>
 </file>
--- a/indicadores/ARG-ISS_out.xlsx
+++ b/indicadores/ARG-ISS_out.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="231">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -23,7 +23,7 @@
     <t xml:space="preserve">Título</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingresos por servicios de Argentina</t>
+    <t xml:space="preserve">Ingresos por servicios</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
@@ -71,6 +71,12 @@
     <t xml:space="preserve">Regresores</t>
   </si>
   <si>
+    <t xml:space="preserve">Alcance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argentina</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resumen del correlograma</t>
   </si>
   <si>
@@ -104,13 +110,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">30/03/2026</t>
+    <t xml:space="preserve">17/06/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">arodriguez</t>
+    <t xml:space="preserve">focampo</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1203,9 +1209,13 @@
       <c r="J6" s="1"/>
     </row>
     <row r="7">
-      <c r="A7"/>
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
       <c r="B7"/>
-      <c r="C7"/>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
       <c r="D7"/>
       <c r="E7"/>
       <c r="F7"/>
@@ -1216,7 +1226,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8"/>
       <c r="C8"/>
@@ -1230,12 +1240,12 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.494964370307679</v>
+        <v>0.4936716467603</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1246,7 +1256,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
@@ -1274,7 +1284,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
@@ -1288,12 +1298,12 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.244989727874077</v>
+        <v>0.243711694815027</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1316,7 +1326,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -1330,7 +1340,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B16"/>
       <c r="C16"/>
@@ -1344,7 +1354,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1358,12 +1368,12 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.213664886406701</v>
+        <v>0.297643251766162</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1374,7 +1384,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1388,12 +1398,12 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.0506467438502353</v>
+        <v>0.0682675277024875</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1536,10 +1546,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C32"/>
       <c r="D32"/>
@@ -1552,10 +1562,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C33"/>
       <c r="D33"/>
@@ -1579,66 +1589,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="R1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>938.6</v>
@@ -1691,7 +1701,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>731.2</v>
@@ -1748,7 +1758,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>812</v>
@@ -1805,7 +1815,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>882.3</v>
@@ -1862,7 +1872,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1117.8</v>
@@ -1921,7 +1931,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>844.7</v>
@@ -1980,7 +1990,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>890.3</v>
@@ -2039,7 +2049,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>972.8</v>
@@ -2098,7 +2108,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1241.45311786661</v>
@@ -2157,7 +2167,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>951.314342369399</v>
@@ -2216,7 +2226,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1059.37770881758</v>
@@ -2275,7 +2285,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1153.20813262492</v>
@@ -2334,7 +2344,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1313.13113092079</v>
@@ -2393,7 +2403,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>986.751208620193</v>
@@ -2452,7 +2462,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1070.461723113</v>
@@ -2511,7 +2521,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1228.42957513478</v>
@@ -2570,7 +2580,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1390.01590374665</v>
@@ -2629,7 +2639,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1131.74469404318</v>
@@ -2688,7 +2698,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1132.38315005501</v>
@@ -2747,7 +2757,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1199.93660347662</v>
@@ -2806,7 +2816,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1395.88556343368</v>
@@ -2865,7 +2875,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1087.93885305562</v>
@@ -2924,7 +2934,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1106.16144137784</v>
@@ -2983,7 +2993,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1128.71717192684</v>
@@ -3042,7 +3052,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1427.26522921678</v>
@@ -3101,7 +3111,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1111.28111175113</v>
@@ -3160,7 +3170,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1143.39024827993</v>
@@ -3219,7 +3229,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1253.57935444932</v>
@@ -3278,7 +3288,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1449.81126794023</v>
@@ -3337,7 +3347,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1073.94141993997</v>
@@ -3396,7 +3406,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1006.17899473794</v>
@@ -3455,7 +3465,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1097.12674299929</v>
@@ -3514,7 +3524,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>925.043759968322</v>
@@ -3573,7 +3583,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>751.640121231456</v>
@@ -3632,7 +3642,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>839.434712132987</v>
@@ -3691,7 +3701,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>979.295252197054</v>
@@ -3750,7 +3760,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1025.67860484186</v>
@@ -3809,7 +3819,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1000.69836644118</v>
@@ -3868,7 +3878,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1086.52423367125</v>
@@ -3927,7 +3937,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1387.01112527143</v>
@@ -3986,7 +3996,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>1344.70366909301</v>
@@ -4045,7 +4055,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>1151.18082419785</v>
@@ -4104,7 +4114,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>1247.82293557512</v>
@@ -4163,7 +4173,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>1544.43982105477</v>
@@ -4222,7 +4232,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>1628.14312336858</v>
@@ -4281,7 +4291,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>1470.67718086851</v>
@@ -4340,7 +4350,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>1577.11367430347</v>
@@ -4399,7 +4409,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>1958.50082068495</v>
@@ -4458,7 +4468,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>1945.13754028478</v>
@@ -4517,7 +4527,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>1712.91881357271</v>
@@ -4576,7 +4586,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>1898.85436922996</v>
@@ -4635,7 +4645,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>2354.10436983294</v>
@@ -4694,7 +4704,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>2600.12971883191</v>
@@ -4753,7 +4763,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>2154.1851770688</v>
@@ -4812,7 +4822,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>2321.41186175029</v>
@@ -4871,7 +4881,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>2970.00973852471</v>
@@ -4930,7 +4940,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>2943.99757674031</v>
@@ -4989,7 +4999,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>2579.42813442157</v>
@@ -5048,7 +5058,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>2838.16101860859</v>
@@ -5107,7 +5117,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>3062.56234200586</v>
@@ -5166,7 +5176,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>2755.1961460775</v>
@@ -5225,7 +5235,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>2346.01620451565</v>
@@ -5284,7 +5294,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>2313.68685692728</v>
@@ -5343,7 +5353,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>3129.72211611434</v>
@@ -5402,7 +5412,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>3164.98577161261</v>
@@ -5461,7 +5471,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>2987.75245463425</v>
@@ -5520,7 +5530,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>2968.07680589468</v>
@@ -5579,7 +5589,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>3696.32832846722</v>
@@ -5638,7 +5648,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>3523.50222767909</v>
@@ -5697,7 +5707,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>3347.59534135146</v>
@@ -5756,7 +5766,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>3450.41139520334</v>
@@ -5815,7 +5825,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>4175.47231114959</v>
@@ -5874,7 +5884,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>3842.8691195722</v>
@@ -5933,7 +5943,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>3354.26213069839</v>
@@ -5992,7 +6002,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>3413.57383659744</v>
@@ -6051,7 +6061,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>3636.39564268968</v>
@@ -6110,7 +6120,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>3401.60556878379</v>
@@ -6169,7 +6179,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>3222.50375079941</v>
@@ -6228,7 +6238,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>3185.85231014052</v>
@@ -6287,7 +6297,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>3869.93013865163</v>
@@ -6346,7 +6356,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>3413.56946580066</v>
@@ -6405,7 +6415,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>3098.85650879477</v>
@@ -6464,7 +6474,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>3199.75362495821</v>
@@ -6523,7 +6533,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>3684.19222817274</v>
@@ -6582,7 +6592,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>3473.96328435329</v>
@@ -6641,7 +6651,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>3047.37400305265</v>
@@ -6700,7 +6710,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>3228.33181776595</v>
@@ -6759,7 +6769,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>3463.84324480454</v>
@@ -6818,7 +6828,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>3610.11150456841</v>
@@ -6877,7 +6887,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>2954.63346329572</v>
@@ -6936,7 +6946,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>3221.79961592558</v>
@@ -6995,7 +7005,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>3638.1623004355</v>
@@ -7054,7 +7064,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>4037.4781476365</v>
@@ -7113,7 +7123,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>3625.34060687029</v>
@@ -7172,7 +7182,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>3659.99110295258</v>
@@ -7231,7 +7241,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>4183.39210452291</v>
@@ -7290,7 +7300,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>4473.66539441506</v>
@@ -7349,7 +7359,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>3517.77670169052</v>
@@ -7408,7 +7418,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>3357.72554729946</v>
@@ -7467,7 +7477,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>3992.99553442729</v>
@@ -7526,7 +7536,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>3941.5912142825</v>
@@ -7585,7 +7595,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>3374.51907473218</v>
@@ -7644,7 +7654,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>3469.76766476378</v>
@@ -7703,7 +7713,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>4016.542850834</v>
@@ -7762,7 +7772,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>3685.04709961106</v>
@@ -7821,7 +7831,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>1880.07334156122</v>
@@ -7880,7 +7890,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>1803.44547006555</v>
@@ -7939,7 +7949,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>2123.17169555586</v>
@@ -7998,7 +8008,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>1981.82749195669</v>
@@ -8057,7 +8067,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>2244.76524089118</v>
@@ -8116,7 +8126,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>2416.28398981369</v>
@@ -8175,7 +8185,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>2945.85895499108</v>
@@ -8234,7 +8244,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>3141.23369626134</v>
@@ -8293,7 +8303,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>3374.61116034377</v>
@@ -8352,7 +8362,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>3733.26985008941</v>
@@ -8411,7 +8421,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B117" s="2" t="n">
         <v>4166.74891556592</v>
@@ -8470,7 +8480,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B118" s="2" t="n">
         <v>4233.78150541524</v>
@@ -8529,7 +8539,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>3910.97166063794</v>
@@ -8588,7 +8598,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>3961.64730583922</v>
@@ -8647,7 +8657,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B121" s="2" t="n">
         <v>4425.94559335052</v>
@@ -8706,7 +8716,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B122" s="2" t="n">
         <v>4179.49876291989</v>
@@ -8765,7 +8775,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B123" s="2" t="n">
         <v>3874.20337444698</v>
@@ -8824,7 +8834,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B124" s="2" t="n">
         <v>4430.14508587482</v>
@@ -8883,7 +8893,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B125" s="2" t="n">
         <v>4683.00158498928</v>
@@ -8942,7 +8952,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B126" s="2" t="n">
         <v>4643.87571398214</v>
@@ -9001,7 +9011,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B127" s="2" t="n">
         <v>4212.04006084719</v>
@@ -9060,7 +9070,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B128" s="2" t="n">
         <v>4416.92558923214</v>
@@ -9119,7 +9129,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B129" s="2" t="n">
         <v>4766.00149933856</v>
@@ -9178,7 +9188,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B130" s="2"/>
       <c r="C130" s="3" t="n">
@@ -9211,7 +9221,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B131" s="2"/>
       <c r="C131" s="3" t="n">
@@ -9244,7 +9254,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B132" s="2"/>
       <c r="C132" s="3" t="n">
@@ -9277,7 +9287,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B133" s="2"/>
       <c r="C133" s="3" t="n">
@@ -9310,7 +9320,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B134" s="2"/>
       <c r="C134" s="3"/>
@@ -9333,7 +9343,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B135" s="2"/>
       <c r="C135" s="3"/>
@@ -9356,7 +9366,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B136" s="2"/>
       <c r="C136" s="3"/>
@@ -9379,7 +9389,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B137" s="2"/>
       <c r="C137" s="3"/>
@@ -9402,7 +9412,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B138" s="2"/>
       <c r="C138" s="3"/>
@@ -9425,7 +9435,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B139" s="2"/>
       <c r="C139" s="3"/>
@@ -9448,7 +9458,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B140" s="2"/>
       <c r="C140" s="3"/>
@@ -9471,7 +9481,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B141" s="2"/>
       <c r="C141" s="3"/>
@@ -9494,7 +9504,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B142" s="2"/>
       <c r="C142" s="3"/>
@@ -9517,7 +9527,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B143" s="2"/>
       <c r="C143" s="3"/>
@@ -9540,7 +9550,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B144" s="2"/>
       <c r="C144" s="3"/>
@@ -9563,7 +9573,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B145" s="2"/>
       <c r="C145" s="3"/>
@@ -9586,7 +9596,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B146" s="2"/>
       <c r="C146" s="3"/>
@@ -9609,7 +9619,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B147" s="2"/>
       <c r="C147" s="3"/>
@@ -9632,7 +9642,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B148" s="2"/>
       <c r="C148" s="3"/>
@@ -9655,7 +9665,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B149" s="2"/>
       <c r="C149" s="3"/>
@@ -9689,97 +9699,97 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -9803,7 +9813,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -9813,80 +9823,80 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.0231806818279697</v>
+        <v>0.0211556347589539</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0994231037845042</v>
+        <v>0.103122817401219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.226926164741323</v>
+        <v>0.231147261464707</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.384246171454591</v>
+        <v>0.384395391172474</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.494964370307679</v>
+        <v>0.4936716467603</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.484650037189408</v>
+        <v>0.482664456923521</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.336029418365472</v>
+        <v>0.335607966593852</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.13627273846482</v>
+        <v>0.139637464961147</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.0100434008054514</v>
+        <v>0.0125624053766106</v>
       </c>
     </row>
     <row r="14">
@@ -9944,237 +9954,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
-    <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5dd4176-d247-4204-85b8-921214f3ccea" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="01529062-7a8b-4d76-943d-e0db5644ee6d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="359b39ce-e1f9-4933-8424-33b611e6fdcd" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c9b73259-0823-4f05-8927-4a40ee49fbe1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="359b39ce-e1f9-4933-8424-33b611e6fdcd">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF0F39F1-988E-493E-BFB2-2B722DAE028C}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BBD8B5E-BD90-4590-A864-BF0DF3E53D05}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51FC1727-50FD-4849-A2DC-85E002F4E194}"/>
 </file>
--- a/indicadores/ARG-ISS_out.xlsx
+++ b/indicadores/ARG-ISS_out.xlsx
@@ -110,13 +110,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">17/06/2026</t>
+    <t xml:space="preserve">25/06/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">focampo</t>
+    <t xml:space="preserve">arodriguez</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1225,9 +1225,7 @@
       <c r="J7" s="1"/>
     </row>
     <row r="8">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
+      <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
@@ -1239,14 +1237,10 @@
       <c r="J8" s="1"/>
     </row>
     <row r="9">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
+      <c r="A9"/>
       <c r="B9"/>
       <c r="C9"/>
-      <c r="D9" t="n">
-        <v>0.4936716467603</v>
-      </c>
+      <c r="D9"/>
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9"/>
@@ -1256,13 +1250,11 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
+      <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
@@ -1271,10 +1263,14 @@
       <c r="J10" s="1"/>
     </row>
     <row r="11">
-      <c r="A11"/>
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
       <c r="B11"/>
       <c r="C11"/>
-      <c r="D11"/>
+      <c r="D11" t="n">
+        <v>0.485729310418434</v>
+      </c>
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11"/>
@@ -1284,11 +1280,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
-      <c r="D12"/>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12"/>
@@ -1297,14 +1295,10 @@
       <c r="J12" s="1"/>
     </row>
     <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
+      <c r="A13"/>
       <c r="B13"/>
       <c r="C13"/>
-      <c r="D13" t="n">
-        <v>0.243711694815027</v>
-      </c>
+      <c r="D13"/>
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13"/>
@@ -1313,7 +1307,9 @@
       <c r="J13" s="1"/>
     </row>
     <row r="14">
-      <c r="A14"/>
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -1326,11 +1322,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
-      <c r="D15"/>
+      <c r="D15" t="n">
+        <v>0.235932962999567</v>
+      </c>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
@@ -1339,9 +1337,7 @@
       <c r="J15" s="1"/>
     </row>
     <row r="16">
-      <c r="A16" t="s">
-        <v>26</v>
-      </c>
+      <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -1354,7 +1350,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1368,13 +1364,11 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
-      <c r="D18" t="n">
-        <v>0.297643251766162</v>
-      </c>
+      <c r="D18"/>
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
@@ -1384,7 +1378,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1403,7 +1397,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.0682675277024875</v>
+        <v>0.207073117055489</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1413,7 +1407,9 @@
       <c r="J20" s="1"/>
     </row>
     <row r="21">
-      <c r="A21"/>
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -1425,10 +1421,14 @@
       <c r="J21" s="1"/>
     </row>
     <row r="22">
-      <c r="A22"/>
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
       <c r="B22"/>
       <c r="C22"/>
-      <c r="D22"/>
+      <c r="D22" t="n">
+        <v>0.0360933322607553</v>
+      </c>
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
@@ -1669,13 +1669,13 @@
         <v>1</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>787.328080192178</v>
+        <v>787.328080192179</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>865.177654549158</v>
+        <v>865.177476089026</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>805.036332075287</v>
+        <v>805.036332099064</v>
       </c>
       <c r="K2" s="11" t="n">
         <v>786.96355327574</v>
@@ -1684,10 +1684,10 @@
         <v>786.96355327574</v>
       </c>
       <c r="M2" s="13" t="n">
-        <v>801.181155821325</v>
+        <v>801.181155821326</v>
       </c>
       <c r="N2" s="14" t="n">
-        <v>801.181155821325</v>
+        <v>801.181155821326</v>
       </c>
       <c r="O2" s="15"/>
       <c r="P2" s="16"/>
@@ -1696,7 +1696,7 @@
         <v>1.01759504833838</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>0.926030800273984</v>
+        <v>0.92603099128633</v>
       </c>
     </row>
     <row r="3">
@@ -1716,44 +1716,44 @@
         <v>731.2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.881371239105931</v>
+        <v>0.88137123910593</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>830.084542665156</v>
+        <v>830.084542665155</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>887.244267810002</v>
+        <v>887.244121486426</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>835.542348197256</v>
+        <v>835.542348213706</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>829.616360912496</v>
+        <v>829.616360912497</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>829.616360912496</v>
+        <v>829.616360912497</v>
       </c>
       <c r="M3" s="13" t="n">
-        <v>829.119918149061</v>
+        <v>829.11991814906</v>
       </c>
       <c r="N3" s="14" t="n">
-        <v>829.119918149061</v>
+        <v>829.11991814906</v>
       </c>
       <c r="O3" s="15" t="n">
-        <v>0.0342777150818465</v>
+        <v>0.0342777150818458</v>
       </c>
       <c r="P3" s="16"/>
       <c r="Q3" s="17" t="n">
-        <v>0.0348719663770598</v>
+        <v>0.0348719663770591</v>
       </c>
       <c r="R3" s="18" t="n">
-        <v>0.998837920155701</v>
+        <v>0.998837920155702</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>0.934488898074923</v>
+        <v>0.934489052190068</v>
       </c>
     </row>
     <row r="4">
@@ -1773,44 +1773,44 @@
         <v>812</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.933029404371913</v>
+        <v>0.933029404371916</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>863.981477130225</v>
+        <v>863.981477130223</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>909.26199725755</v>
+        <v>909.261883182068</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>865.958000425227</v>
+        <v>865.958000434232</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>870.283397495509</v>
+        <v>870.283397495507</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>870.283397495509</v>
+        <v>870.283397495507</v>
       </c>
       <c r="M4" s="13" t="n">
-        <v>864.116639474058</v>
+        <v>864.116639474057</v>
       </c>
       <c r="N4" s="14" t="n">
-        <v>864.116639474058</v>
+        <v>864.116639474057</v>
       </c>
       <c r="O4" s="15" t="n">
-        <v>0.0413429604302455</v>
+        <v>0.0413429604302442</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="17" t="n">
-        <v>0.0422094808711444</v>
+        <v>0.0422094808711431</v>
       </c>
       <c r="R4" s="18" t="n">
         <v>1.00015644125182</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.95034945052179</v>
+        <v>0.950349569752094</v>
       </c>
     </row>
     <row r="5">
@@ -1830,44 +1830,44 @@
         <v>882.3</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.995505498598122</v>
+        <v>0.995505498598123</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>896.640668661376</v>
+        <v>896.640668661375</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>931.145941636695</v>
+        <v>931.145860123834</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>896.163294928778</v>
+        <v>896.163294930019</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>886.283401992717</v>
+        <v>886.283401992716</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>886.283401992717</v>
+        <v>886.283401992716</v>
       </c>
       <c r="M5" s="13" t="n">
-        <v>895.902867099815</v>
+        <v>895.902867099814</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>895.902867099815</v>
+        <v>895.902867099814</v>
       </c>
       <c r="O5" s="15" t="n">
-        <v>0.0361242407600394</v>
+        <v>0.0361242407600398</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="17" t="n">
-        <v>0.0367846494023112</v>
+        <v>0.0367846494023116</v>
       </c>
       <c r="R5" s="18" t="n">
         <v>0.999177149121885</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>0.96215085846271</v>
+        <v>0.962150942689759</v>
       </c>
     </row>
     <row r="6">
@@ -1893,13 +1893,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>933.341254450799</v>
+        <v>933.341254450802</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>952.78683806748</v>
+        <v>952.786789706053</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>926.059864862841</v>
+        <v>926.05986485575</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>940.761266918315</v>
@@ -1914,19 +1914,19 @@
         <v>930.90292816305</v>
       </c>
       <c r="O6" s="15" t="n">
-        <v>0.0383230057920975</v>
+        <v>0.0383230057920988</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>0.161913159588409</v>
+        <v>0.161913159588408</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>0.0390668032758235</v>
+        <v>0.0390668032758248</v>
       </c>
       <c r="R6" s="18" t="n">
-        <v>0.997387529720644</v>
+        <v>0.997387529720641</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.977031683236916</v>
+        <v>0.977031732828962</v>
       </c>
     </row>
     <row r="7">
@@ -1946,7 +1946,7 @@
         <v>844.7</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.883756951969706</v>
+        <v>0.883756951969705</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>1</v>
@@ -1955,37 +1955,37 @@
         <v>954.723469186352</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>974.047384582669</v>
+        <v>974.047370286722</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>955.499943917663</v>
+        <v>955.499943901422</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>955.805776822851</v>
+        <v>955.805776822852</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>955.805776822851</v>
+        <v>955.805776822852</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>951.733009987473</v>
+        <v>951.733009987472</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>951.733009987473</v>
+        <v>951.733009987472</v>
       </c>
       <c r="O7" s="15" t="n">
-        <v>0.0221295381277381</v>
+        <v>0.0221295381277366</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>0.147883423319676</v>
+        <v>0.147883423319674</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>0.0223762125934308</v>
+        <v>0.0223762125934293</v>
       </c>
       <c r="R7" s="18" t="n">
-        <v>0.996867722125416</v>
+        <v>0.996867722125414</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>0.977091078988158</v>
+        <v>0.977091093328775</v>
       </c>
     </row>
     <row r="8">
@@ -2005,46 +2005,46 @@
         <v>890.3</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.932681788535637</v>
+        <v>0.932681788535645</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>954.899709050321</v>
+        <v>954.899709050316</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>994.782763233057</v>
+        <v>994.782784272096</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>984.409272793773</v>
+        <v>984.409272767346</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>954.559219385876</v>
+        <v>954.559219385868</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>954.559219385876</v>
+        <v>954.559219385868</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>959.957024280367</v>
+        <v>959.957024280363</v>
       </c>
       <c r="N8" s="14" t="n">
-        <v>959.957024280367</v>
+        <v>959.957024280363</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>0.00860397332161607</v>
+        <v>0.00860397332161365</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>0.110911398332338</v>
+        <v>0.110911398332335</v>
       </c>
       <c r="Q8" s="17" t="n">
-        <v>0.00864109388514533</v>
+        <v>0.00864109388514289</v>
       </c>
       <c r="R8" s="18" t="n">
         <v>1.00529617422868</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>0.964991614008765</v>
+        <v>0.964991593599786</v>
       </c>
     </row>
     <row r="9">
@@ -2070,13 +2070,13 @@
         <v>1</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>985.343367101596</v>
+        <v>985.343367101597</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>1014.83675506459</v>
+        <v>1014.83681307252</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>1012.71512135622</v>
+        <v>1012.71512131844</v>
       </c>
       <c r="K9" s="11" t="n">
         <v>974.903881526865</v>
@@ -2085,25 +2085,25 @@
         <v>974.903881526865</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>988.612971912754</v>
+        <v>988.612971912757</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>988.612971912754</v>
+        <v>988.612971912757</v>
       </c>
       <c r="O9" s="15" t="n">
-        <v>0.0294144051993824</v>
+        <v>0.0294144051993889</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>0.103482317355516</v>
+        <v>0.10348231735552</v>
       </c>
       <c r="Q9" s="17" t="n">
-        <v>0.0298512817840668</v>
+        <v>0.0298512817840735</v>
       </c>
       <c r="R9" s="18" t="n">
         <v>1.00331823902238</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>0.974159604467452</v>
+        <v>0.974159548784632</v>
       </c>
     </row>
     <row r="10">
@@ -2123,46 +2123,46 @@
         <v>1241.45311786661</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1.18224070425683</v>
+        <v>1.18224070425681</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>1034.80641046859</v>
+        <v>1034.8064104686</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>1034.02800140831</v>
+        <v>1034.02809837027</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>1040.19550920303</v>
+        <v>1040.19550915271</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>1050.08490521141</v>
+        <v>1050.08490521143</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>1050.08490521141</v>
+        <v>1050.08490521143</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>1036.56131829855</v>
+        <v>1036.56131829856</v>
       </c>
       <c r="N10" s="14" t="n">
-        <v>1036.56131829855</v>
+        <v>1036.56131829856</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>0.0473611668366306</v>
+        <v>0.0473611668366361</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>0.113500975170413</v>
+        <v>0.113500975170422</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>0.0485006243576034</v>
+        <v>0.0485006243576092</v>
       </c>
       <c r="R10" s="18" t="n">
         <v>1.00169588032332</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>1.00244994998858</v>
+        <v>1.00244985598775</v>
       </c>
     </row>
     <row r="11">
@@ -2182,25 +2182,25 @@
         <v>951.314342369399</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.888106405198078</v>
+        <v>0.88810640519808</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>1085.56532501183</v>
+        <v>1085.56532501182</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>1052.1501855493</v>
+        <v>1052.15032376542</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1066.43939973305</v>
+        <v>1066.43939966921</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>1071.17158124451</v>
+        <v>1071.1715812445</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>1071.17158124451</v>
+        <v>1071.1715812445</v>
       </c>
       <c r="M11" s="13" t="n">
         <v>1082.43495389537</v>
@@ -2209,19 +2209,19 @@
         <v>1082.43495389537</v>
       </c>
       <c r="O11" s="15" t="n">
-        <v>0.0433042801697507</v>
+        <v>0.043304280169742</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>0.13733047245006</v>
+        <v>0.137330472450061</v>
       </c>
       <c r="Q11" s="17" t="n">
-        <v>0.044255592782606</v>
+        <v>0.0442555927825969</v>
       </c>
       <c r="R11" s="18" t="n">
-        <v>0.997116367809164</v>
+        <v>0.997116367809172</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>1.02878369339474</v>
+        <v>1.02878355824819</v>
       </c>
     </row>
     <row r="12">
@@ -2241,46 +2241,46 @@
         <v>1059.37770881758</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.931475218462587</v>
+        <v>0.9314752184626</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>1129.95330183587</v>
+        <v>1129.95330183585</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>1069.00702633752</v>
+        <v>1069.00720836231</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1091.0852033252</v>
+        <v>1091.08520324729</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>1137.31174788106</v>
+        <v>1137.31174788104</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>1137.31174788106</v>
+        <v>1137.31174788104</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>1124.35480964979</v>
+        <v>1124.35480964978</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>1124.35480964979</v>
+        <v>1124.35480964978</v>
       </c>
       <c r="O12" s="15" t="n">
-        <v>0.037996278298533</v>
+        <v>0.0379962782985236</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>0.171255359574728</v>
+        <v>0.171255359574721</v>
       </c>
       <c r="Q12" s="17" t="n">
-        <v>0.0387273670381383</v>
+        <v>0.0387273670381285</v>
       </c>
       <c r="R12" s="18" t="n">
-        <v>0.995045377382422</v>
+        <v>0.995045377382429</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>1.05177494810478</v>
+        <v>1.05177476901419</v>
       </c>
     </row>
     <row r="13">
@@ -2300,25 +2300,25 @@
         <v>1153.20813262492</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1.00137542358455</v>
+        <v>1.00137542358456</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>1146.69389986816</v>
+        <v>1146.69389986817</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>1084.41413099523</v>
+        <v>1084.41435955123</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>1113.79499126595</v>
+        <v>1113.79499117417</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>1151.62416159253</v>
+        <v>1151.62416159251</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>1151.62416159253</v>
+        <v>1151.62416159251</v>
       </c>
       <c r="M13" s="13" t="n">
         <v>1139.50066925204</v>
@@ -2327,19 +2327,19 @@
         <v>1139.50066925204</v>
       </c>
       <c r="O13" s="15" t="n">
-        <v>0.0133807884168391</v>
+        <v>0.0133807884168514</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>0.152625649901549</v>
+        <v>0.152625649901548</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>0.0134707118004593</v>
+        <v>0.0134707118004718</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>0.99372698274845</v>
+        <v>0.993726982748443</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>1.05079843270416</v>
+        <v>1.05079821123321</v>
       </c>
     </row>
     <row r="14">
@@ -2359,46 +2359,46 @@
         <v>1313.13113092079</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>1.17512176816792</v>
+        <v>1.17512176816787</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>1120.02758790004</v>
+        <v>1120.02758790005</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>1098.22979719567</v>
+        <v>1098.23007505963</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>1134.46196756453</v>
+        <v>1134.46196746023</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>1117.44260594205</v>
+        <v>1117.4426059421</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>1117.44260594205</v>
+        <v>1117.4426059421</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>1122.93892679198</v>
+        <v>1122.93892679199</v>
       </c>
       <c r="N14" s="14" t="n">
-        <v>1122.93892679198</v>
+        <v>1122.93892679199</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.0146408667254238</v>
+        <v>-0.0146408667254178</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>0.0833309201960306</v>
+        <v>0.0833309201960308</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>-0.01453421038439</v>
+        <v>-0.014534210384384</v>
       </c>
       <c r="R14" s="18" t="n">
         <v>1.00259934569772</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>1.02249905225609</v>
+        <v>1.0224987935529</v>
       </c>
     </row>
     <row r="15">
@@ -2418,46 +2418,46 @@
         <v>986.751208620193</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.892788492973017</v>
+        <v>0.892788492973055</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>1110.73830140417</v>
+        <v>1110.73830140415</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>1110.35432888119</v>
+        <v>1110.35465874126</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>1153.16848208184</v>
+        <v>1153.16848196797</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>1105.24633369128</v>
+        <v>1105.24633369124</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>1105.24633369128</v>
+        <v>1105.24633369124</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>1119.56121963657</v>
+        <v>1119.56121963656</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>1119.56121963657</v>
+        <v>1119.56121963656</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.00301244993462712</v>
+        <v>-0.00301244993464917</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>0.0342988422607702</v>
+        <v>0.0342988422607566</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>-0.00300791706015102</v>
+        <v>-0.003007917060173</v>
       </c>
       <c r="R15" s="18" t="n">
         <v>1.00794329161176</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>1.00829184929162</v>
+        <v>1.00829154975198</v>
       </c>
     </row>
     <row r="16">
@@ -2477,46 +2477,46 @@
         <v>1070.461723113</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.930585746875263</v>
+        <v>0.930585746875276</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>1154.7317803985</v>
+        <v>1154.73178039847</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>1120.70003799961</v>
+        <v>1120.70042228166</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>1169.91178787062</v>
+        <v>1169.91178775227</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>1150.30960522167</v>
+        <v>1150.30960522166</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>1150.30960522167</v>
+        <v>1150.30960522166</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>1154.60742527368</v>
+        <v>1154.60742527366</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>1154.60742527368</v>
+        <v>1154.60742527366</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.0308235542954299</v>
+        <v>0.0308235542954276</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>0.0269066449169348</v>
+        <v>0.0269066449169284</v>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>0.0313035187557551</v>
+        <v>0.0313035187557527</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>0.999892308216567</v>
+        <v>0.999892308216576</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>1.03025554218289</v>
+        <v>1.03025518891388</v>
       </c>
     </row>
     <row r="17">
@@ -2536,46 +2536,46 @@
         <v>1228.42957513478</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1.00477510295669</v>
+        <v>1.0047751029567</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>0.657647058539798</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>1193.30186694772</v>
+        <v>1193.30186694775</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>1129.17604400176</v>
+        <v>1129.17648466324</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>1184.44952724171</v>
+        <v>1184.44952712664</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>1222.5915744926</v>
+        <v>1222.59157449259</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>1212.5641569601</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>1192.30983111867</v>
+        <v>1192.30983111869</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>1192.30983111867</v>
+        <v>1192.30983111869</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.0321320656439266</v>
+        <v>0.0321320656439554</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>0.0463441253626458</v>
+        <v>0.0463441253626564</v>
       </c>
       <c r="Q17" s="17" t="n">
-        <v>0.0326538743989599</v>
+        <v>0.0326538743989897</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>0.99916866313837</v>
+        <v>0.999168663138357</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>1.05591137666467</v>
+        <v>1.05591096459495</v>
       </c>
     </row>
     <row r="18">
@@ -2595,25 +2595,25 @@
         <v>1390.01590374665</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1.16849929434796</v>
+        <v>1.16849929434787</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0.865893581389257</v>
+        <v>0.865893581389623</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>1221.09939587363</v>
+        <v>1221.09939587365</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>1135.70997231799</v>
+        <v>1135.71047060771</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>1196.44133159265</v>
+        <v>1196.44133149193</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>1189.57359278706</v>
+        <v>1189.57359278715</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>1193.80140533283</v>
+        <v>1193.8014053329</v>
       </c>
       <c r="M18" s="13" t="n">
         <v>1215.72376550208</v>
@@ -2622,19 +2622,19 @@
         <v>1215.72376550208</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.0194471309063294</v>
+        <v>0.0194471309063204</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>0.0826267898425859</v>
+        <v>0.0826267898425805</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>0.0196374581273342</v>
+        <v>0.0196374581273251</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>0.99559771269258</v>
+        <v>0.995597712692566</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>1.07045266409062</v>
+        <v>1.07045219443258</v>
       </c>
     </row>
     <row r="19">
@@ -2654,46 +2654,46 @@
         <v>1131.74469404318</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.896269512872903</v>
+        <v>0.896269512872993</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>1239.17609899248</v>
+        <v>1239.1760989924</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>1140.28156594922</v>
+        <v>1140.28212213198</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>1205.68740546962</v>
+        <v>1205.68740539818</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>1262.72809438255</v>
+        <v>1262.72809438243</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>1262.72809438255</v>
+        <v>1262.72809438243</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>1234.62755985185</v>
+        <v>1234.62755985178</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>1234.62755985185</v>
+        <v>1234.62755985178</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.015429762418255</v>
+        <v>0.0154297624181964</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.102778068940821</v>
+        <v>0.102778068940776</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>0.0155494158181284</v>
+        <v>0.0155494158180689</v>
       </c>
       <c r="R19" s="18" t="n">
-        <v>0.996329384383439</v>
+        <v>0.996329384383448</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>1.08273920820959</v>
+        <v>1.08273868009384</v>
       </c>
     </row>
     <row r="20">
@@ -2713,46 +2713,46 @@
         <v>1132.38315005501</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.928751850087309</v>
+        <v>0.928751850087378</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>1224.46749876136</v>
+        <v>1224.46749876132</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>1142.90687504205</v>
+        <v>1142.90748808718</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>1211.97475378748</v>
+        <v>1211.9747537646</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>1219.25264530946</v>
+        <v>1219.25264530937</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>1219.25264530946</v>
+        <v>1219.25264530937</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>1221.28448651603</v>
+        <v>1221.284486516</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>1221.28448651603</v>
+        <v>1221.284486516</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>-0.0108661909489647</v>
+        <v>-0.0108661909489315</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>0.0577486856422602</v>
+        <v>0.057748685642254</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>-0.0108073671524227</v>
+        <v>-0.0108073671523899</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>0.997400492664322</v>
+        <v>0.997400492664333</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>1.06857742584766</v>
+        <v>1.06857685267248</v>
       </c>
     </row>
     <row r="21">
@@ -2772,46 +2772,46 @@
         <v>1199.93660347662</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1.01354166791924</v>
+        <v>1.01354166791907</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>1193.01539789214</v>
+        <v>1193.01539789224</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>1143.67847882331</v>
+        <v>1143.67914605707</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1215.37558490565</v>
+        <v>1215.37558495534</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>1183.90456106264</v>
+        <v>1183.90456106284</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>1183.90456106264</v>
+        <v>1183.90456106284</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>1198.28766306215</v>
+        <v>1198.28766306223</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>1198.28766306215</v>
+        <v>1198.28766306223</v>
       </c>
       <c r="O21" s="15" t="n">
-        <v>-0.0190095723924504</v>
+        <v>-0.0190095723923662</v>
       </c>
       <c r="P21" s="16" t="n">
-        <v>0.00501365650727625</v>
+        <v>0.00501365650732621</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>-0.0188300299461607</v>
+        <v>-0.0188300299460781</v>
       </c>
       <c r="R21" s="18" t="n">
-        <v>1.00441927671623</v>
+        <v>1.00441927671621</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.04774872068506</v>
+        <v>1.04774810941812</v>
       </c>
     </row>
     <row r="22">
@@ -2831,46 +2831,46 @@
         <v>1395.88556343368</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1.15736541560874</v>
+        <v>1.15736541560875</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1201.26749695839</v>
+        <v>1201.26749695841</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>1142.73667262626</v>
+        <v>1142.73738934871</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>1215.99849664116</v>
+        <v>1215.99849679228</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>1206.08888481386</v>
+        <v>1206.08888481385</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>1206.08888481386</v>
+        <v>1206.08888481385</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>1201.80301744872</v>
+        <v>1201.80301744873</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>1201.80301744872</v>
+        <v>1201.80301744873</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>0.00292935340228323</v>
+        <v>0.00292935340222854</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>-0.0114505847860985</v>
+        <v>-0.0114505847860947</v>
       </c>
       <c r="Q22" s="17" t="n">
-        <v>0.00293364815054886</v>
+        <v>0.00293364815049402</v>
       </c>
       <c r="R22" s="18" t="n">
         <v>1.00044579620416</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>1.05168850027952</v>
+        <v>1.05168784066275</v>
       </c>
     </row>
     <row r="23">
@@ -2890,46 +2890,46 @@
         <v>1087.93885305562</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.89828431911846</v>
+        <v>0.898284319118567</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>1208.18083055082</v>
+        <v>1208.18083055065</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>1140.24689308558</v>
+        <v>1140.24765215349</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>1213.79473169184</v>
+        <v>1213.79473197783</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>1211.12973910451</v>
+        <v>1211.12973910437</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>1211.12973910451</v>
+        <v>1211.12973910437</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>1204.59058007312</v>
+        <v>1204.59058007301</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>1204.59058007312</v>
+        <v>1204.59058007301</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>0.0023167979453862</v>
+        <v>0.00231679794528784</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>-0.0243287779695559</v>
+        <v>-0.024328777969591</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>0.00231948379553626</v>
+        <v>0.00231948379543767</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>0.997028383179972</v>
+        <v>0.997028383180021</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>1.05642960956765</v>
+        <v>1.05642890629768</v>
       </c>
     </row>
     <row r="24">
@@ -2949,46 +2949,46 @@
         <v>1106.16144137784</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.929536527383139</v>
+        <v>0.929536527383249</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>1186.16846425595</v>
+        <v>1186.16846425605</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>1136.41417196853</v>
+        <v>1136.4149633475</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>1208.66598469637</v>
+        <v>1208.6659851545</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>1190.01395726959</v>
+        <v>1190.01395726945</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>1190.01395726959</v>
+        <v>1190.01395726945</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>1195.96405946775</v>
+        <v>1195.9640594676</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>1195.96405946775</v>
+        <v>1195.9640594676</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>-0.00718713716970424</v>
+        <v>-0.00718713716973746</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>-0.0207326198996569</v>
+        <v>-0.0207326198997569</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>-0.00716137146353013</v>
+        <v>-0.0071613714635631</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>1.00825818212756</v>
+        <v>1.00825818212735</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>1.05240157063165</v>
+        <v>1.05240083775797</v>
       </c>
     </row>
     <row r="25">
@@ -3008,46 +3008,46 @@
         <v>1128.71717192684</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1.0247140344723</v>
+        <v>1.02471403447194</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>1192.6985842273</v>
+        <v>1192.69858422713</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>1131.48784282116</v>
+        <v>1131.48865311116</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>1200.5006253305</v>
+        <v>1200.50062600045</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>1101.49479167434</v>
+        <v>1101.49479167473</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>1192.6985842273</v>
+        <v>1192.69858422713</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>1205.78556989278</v>
+        <v>1205.78556989246</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>1205.78556989278</v>
+        <v>1205.78556989246</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>0.00817867528924469</v>
+        <v>0.0081786752891055</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>0.00625718436544953</v>
+        <v>0.00625718436512179</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>0.0082122120203183</v>
+        <v>0.00821221202017797</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>1.01097258422081</v>
+        <v>1.01097258422069</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>1.0656637431352</v>
+        <v>1.06566297998394</v>
       </c>
     </row>
     <row r="26">
@@ -3067,46 +3067,46 @@
         <v>1427.26522921678</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1.14252300854203</v>
+        <v>1.14252300854221</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>0.933234916956807</v>
+        <v>0.933234916931458</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>1226.88797227137</v>
+        <v>1226.88797227076</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>1125.75073905533</v>
+        <v>1125.75155099611</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>1189.09376313284</v>
+        <v>1189.0937640544</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>1249.22230759984</v>
+        <v>1249.22230759964</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>1247.73115384692</v>
+        <v>1247.73115384613</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>1230.67449553744</v>
+        <v>1230.67449553696</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>1230.67449553744</v>
+        <v>1230.67449553696</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>0.0204311096859823</v>
+        <v>0.0204311096858622</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>0.024023469461748</v>
+        <v>0.0240234694613477</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>0.0206412535247651</v>
+        <v>0.0206412535246425</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>1.00308628281607</v>
+        <v>1.00308628281619</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>1.09320336451225</v>
+        <v>1.09320257604621</v>
       </c>
     </row>
     <row r="27">
@@ -3126,46 +3126,46 @@
         <v>1111.28111175113</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.900160165739003</v>
+        <v>0.900160165739104</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>1243.43392363155</v>
+        <v>1243.43392363094</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>1119.52395079627</v>
+        <v>1119.52474276092</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>1174.20149743649</v>
+        <v>1174.2014986462</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>1234.53709022861</v>
+        <v>1234.53709022847</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>1234.53709022861</v>
+        <v>1234.53709022847</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>1236.72429918105</v>
+        <v>1236.72429918071</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>1236.72429918105</v>
+        <v>1236.72429918071</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>0.00490380053681951</v>
+        <v>0.00490380053692535</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>0.0266760504685191</v>
+        <v>0.0266760504683272</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.00491584384461774</v>
+        <v>0.0049158438447241</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>0.994603955768794</v>
+        <v>0.994603955769006</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>1.10468766505748</v>
+        <v>1.10468688358844</v>
       </c>
     </row>
     <row r="28">
@@ -3185,46 +3185,46 @@
         <v>1143.39024827993</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.929516146892019</v>
+        <v>0.929516146892252</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>1217.85697809378</v>
+        <v>1217.85697809373</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>1113.20480592845</v>
+        <v>1113.20555141593</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>1155.87311452812</v>
+        <v>1155.87311605468</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>1230.09186242007</v>
+        <v>1230.09186241977</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>1230.09186242007</v>
+        <v>1230.09186241977</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>1224.47948183801</v>
+        <v>1224.47948183791</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>1224.47948183801</v>
+        <v>1224.47948183791</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>-0.00995034906633318</v>
+        <v>-0.0099503490661337</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>0.0238430428945773</v>
+        <v>0.0238430428946241</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>-0.00990100813184647</v>
+        <v>-0.00990100813164896</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>1.00543783372215</v>
+        <v>1.00543783372211</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>1.09995885331878</v>
+        <v>1.09995811670221</v>
       </c>
     </row>
     <row r="29">
@@ -3244,46 +3244,46 @@
         <v>1253.57935444932</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>1.04187363953229</v>
+        <v>1.04187363953197</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>1235.27197745011</v>
+        <v>1235.27197745032</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>1107.2625155485</v>
+        <v>1107.26318268867</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>1134.45957865835</v>
+        <v>1134.45958051657</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>1203.19711228328</v>
+        <v>1203.19711228365</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>1203.19711228328</v>
+        <v>1203.19711228365</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>1231.80552991619</v>
+        <v>1231.80552991643</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>1231.80552991619</v>
+        <v>1231.80552991643</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>0.00596516264747267</v>
+        <v>0.00596516264775057</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>0.0215792597565467</v>
+        <v>0.0215792597570197</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>0.00598298965955935</v>
+        <v>0.0059829896598389</v>
       </c>
       <c r="R29" s="18" t="n">
-        <v>0.99719377789086</v>
+        <v>0.997193777890889</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>1.1124783080966</v>
+        <v>1.11247763781447</v>
       </c>
     </row>
     <row r="30">
@@ -3303,46 +3303,46 @@
         <v>1449.81126794023</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1.12324381688799</v>
+        <v>1.12324381688751</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>1256.17646698602</v>
+        <v>1256.17646698708</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>1102.23934516335</v>
+        <v>1102.23989625106</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1110.68294781728</v>
+        <v>1110.68295000041</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>1290.73603267812</v>
+        <v>1290.73603267867</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>1290.73603267812</v>
+        <v>1290.73603267867</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>1244.35796950558</v>
+        <v>1244.35796950621</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>1244.35796950558</v>
+        <v>1244.35796950621</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>0.010138706202367</v>
+        <v>0.010138706202673</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>0.0111186784302111</v>
+        <v>0.0111186784311101</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>0.0101902770238786</v>
+        <v>0.0101902770241877</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>0.990591690108002</v>
+        <v>0.990591690107666</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>1.12893626503703</v>
+        <v>1.1289357006025</v>
       </c>
     </row>
     <row r="31">
@@ -3362,46 +3362,46 @@
         <v>1073.94141993997</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.90038145860472</v>
+        <v>0.900381458603933</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>1201.36291431613</v>
+        <v>1201.36291431589</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>1098.7375194029</v>
+        <v>1098.73791048097</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>1085.60896766311</v>
+        <v>1085.60897013361</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>1192.7627003828</v>
+        <v>1192.76270038384</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>1192.7627003828</v>
+        <v>1192.76270038384</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>1189.06524911837</v>
+        <v>1189.06524911799</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>1189.06524911837</v>
+        <v>1189.06524911799</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>-0.0454522162499804</v>
+        <v>-0.0454522162508088</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>-0.0385365194928589</v>
+        <v>-0.038536519492902</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>-0.0444347380273374</v>
+        <v>-0.044434738028129</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>0.989763571813967</v>
+        <v>0.989763571813845</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>1.08221047167349</v>
+        <v>1.08221008647774</v>
       </c>
     </row>
     <row r="32">
@@ -3421,46 +3421,46 @@
         <v>1006.17899473794</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.931647594296492</v>
+        <v>0.931647594300093</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>1092.52573848053</v>
+        <v>1092.52573847687</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>1097.47707332672</v>
+        <v>1097.47725384158</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>1061.20364927836</v>
+        <v>1061.20365195693</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>1079.99956302976</v>
+        <v>1079.99956302559</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>1079.99956302976</v>
+        <v>1079.99956302559</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>1089.09872865313</v>
+        <v>1089.09872865009</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>1089.09872865313</v>
+        <v>1089.09872865009</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>-0.0878169937485426</v>
+        <v>-0.0878169937510056</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>-0.110561879715344</v>
+        <v>-0.110561879717752</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>-0.0840715179754528</v>
+        <v>-0.0840715179777086</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>0.996863222799522</v>
+        <v>0.996863222800084</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>0.992365813485111</v>
+        <v>0.99236565025639</v>
       </c>
     </row>
     <row r="33">
@@ -3480,46 +3480,46 @@
         <v>1097.12674299929</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>1.05926121942526</v>
+        <v>1.0592612194256</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>0.402706876665518</v>
+        <v>0.402706876595951</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>981.981179759969</v>
+        <v>981.981179758366</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>1099.23680773252</v>
+        <v>1099.23672028974</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>1039.96877240915</v>
+        <v>1039.96877516241</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>1035.7471064546</v>
+        <v>1035.74710645427</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>1003.63308817019</v>
+        <v>1003.63308816536</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>984.819445898267</v>
+        <v>984.819445896608</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>984.819445898267</v>
+        <v>984.819445896608</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>-0.100647458030487</v>
+        <v>-0.100647458029386</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>-0.200507367453307</v>
+        <v>-0.200507367454813</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>-0.0957482366027748</v>
+        <v>-0.095748236601779</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>1.00289034677731</v>
+        <v>1.00289034677726</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.895911999098472</v>
+        <v>0.895912070365544</v>
       </c>
     </row>
     <row r="34">
@@ -3539,46 +3539,46 @@
         <v>925.043759968322</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1.10386259851174</v>
+        <v>1.10386259850482</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>0.596425102269621</v>
+        <v>0.596425102218408</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>872.710570146253</v>
+        <v>872.710570151928</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>1104.78459997407</v>
+        <v>1104.78418022554</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1024.50009637035</v>
+        <v>1024.50009899743</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>838.006252966169</v>
+        <v>838.006252971422</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>852.012044222924</v>
+        <v>852.012044230125</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>885.474395049009</v>
+        <v>885.474395052341</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>885.474395049009</v>
+        <v>885.474395052341</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>-0.106334779719917</v>
+        <v>-0.106334779714469</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>-0.288408627783503</v>
+        <v>-0.288408627781185</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>-0.100876410658854</v>
+        <v>-0.100876410653956</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>1.01462549594262</v>
+        <v>1.01462549593984</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.801490530434433</v>
+        <v>0.801490834953462</v>
       </c>
     </row>
     <row r="35">
@@ -3598,46 +3598,46 @@
         <v>751.640121231456</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.900987434804073</v>
+        <v>0.900987434800015</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>841.773184953336</v>
+        <v>841.773184952378</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1114.82857508039</v>
+        <v>1114.827751779</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>1017.21170205565</v>
+        <v>1017.21170427437</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>834.240403579996</v>
+        <v>834.240403583754</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>834.240403579996</v>
+        <v>834.240403583754</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>855.495684594114</v>
+        <v>855.495684592805</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>855.495684594114</v>
+        <v>855.495684592805</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>-0.0344424919823548</v>
+        <v>-0.0344424919876476</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.280530916845463</v>
+        <v>-0.280530916846332</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>-0.033856100890682</v>
+        <v>-0.0338561008957957</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>1.01630189686018</v>
+        <v>1.01630189685979</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.767378683787706</v>
+        <v>0.767379250496444</v>
       </c>
     </row>
     <row r="36">
@@ -3657,46 +3657,46 @@
         <v>839.434712132987</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.931163759287965</v>
+        <v>0.931163759308572</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>883.713693480859</v>
+        <v>883.713693465474</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>1129.91887523318</v>
+        <v>1129.91757049514</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1019.65523009797</v>
+        <v>1019.65523153179</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>901.489886993539</v>
+        <v>901.489886973589</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>901.489886993539</v>
+        <v>901.489886973589</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>886.168604032376</v>
+        <v>886.168604021672</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>886.168604032376</v>
+        <v>886.168604021672</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>0.0352261814945845</v>
+        <v>0.0352261814840344</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>-0.186328492800384</v>
+        <v>-0.186328492807946</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>0.03585397330533</v>
+        <v>0.0358539732944017</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>1.00277794784626</v>
+        <v>1.00277794785161</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>0.784276308199115</v>
+        <v>0.784277213808919</v>
       </c>
     </row>
     <row r="37">
@@ -3716,46 +3716,46 @@
         <v>979.295252197054</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>1.07916764348187</v>
+        <v>1.07916764348981</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>907.52982370898</v>
+        <v>907.529823709802</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>1150.43027500696</v>
+        <v>1150.42840482636</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1032.46746463788</v>
+        <v>1032.46746480479</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>907.454238562431</v>
+        <v>907.454238555755</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>907.454238562431</v>
+        <v>907.454238555755</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>915.610061324423</v>
+        <v>915.610061325828</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>915.610061324423</v>
+        <v>915.610061325828</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>0.0326833462896037</v>
+        <v>0.0326833463032188</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>-0.0702762164801872</v>
+        <v>-0.0702762164771935</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>0.033223313439539</v>
+        <v>0.0332233134536064</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>1.00890355049977</v>
+        <v>1.00890355050041</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>0.795884879958402</v>
+        <v>0.795886173780653</v>
       </c>
     </row>
     <row r="38">
@@ -3775,46 +3775,46 @@
         <v>1025.67860484186</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1.0841788563983</v>
+        <v>1.08417885635369</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>970.103942588299</v>
+        <v>970.103942617978</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>1176.59478085856</v>
+        <v>1176.59225592284</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>1055.69436310042</v>
+        <v>1055.69436140569</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>946.041881179289</v>
+        <v>946.041881218215</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>946.041881179289</v>
+        <v>946.041881218215</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>977.417460236894</v>
+        <v>977.417460257216</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>977.417460236894</v>
+        <v>977.417460257216</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>0.065323271843685</v>
+        <v>0.0653232718629414</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>0.103834809568712</v>
+        <v>0.103834809587509</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>0.0675040626170784</v>
+        <v>0.0675040626376346</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>1.00753890106774</v>
+        <v>1.00753890105786</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>0.83071714760087</v>
+        <v>0.830718930315067</v>
       </c>
     </row>
     <row r="39">
@@ -3834,46 +3834,46 @@
         <v>1000.69836644118</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.901422993522309</v>
+        <v>0.901422993514098</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>1081.07321788967</v>
+        <v>1081.07321789027</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>1208.49253922207</v>
+        <v>1208.48926608088</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1088.75681678026</v>
+        <v>1088.75681251553</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>1110.13184002656</v>
+        <v>1110.13184003668</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>1110.13184002656</v>
+        <v>1110.13184003668</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>1082.80158534435</v>
+        <v>1082.80158534066</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>1082.80158534435</v>
+        <v>1082.80158534066</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>0.102393173215709</v>
+        <v>0.102393173191516</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.265700815145637</v>
+        <v>0.265700815143268</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>0.10781895085229</v>
+        <v>0.107818950825488</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>1.00159875152402</v>
+        <v>1.00159875152005</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>0.895993603768018</v>
+        <v>0.895996030525103</v>
       </c>
     </row>
     <row r="40">
@@ -3893,46 +3893,46 @@
         <v>1086.52423367125</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.932718264242253</v>
+        <v>0.93271826430141</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>1189.56260180146</v>
+        <v>1189.5626017281</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>1246.05960096927</v>
+        <v>1246.05548361255</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>1130.52745456245</v>
+        <v>1130.52744691446</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>1164.90078014496</v>
+        <v>1164.90078007108</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>1164.90078014496</v>
+        <v>1164.90078007108</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>1177.80238137948</v>
+        <v>1177.80238132901</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>1177.80238137948</v>
+        <v>1177.80238132901</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>0.084098570541603</v>
+        <v>0.0840985705021562</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>0.329095136094948</v>
+        <v>0.329095136054054</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>0.0877361072619092</v>
+        <v>0.0877361072190015</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>0.990113828053968</v>
+        <v>0.990113828072604</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>0.945221545151856</v>
+        <v>0.945224668418735</v>
       </c>
     </row>
     <row r="41">
@@ -3952,46 +3952,46 @@
         <v>1387.01112527143</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1.09103844379336</v>
+        <v>1.09103844384847</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>1246.60401004189</v>
+        <v>1246.60401004007</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>1289.17054153494</v>
+        <v>1289.16548343866</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>1179.98578044828</v>
+        <v>1179.98576852019</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>1271.27612520144</v>
+        <v>1271.27612513723</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>1271.27612520144</v>
+        <v>1271.27612513723</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>1240.44195147463</v>
+        <v>1240.44195146927</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>1240.44195147463</v>
+        <v>1240.44195146927</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>0.0518174151825267</v>
+        <v>0.0518174152210539</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.354770992446649</v>
+        <v>0.354770992438715</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>0.0531834296529257</v>
+        <v>0.0531834296935019</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>0.995056923836578</v>
+        <v>0.995056923833731</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>0.962201595141711</v>
+        <v>0.962205370376944</v>
       </c>
     </row>
     <row r="42">
@@ -4011,46 +4011,46 @@
         <v>1344.70366909301</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1.07206236864832</v>
+        <v>1.07206236849373</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>1265.64713671646</v>
+        <v>1265.64713679668</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>1337.64921209084</v>
+        <v>1337.6431187903</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>1236.28316506695</v>
+        <v>1236.28314791626</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>1254.31477535066</v>
+        <v>1254.31477553153</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>1254.31477535066</v>
+        <v>1254.31477553153</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>1263.74750446761</v>
+        <v>1263.74750453036</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>1263.74750446761</v>
+        <v>1263.74750453036</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>0.0186137880497854</v>
+        <v>0.0186137881037608</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0.292945497578198</v>
+        <v>0.292945497615516</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>0.0187881044858875</v>
+        <v>0.0187881045408771</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>0.998499082253069</v>
+        <v>0.998499082239361</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>0.94475255025365</v>
+        <v>0.944756853885832</v>
       </c>
     </row>
     <row r="43">
@@ -4070,46 +4070,46 @@
         <v>1151.18082419785</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.902827198412127</v>
+        <v>0.90282719844507</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>1278.88937793292</v>
+        <v>1278.88937794833</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>1391.30827979853</v>
+        <v>1391.30106204964</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>1299.02743077143</v>
+        <v>1299.02740746925</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>1275.08434196768</v>
+        <v>1275.08434192115</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>1275.08434196768</v>
+        <v>1275.08434192115</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>1286.19998165909</v>
+        <v>1286.19998166019</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>1286.19998165909</v>
+        <v>1286.19998166019</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>0.0176106038124353</v>
+        <v>0.0176106037636303</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.187844568264152</v>
+        <v>0.187844568269202</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>0.0177665847901656</v>
+        <v>0.0177665847404935</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>1.005716369103</v>
+        <v>1.00571636909174</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>0.924453624214283</v>
+        <v>0.924458420067171</v>
       </c>
     </row>
     <row r="44">
@@ -4129,46 +4129,46 @@
         <v>1247.82293557512</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.930991274054785</v>
+        <v>0.930991274112749</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>1332.79147643215</v>
+        <v>1332.7914763159</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>1449.9083277966</v>
+        <v>1449.89990538428</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>1367.9165579661</v>
+        <v>1367.91652768384</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>1340.31646735036</v>
+        <v>1340.31646726691</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>1340.31646735036</v>
+        <v>1340.31646726691</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>1340.15977611552</v>
+        <v>1340.15977603456</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>1340.15977611552</v>
+        <v>1340.15977603456</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>0.0410967223030267</v>
+        <v>0.041096722241766</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.137847738553458</v>
+        <v>0.137847738533474</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>0.0419528807540677</v>
+        <v>0.0419528806902369</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>1.00552847149285</v>
+        <v>1.00552847151981</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>0.924306558161601</v>
+        <v>0.924311927366711</v>
       </c>
     </row>
     <row r="45">
@@ -4188,46 +4188,46 @@
         <v>1544.43982105477</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>1.09930658809692</v>
+        <v>1.09930658818332</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>1414.47952439662</v>
+        <v>1414.47952432983</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>1513.13729926251</v>
+        <v>1513.12760551179</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>1442.52881161133</v>
+        <v>1442.52877373698</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>1404.92182779369</v>
+        <v>1404.92182768327</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>1404.92182779369</v>
+        <v>1404.92182768327</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>1419.11360804459</v>
+        <v>1419.11360800321</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>1419.11360804459</v>
+        <v>1419.11360800321</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>0.0572436142581482</v>
+        <v>0.0572436142893991</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.144038708427718</v>
+        <v>0.144038708399301</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>0.0589137454624382</v>
+        <v>0.0589137454955302</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>1.0032761758428</v>
+        <v>1.00327617586092</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>0.937861758305909</v>
+        <v>0.937867766627137</v>
       </c>
     </row>
     <row r="46">
@@ -4247,46 +4247,46 @@
         <v>1628.14312336858</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1.06672947249514</v>
+        <v>1.06672947239816</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>1523.12820100023</v>
+        <v>1523.12820120016</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>1580.61464246091</v>
+        <v>1580.60362950085</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>1522.30445621441</v>
+        <v>1522.30441050352</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>1526.29430924062</v>
+        <v>1526.29430937938</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>1526.29430924062</v>
+        <v>1526.29430937938</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>1522.29287968633</v>
+        <v>1522.29287981214</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>1522.29287968633</v>
+        <v>1522.29287981214</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0.070185214712759</v>
+        <v>0.0701852148245667</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0.204586259758938</v>
+        <v>0.204586259798681</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>0.0727068439459979</v>
+        <v>0.0727068440659349</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>0.999451575177091</v>
+        <v>0.999451575128502</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>0.96310184582133</v>
+        <v>0.963108556376576</v>
       </c>
     </row>
     <row r="47">
@@ -4306,46 +4306,46 @@
         <v>1470.67718086851</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.901337419689653</v>
+        <v>0.901337419503962</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>1623.94071432103</v>
+        <v>1623.94071432043</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>1651.89217098684</v>
+        <v>1651.87981580907</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>1606.49572136354</v>
+        <v>1606.49566812803</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>1631.66107247039</v>
+        <v>1631.66107280654</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>1631.66107247039</v>
+        <v>1631.66107280654</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>1620.24627783415</v>
+        <v>1620.24627786711</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>1620.24627783415</v>
+        <v>1620.24627786711</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>0.0623604893115308</v>
+        <v>0.0623604892492243</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>0.259715674808334</v>
+        <v>0.259715674832887</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>0.0643459609217938</v>
+        <v>0.0643459608554782</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>0.997725017635004</v>
+        <v>0.997725017655667</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>0.980842639908038</v>
+        <v>0.980849976106484</v>
       </c>
     </row>
     <row r="48">
@@ -4365,46 +4365,46 @@
         <v>1577.11367430347</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.932448208515398</v>
+        <v>0.932448208889858</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>1702.59001324888</v>
+        <v>1702.59001311088</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>1726.48774822701</v>
+        <v>1726.47405956893</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>1694.37478591205</v>
+        <v>1694.37472624948</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>1691.3686571552</v>
+        <v>1691.36865647597</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>1691.3686571552</v>
+        <v>1691.36865647597</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>1698.82647875509</v>
+        <v>1698.82647862896</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>1698.82647875509</v>
+        <v>1698.82647862896</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>0.0473595450318714</v>
+        <v>0.0473595449372871</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>0.267629807304894</v>
+        <v>0.26762980728736</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>0.0484989238956797</v>
+        <v>0.0484989237965081</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>0.997789523922667</v>
+        <v>0.997789523929462</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>0.983978299585194</v>
+        <v>0.983986101159915</v>
       </c>
     </row>
     <row r="49">
@@ -4424,46 +4424,46 @@
         <v>1958.50082068495</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1.09972067029272</v>
+        <v>1.09972066997297</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>1769.14027918263</v>
+        <v>1769.14027929936</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>1803.90659313161</v>
+        <v>1803.89161919855</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>1785.3396554688</v>
+        <v>1785.33959153023</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>1780.90752823955</v>
+        <v>1780.90752875736</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>1780.90752823955</v>
+        <v>1780.90752875736</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>1769.03192032806</v>
+        <v>1769.03192041248</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>1769.03192032806</v>
+        <v>1769.03192041248</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>0.0404947532168095</v>
+        <v>0.0404947533387762</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.246575263812476</v>
+        <v>0.246575263908317</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>0.0413258460772392</v>
+        <v>0.0413258462042463</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>0.999938750558197</v>
+        <v>0.99993875053994</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>0.980667140451543</v>
+        <v>0.980675280923166</v>
       </c>
     </row>
     <row r="50">
@@ -4483,46 +4483,46 @@
         <v>1945.13754028478</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1.06703089879526</v>
+        <v>1.0670308988062</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>1826.98871220342</v>
+        <v>1826.98871211719</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>1883.63197521886</v>
+        <v>1883.61581223912</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>1878.77330499888</v>
+        <v>1878.77324028376</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>1822.94396767793</v>
+        <v>1822.94396765924</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>1822.94396767793</v>
+        <v>1822.94396765924</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>1831.79961156794</v>
+        <v>1831.79961149492</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>1831.79961156794</v>
+        <v>1831.79961149492</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>0.0348664186443345</v>
+        <v>0.0348664185567485</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>0.203316152897846</v>
+        <v>0.203316152750428</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>0.0354813785543444</v>
+        <v>0.0354813784636507</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>1.00263323978544</v>
+        <v>1.00263323979279</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>0.972482754416555</v>
+        <v>0.972491099083203</v>
       </c>
     </row>
     <row r="51">
@@ -4542,46 +4542,46 @@
         <v>1712.91881357271</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0.901345045859905</v>
+        <v>0.9013450462263</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>1910.54382485871</v>
+        <v>1910.54382473005</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>1965.13278959148</v>
+        <v>1965.11559117529</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>1974.03654883122</v>
+        <v>1974.03648850969</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>1900.40298267634</v>
+        <v>1900.40298190383</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>1900.40298267634</v>
+        <v>1900.40298190383</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>1916.21848629299</v>
+        <v>1916.21848607515</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>1916.21848629299</v>
+        <v>1916.21848607515</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>0.0450548276221128</v>
+        <v>0.0450548275482921</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>0.182671123833396</v>
+        <v>0.182671123674889</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>0.0460852127011837</v>
+        <v>0.046085212623961</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>1.00297018124392</v>
+        <v>1.00297018119744</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>0.97510890685985</v>
+        <v>0.975117440765456</v>
       </c>
     </row>
     <row r="52">
@@ -4601,46 +4601,46 @@
         <v>1898.85436922996</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.930298383603775</v>
+        <v>0.930298383288222</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>2021.33452898574</v>
+        <v>2021.33452849083</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>2047.84000134742</v>
+        <v>2047.82198858888</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>2070.21105460816</v>
+        <v>2070.21100584454</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>2041.12401214136</v>
+        <v>2041.1240128337</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>2041.12401214136</v>
+        <v>2041.1240128337</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>2029.37222233992</v>
+        <v>2029.37222200378</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>2029.37222233992</v>
+        <v>2029.37222200378</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>0.057372789587717</v>
+        <v>0.0573727895357632</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>0.194572987717415</v>
+        <v>0.194572987608239</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>0.0590505398295318</v>
+        <v>0.05905053977451</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>1.00397642905661</v>
+        <v>1.00397642913613</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.990981825242526</v>
+        <v>0.990990541810808</v>
       </c>
     </row>
     <row r="53">
@@ -4660,46 +4660,46 @@
         <v>2354.10436983294</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1.10270872989463</v>
+        <v>1.10270873090534</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>2166.58784114105</v>
+        <v>2166.5878408308</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>2131.14411945535</v>
+        <v>2131.12559168089</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>2166.01032214123</v>
+        <v>2166.01029439176</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>2134.83788240063</v>
+        <v>2134.8378804439</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>2134.83788240063</v>
+        <v>2134.8378804439</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>2155.07297482541</v>
+        <v>2155.07297264865</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>2155.07297482541</v>
+        <v>2155.07297264865</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>0.0600980908632322</v>
+        <v>0.060098090018804</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>0.218221644313667</v>
+        <v>0.218221643025046</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>0.0619407081173875</v>
+        <v>0.0619407072206548</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>0.994685252959985</v>
+        <v>0.994685252097724</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>1.01122817323879</v>
+        <v>1.01123696372529</v>
       </c>
     </row>
     <row r="54">
@@ -4719,46 +4719,46 @@
         <v>2600.12971883191</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>1.06458671063023</v>
+        <v>1.06458670795858</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>0.0387982204834509</v>
+        <v>0.0387981799010197</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>2304.12803057205</v>
+        <v>2304.12803045451</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>2214.43145539067</v>
+        <v>2214.41280141746</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>2260.00241602968</v>
+        <v>2260.00242128978</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>2442.38415985171</v>
+        <v>2442.38416598103</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>2309.49212235903</v>
+        <v>2309.49211687309</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>2284.91025788842</v>
+        <v>2284.91025398779</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>2284.91025788842</v>
+        <v>2284.91025398779</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>0.0585021631174207</v>
+        <v>0.0585021624203597</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>0.247358195437459</v>
+        <v>0.247358193357784</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>0.0602472791314765</v>
+        <v>0.0602472783924195</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>0.991659416304719</v>
+        <v>0.991659414662418</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>1.03182704180171</v>
+        <v>1.0318357320393</v>
       </c>
     </row>
     <row r="55">
@@ -4778,46 +4778,46 @@
         <v>2154.1851770688</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.902912275975512</v>
+        <v>0.902912276987453</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>2401.05607751034</v>
+        <v>2401.05607408335</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>2297.09062923062</v>
+        <v>2297.07233894525</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>2350.59953867401</v>
+        <v>2350.59959160727</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>2385.81890443499</v>
+        <v>2385.81890176108</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>2385.81890443499</v>
+        <v>2385.81890176108</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>2394.29727343993</v>
+        <v>2394.29726845533</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>2394.29727343993</v>
+        <v>2394.29726845533</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>0.0467630246681838</v>
+        <v>0.0467630242934475</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>0.249490749915373</v>
+        <v>0.24949074745615</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>0.0478736594463007</v>
+        <v>0.0478736590536244</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>0.997185070297309</v>
+        <v>0.997185069644573</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>1.04231728734267</v>
+        <v>1.04232558455461</v>
       </c>
     </row>
     <row r="56">
@@ -4837,46 +4837,46 @@
         <v>2321.41186175029</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.930030784765797</v>
+        <v>0.930030788158179</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>2511.24096798117</v>
+        <v>2511.24095778869</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>2378.56967396931</v>
+        <v>2378.55234998304</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>2436.46134100639</v>
+        <v>2436.46145889083</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>2496.05916253071</v>
+        <v>2496.05915342608</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>2496.05916253071</v>
+        <v>2496.05915342608</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>2517.01602946351</v>
+        <v>2517.01602331903</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>2517.01602946351</v>
+        <v>2517.01602331903</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>0.0499843108166302</v>
+        <v>0.04998431045732</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>0.240292934807848</v>
+        <v>0.240292931985517</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>0.0512546029204064</v>
+        <v>0.0512546025426799</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>1.0022996843218</v>
+        <v>1.00229968594309</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>1.05820571791919</v>
+        <v>1.05821342268837</v>
       </c>
     </row>
     <row r="57">
@@ -4896,46 +4896,46 @@
         <v>2970.00973852471</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1.10404076156347</v>
+        <v>1.1040407630798</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>2671.1154842476</v>
+        <v>2671.11549504705</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>2458.37207777282</v>
+        <v>2458.35644685139</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>2516.42357078779</v>
+        <v>2516.42377323783</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>2690.12688835761</v>
+        <v>2690.12688466289</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>2690.12688835761</v>
+        <v>2690.12688466289</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>2664.04751765615</v>
+        <v>2664.04752424559</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>2664.04751765615</v>
+        <v>2664.04752424559</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>0.0567725048644387</v>
+        <v>0.0567725097790841</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>0.236175084916541</v>
+        <v>0.236175089222803</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>0.0584149987411799</v>
+        <v>0.0584150039429143</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>0.997353926989254</v>
+        <v>0.99735392542383</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>1.08366326714452</v>
+        <v>1.08367016006066</v>
       </c>
     </row>
     <row r="58">
@@ -4955,46 +4955,46 @@
         <v>2943.99757674031</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>1.0590387407807</v>
+        <v>1.0590387244556</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>2773.86896446549</v>
+        <v>2773.86897753295</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>2536.07475973761</v>
+        <v>2536.061683623</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>2589.61996488681</v>
+        <v>2589.62027321829</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>2779.87713137865</v>
+        <v>2779.8771742305</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>2779.87713137865</v>
+        <v>2779.8771742305</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>2771.49082751269</v>
+        <v>2771.49083862357</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>2771.49082751269</v>
+        <v>2771.49083862357</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0.0395387908200955</v>
+        <v>0.0395387923556132</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>0.212953908340338</v>
+        <v>0.212953915273724</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>0.0403308533892344</v>
+        <v>0.0403308549866808</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>0.999142664277489</v>
+        <v>0.999142663576166</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>1.09282694324021</v>
+        <v>1.09283258231489</v>
       </c>
     </row>
     <row r="59">
@@ -5014,46 +5014,46 @@
         <v>2579.42813442157</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0.909504023462221</v>
+        <v>0.909504035509104</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>2887.05647042638</v>
+        <v>2887.05645864333</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>2611.39948571675</v>
+        <v>2611.38997089422</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>2656.05277675988</v>
+        <v>2656.0532129594</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>2836.08215893585</v>
+        <v>2836.08212137037</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>2836.08215893585</v>
+        <v>2836.08212137037</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2863.46681228152</v>
+        <v>2863.46680740126</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>2863.46681228152</v>
+        <v>2863.46680740126</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>0.0326476825735274</v>
+        <v>0.0326476768602206</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>0.195952918648036</v>
+        <v>0.195952919099564</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>0.033186465513716</v>
+        <v>0.0331864596108047</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>0.991829166354555</v>
+        <v>0.991829168712152</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.09652576250531</v>
+        <v>1.0965297559218</v>
       </c>
     </row>
     <row r="60">
@@ -5073,46 +5073,46 @@
         <v>2838.16101860859</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>0.926665437336485</v>
+        <v>0.926665452527764</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.531286017005079</v>
+        <v>0.531286391690894</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>2932.74826362613</v>
+        <v>2932.74824382131</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>2684.22039804558</v>
+        <v>2684.21560394301</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>2716.67554569591</v>
+        <v>2716.67613109337</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>3062.76775226053</v>
+        <v>3062.76770205108</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>3001.82579987574</v>
+        <v>3001.82581263381</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>2900.93996633742</v>
+        <v>2900.93996825396</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>2900.93996633742</v>
+        <v>2900.93996825396</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>0.0130017479273876</v>
+        <v>0.0130017502923655</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0.152531383344329</v>
+        <v>0.15253138691929</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>0.0130866381601424</v>
+        <v>0.0130866405560699</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>0.989154099012447</v>
+        <v>0.989154106345691</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.08073836576521</v>
+        <v>1.08074029671558</v>
       </c>
     </row>
     <row r="61">
@@ -5132,46 +5132,46 @@
         <v>3062.56234200586</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>1.10800774805415</v>
+        <v>1.10800774015086</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>2804.85502615529</v>
+        <v>2804.85507001401</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>2754.5520657302</v>
+        <v>2754.55331064139</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>2773.34195789467</v>
+        <v>2773.34271079448</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>2764.02610666238</v>
+        <v>2764.02612637785</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>2764.02610666238</v>
+        <v>2764.02612637785</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>2788.18415925912</v>
+        <v>2788.18419705627</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>2788.18415925912</v>
+        <v>2788.18419705627</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>-0.0396442658276678</v>
+        <v>-0.0396442529321402</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.0465970072906925</v>
+        <v>0.0465970188898306</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>-0.03886871441213</v>
+        <v>-0.0388687020178349</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>0.994056424756105</v>
+        <v>0.994056422687945</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>1.01220964161373</v>
+        <v>1.01220919787065</v>
       </c>
     </row>
     <row r="62">
@@ -5191,46 +5191,46 @@
         <v>2755.1961460775</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>1.05045545384675</v>
+        <v>1.0504554141974</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>2624.79752296184</v>
+        <v>2624.79759932966</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>2822.60756115286</v>
+        <v>2822.6163252418</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>2829.33145082684</v>
+        <v>2829.33238364472</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>2622.85862383599</v>
+        <v>2622.85872283557</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>2622.85862383599</v>
+        <v>2622.85872283557</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>2642.56176265453</v>
+        <v>2642.56180628708</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>2642.56176265453</v>
+        <v>2642.56180628708</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>-0.0536417336697503</v>
+        <v>-0.053641730714481</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>-0.0465197516002114</v>
+        <v>-0.0465197396793551</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>-0.0522283996632706</v>
+        <v>-0.0522283968623504</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>1.00676785143894</v>
+        <v>1.00676783877049</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>0.936212953945044</v>
+        <v>0.93621006250671</v>
       </c>
     </row>
     <row r="63">
@@ -5250,46 +5250,46 @@
         <v>2346.01620451565</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0.916232305354833</v>
+        <v>0.916232320807643</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>2533.47971696673</v>
+        <v>2533.47959554577</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>2888.60587797139</v>
+        <v>2888.62380250652</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>2887.87688270695</v>
+        <v>2887.87799830399</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>2560.50369628377</v>
+        <v>2560.50365309934</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>2560.50369628377</v>
+        <v>2560.50365309934</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>2566.5579748969</v>
+        <v>2566.55789435482</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>2566.5579748969</v>
+        <v>2566.55789435482</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>-0.0291831194485888</v>
+        <v>-0.029183167341406</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>-0.103688590386719</v>
+        <v>-0.103688616986591</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>-0.0287614044945883</v>
+        <v>-0.0287614510099397</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>1.01305645263652</v>
+        <v>1.01305646939774</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>0.888510957645539</v>
+        <v>0.888505416360469</v>
       </c>
     </row>
     <row r="64">
@@ -5309,46 +5309,46 @@
         <v>2313.68685692728</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>0.927837006402059</v>
+        <v>0.927837099084918</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>0.658289879807384</v>
+        <v>0.658291170729635</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>2577.71464773665</v>
+        <v>2577.7144654663</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>2952.64116675781</v>
+        <v>2952.67004869635</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>2951.17874761456</v>
+        <v>2951.18003512815</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>2493.63502529311</v>
+        <v>2493.63477620065</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>2522.36588318404</v>
+        <v>2522.36554838503</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>2607.63739328193</v>
+        <v>2607.63726807194</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>2607.63739328193</v>
+        <v>2607.63726807194</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>0.0158789062275997</v>
+        <v>0.0158788895923189</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>-0.101106047163674</v>
+        <v>-0.101106090919404</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>0.0160056460001381</v>
+        <v>0.016005629098599</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>1.01160824592107</v>
+        <v>1.01160826887792</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>0.883154181632333</v>
+        <v>0.883145500535442</v>
       </c>
     </row>
     <row r="65">
@@ -5368,46 +5368,46 @@
         <v>3129.72211611434</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.10774306634076</v>
+        <v>1.1077429832428</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>2789.05104443279</v>
+        <v>2789.05113281841</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>3014.60251422055</v>
+        <v>3014.64429497867</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>3019.8006736971</v>
+        <v>3019.80210274702</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>2825.31411047585</v>
+        <v>2825.31432241837</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>2825.31411047585</v>
+        <v>2825.31432241837</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>2802.9837277893</v>
+        <v>2802.98380563048</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>2802.9837277893</v>
+        <v>2802.98380563048</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>0.0722398688022427</v>
+        <v>0.0722399445897131</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>0.00530795947643159</v>
+        <v>0.00530797376652381</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>0.074913151272735</v>
+        <v>0.0749132327376867</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>1.00499549242181</v>
+        <v>1.00499548848285</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>0.929802093167174</v>
+        <v>0.929789232613367</v>
       </c>
     </row>
     <row r="66">
@@ -5427,46 +5427,46 @@
         <v>3164.98577161261</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>1.04147661063353</v>
+        <v>1.04147653445631</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>3058.61954194895</v>
+        <v>3058.61978728294</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>3074.11008501585</v>
+        <v>3074.1668322082</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>3092.16222477988</v>
+        <v>3092.16373735672</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>3038.94080702144</v>
+        <v>3038.94102930015</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>3038.94080702144</v>
+        <v>3038.94102930015</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>3033.33151376016</v>
+        <v>3033.33164148955</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>3033.33151376016</v>
+        <v>3033.33164148955</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>0.0789770581133029</v>
+        <v>0.0789770724510876</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>0.147875352102683</v>
+        <v>0.147875381485029</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>0.0821794945461709</v>
+        <v>0.0821795100622276</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>0.991732208651007</v>
+        <v>0.991732170863953</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.986734837033177</v>
+        <v>0.986716664075999</v>
       </c>
     </row>
     <row r="67">
@@ -5486,46 +5486,46 @@
         <v>2987.75245463425</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>0.924963437667698</v>
+        <v>0.924963479355918</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>3186.01437251162</v>
+        <v>3186.01395678804</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>3130.66573854758</v>
+        <v>3130.73962000678</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>3165.71053187209</v>
+        <v>3165.71203625171</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>3230.13033052192</v>
+        <v>3230.13018493954</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>3230.13033052192</v>
+        <v>3230.13018493954</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>3174.02675057168</v>
+        <v>3174.02648085416</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>3174.02675057168</v>
+        <v>3174.02648085416</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>0.0453395251048791</v>
+        <v>0.0453393980198141</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>0.236686169420812</v>
+        <v>0.236686103140507</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>0.0463830729260151</v>
+        <v>0.0463829399463627</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>0.996237423772043</v>
+        <v>0.996237469108277</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>1.01385041254651</v>
+        <v>1.0138264008194</v>
       </c>
     </row>
     <row r="68">
@@ -5545,46 +5545,46 @@
         <v>2968.07680589468</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>0.928421804811794</v>
+        <v>0.928422098124019</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>3244.08404039134</v>
+        <v>3244.08377128764</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>3183.74935342088</v>
+        <v>3183.84260186946</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>3237.62661889411</v>
+        <v>3237.62798318621</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>3196.90553422144</v>
+        <v>3196.90452423743</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>3196.90553422144</v>
+        <v>3196.90452423743</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>3240.51200080778</v>
+        <v>3240.51175686929</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>3240.51200080778</v>
+        <v>3240.51175686929</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.0207302921601798</v>
+        <v>0.0207303018588646</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>0.242700388158391</v>
+        <v>0.24270035428098</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.0209466571836958</v>
+        <v>0.0209466670855356</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>0.998898906582234</v>
+        <v>0.998898914248157</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>1.01782886813182</v>
+        <v>1.01779898132105</v>
       </c>
     </row>
     <row r="69">
@@ -5604,46 +5604,46 @@
         <v>3696.32832846722</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1.10731284727188</v>
+        <v>1.10731245259413</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>3306.91265515426</v>
+        <v>3306.91303370372</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>3232.90297361086</v>
+        <v>3233.01784039435</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>3305.41360875961</v>
+        <v>3305.41465265782</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>3338.10660426634</v>
+        <v>3338.10779406277</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>3338.10660426634</v>
+        <v>3338.10779406277</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>3320.79153685842</v>
+        <v>3320.79186035994</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>3320.79153685842</v>
+        <v>3320.79186035994</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>0.0244718269682295</v>
+        <v>0.0244719996629828</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>0.18473450414124</v>
+        <v>0.18473458665345</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>0.0247737197179401</v>
+        <v>0.0247738966910001</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>1.00419693023416</v>
+        <v>1.00419691310741</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>1.02718564830586</v>
+        <v>1.02714925320514</v>
       </c>
     </row>
     <row r="70">
@@ -5663,46 +5663,46 @@
         <v>3523.50222767909</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>1.03327074657198</v>
+        <v>1.0332707694802</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>3437.22756504671</v>
+        <v>3437.22800102012</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>3277.67686570563</v>
+        <v>3277.81556188106</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>3366.37101895886</v>
+        <v>3366.37150186943</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>3410.04740467956</v>
+        <v>3410.0473290768</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>3410.04740467956</v>
+        <v>3410.0473290768</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>3438.01877287324</v>
+        <v>3438.01896073795</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>3438.01877287324</v>
+        <v>3438.01896073795</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>0.0346921981224809</v>
+        <v>0.0346921553487963</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0.133413462154495</v>
+        <v>0.13341347636148</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>0.035300992162165</v>
+        <v>0.0353009478785278</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>1.00023018779279</v>
+        <v>1.00023011558081</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>1.04891937605115</v>
+        <v>1.0488750498106</v>
       </c>
     </row>
     <row r="71">
@@ -5722,46 +5722,46 @@
         <v>3347.59534135146</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>0.931472734272011</v>
+        <v>0.931472808691917</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>3575.99237133013</v>
+        <v>3575.99136282767</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>3317.68704856248</v>
+        <v>3317.85167385023</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>3417.96183195967</v>
+        <v>3417.96145373096</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>3593.87367786751</v>
+        <v>3593.87339073541</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>3593.87367786751</v>
+        <v>3593.87339073541</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>3574.5895070794</v>
+        <v>3574.58887138213</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>3574.5895070794</v>
+        <v>3574.58887138213</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>0.0389549790077133</v>
+        <v>0.0389547465265571</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>0.12620018291767</v>
+        <v>0.126200078337145</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>0.0397236732049677</v>
+        <v>0.0397234314888342</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>0.999607699316705</v>
+        <v>0.999607803458332</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>1.07743420484106</v>
+        <v>1.07738055307155</v>
       </c>
     </row>
     <row r="72">
@@ -5781,46 +5781,46 @@
         <v>3450.41139520334</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>0.932401676558435</v>
+        <v>0.932402153503304</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>3712.71081053977</v>
+        <v>3712.7104372995</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>3352.63227262553</v>
+        <v>3352.82472867699</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>3457.86741215847</v>
+        <v>3457.86581028836</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>3700.56326790303</v>
+        <v>3700.5613749809</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>3700.56326790303</v>
+        <v>3700.5613749809</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>3694.90514943896</v>
+        <v>3694.90475201341</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>3694.90514943896</v>
+        <v>3694.90475201341</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>0.0331045377360504</v>
+        <v>0.0331046080134791</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>0.140222640285826</v>
+        <v>0.140222603476408</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>0.0336585899223598</v>
+        <v>0.0336586625652302</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>0.995204134658087</v>
+        <v>0.995204127661774</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>1.1020907898573</v>
+        <v>1.10202741002552</v>
       </c>
     </row>
     <row r="73">
@@ -5840,46 +5840,46 @@
         <v>4175.47231114959</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>1.10327374674385</v>
+        <v>1.10327302283257</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>3773.83853519508</v>
+        <v>3773.83928862889</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>3382.38390498223</v>
+        <v>3382.60579230954</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>3484.64868318122</v>
+        <v>3484.64543327257</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>3784.62038408227</v>
+        <v>3784.62286735642</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>3784.62038408227</v>
+        <v>3784.62286735642</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>3751.22882753617</v>
+        <v>3751.22947621377</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>3751.22882753617</v>
+        <v>3751.22947621377</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>0.0151285895527656</v>
+        <v>0.0151288700372043</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>0.12961888329942</v>
+        <v>0.129618968593585</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>0.01524360594365</v>
+        <v>0.0152438907037229</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>0.994008830147858</v>
+        <v>0.994008803585451</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>1.10904880490078</v>
+        <v>1.10897624687521</v>
       </c>
     </row>
     <row r="74">
@@ -5899,46 +5899,46 @@
         <v>3842.8691195722</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>1.0288499692748</v>
+        <v>1.02885010119391</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>3722.993420475</v>
+        <v>3722.99356096208</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>3407.03076959209</v>
+        <v>3407.28326610002</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>3498.08004793258</v>
+        <v>3498.07466223805</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>3735.11127407711</v>
+        <v>3735.11079516133</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>3735.11127407711</v>
+        <v>3735.11079516133</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>3710.69590780298</v>
+        <v>3710.69615389197</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>3710.69590780298</v>
+        <v>3710.69615389197</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>-0.0108640383911853</v>
+        <v>-0.0108641449963765</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0.0793122879610852</v>
+        <v>0.0793123005626171</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>-0.0108052378558339</v>
+        <v>-0.010805343309125</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>0.996696874991938</v>
+        <v>0.996696903481367</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>1.08912896852037</v>
+        <v>1.0890483309124</v>
       </c>
     </row>
     <row r="75">
@@ -5958,46 +5958,46 @@
         <v>3354.26213069839</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>0.93487111747868</v>
+        <v>0.934871258463822</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>3623.64130562075</v>
+        <v>3623.64166111755</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>3426.91308821404</v>
+        <v>3427.19681207245</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>3499.43576782176</v>
+        <v>3499.42772390964</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>3587.94069897542</v>
+        <v>3587.9401578888</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>3587.94069897542</v>
+        <v>3587.9401578888</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>3612.68918229064</v>
+        <v>3612.69062482673</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>3612.68918229064</v>
+        <v>3612.69062482673</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>-0.0267670143888114</v>
+        <v>-0.0267666814106744</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>0.0106584756475623</v>
+        <v>0.0106590589339208</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>-0.0264119528917065</v>
+        <v>-0.0264116287081184</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>0.996977591762981</v>
+        <v>0.996977892044811</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.05421091498221</v>
+        <v>1.05412406200335</v>
       </c>
     </row>
     <row r="76">
@@ -6017,46 +6017,46 @@
         <v>3413.57383659744</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>0.937755373126117</v>
+        <v>0.937755960856985</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>0.30949986429986</v>
+        <v>0.309540310776156</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>3494.76677584293</v>
+        <v>3494.76989989924</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>3442.57613292233</v>
+        <v>3442.89098445655</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>3491.17526038866</v>
+        <v>3491.16402567681</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>3640.15385506979</v>
+        <v>3640.15157363317</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>3539.7640571346</v>
+        <v>3539.771388368</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>3496.40731253467</v>
+        <v>3496.41160161194</v>
       </c>
       <c r="N76" s="14" t="n">
-        <v>3496.40731253467</v>
+        <v>3496.41160161194</v>
       </c>
       <c r="O76" s="15" t="n">
-        <v>-0.0327164616986975</v>
+        <v>-0.0327156342865674</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>-0.0537220385574509</v>
+        <v>-0.0537207759667725</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>-0.0321870672755292</v>
+        <v>-0.0321862664950378</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>1.00046942665905</v>
+        <v>1.00046975960069</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.01563688863626</v>
+        <v>1.01554525467028</v>
       </c>
     </row>
     <row r="77">
@@ -6076,46 +6076,46 @@
         <v>3636.39564268968</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>1.09590711837113</v>
+        <v>1.09590611600938</v>
       </c>
       <c r="G77" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>3347.90897779938</v>
+        <v>3347.91171679836</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>3454.66581804791</v>
+        <v>3455.01080207315</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>3476.20046782897</v>
+        <v>3476.18553709892</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>3318.16043689408</v>
+        <v>3318.16347182294</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>3318.16043689408</v>
+        <v>3318.16347182294</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>3368.06156587855</v>
+        <v>3368.06470160639</v>
       </c>
       <c r="N77" s="14" t="n">
-        <v>3368.06156587855</v>
+        <v>3368.06470160639</v>
       </c>
       <c r="O77" s="15" t="n">
-        <v>-0.0373985833006721</v>
+        <v>-0.0373988789916308</v>
       </c>
       <c r="P77" s="16" t="n">
-        <v>-0.102144464993699</v>
+        <v>-0.102143784334441</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>-0.0367078933269601</v>
+        <v>-0.0367081781636845</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>1.00601945519212</v>
+        <v>1.00601956876787</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>0.974931221504285</v>
+        <v>0.97483478187258</v>
       </c>
     </row>
     <row r="78">
@@ -6135,46 +6135,46 @@
         <v>3401.60556878379</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>1.03199001066779</v>
+        <v>1.03199027935402</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>3327.05324721695</v>
+        <v>3327.05331145544</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>3463.8888003744</v>
+        <v>3464.26183399554</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>3457.65627632207</v>
+        <v>3457.63726454879</v>
       </c>
       <c r="K78" s="11" t="n">
-        <v>3296.16133259143</v>
+        <v>3296.16047441168</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>3296.16133259143</v>
+        <v>3296.16047441168</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>3342.31662434204</v>
+        <v>3342.31678574351</v>
       </c>
       <c r="N78" s="14" t="n">
-        <v>3342.31662434204</v>
+        <v>3342.31678574351</v>
       </c>
       <c r="O78" s="15" t="n">
-        <v>-0.00767320920652527</v>
+        <v>-0.00767409193435931</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>-0.0992749857745805</v>
+        <v>-0.0992750020133243</v>
       </c>
       <c r="Q78" s="17" t="n">
-        <v>-0.00764384528992035</v>
+        <v>-0.00764472126993276</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>1.00458765640071</v>
+        <v>1.00458768551604</v>
       </c>
       <c r="S78" s="19" t="n">
-        <v>0.964902979558925</v>
+        <v>0.964799124865403</v>
       </c>
     </row>
     <row r="79">
@@ -6194,46 +6194,46 @@
         <v>3222.50375079941</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>0.931687065222562</v>
+        <v>0.931687246497719</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>3397.44365096179</v>
+        <v>3397.44349390417</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>3470.86642082216</v>
+        <v>3471.26411971558</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>3437.89737189272</v>
+        <v>3437.87410407286</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>3458.78339529123</v>
+        <v>3458.78272232774</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>3458.78339529123</v>
+        <v>3458.78272232774</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>3394.94248873126</v>
+        <v>3394.94142145267</v>
       </c>
       <c r="N79" s="14" t="n">
-        <v>3394.94248873126</v>
+        <v>3394.94142145267</v>
       </c>
       <c r="O79" s="15" t="n">
-        <v>0.0156226542147502</v>
+        <v>0.0156222915513028</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>-0.0602727449199801</v>
+        <v>-0.0602734155749943</v>
       </c>
       <c r="Q79" s="17" t="n">
-        <v>0.0157453258634881</v>
+        <v>0.0157449574898534</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>0.999263810533011</v>
+        <v>0.999263542585478</v>
       </c>
       <c r="S79" s="19" t="n">
-        <v>0.978125366151974</v>
+        <v>0.978012995948816</v>
       </c>
     </row>
     <row r="80">
@@ -6253,46 +6253,46 @@
         <v>3185.85231014052</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>0.946468424750118</v>
+        <v>0.946469005392261</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>3418.69534254549</v>
+        <v>3418.68887831757</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>3476.1151906442</v>
+        <v>3476.53263537542</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>3418.47096584699</v>
+        <v>3418.44356776688</v>
       </c>
       <c r="K80" s="11" t="n">
-        <v>3366.04183175116</v>
+        <v>3366.03976674351</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>3366.04183175116</v>
+        <v>3366.03976674351</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>3389.42350510521</v>
+        <v>3389.41505356302</v>
       </c>
       <c r="N80" s="14" t="n">
-        <v>3389.42350510521</v>
+        <v>3389.41505356302</v>
       </c>
       <c r="O80" s="15" t="n">
-        <v>-0.00162697143652829</v>
+        <v>-0.00162915057081782</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>-0.0305982106392244</v>
+        <v>-0.0306018170170768</v>
       </c>
       <c r="Q80" s="17" t="n">
-        <v>-0.00162564863598413</v>
+        <v>-0.00162782422539653</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>0.99143771687521</v>
+        <v>0.991437119376317</v>
       </c>
       <c r="S80" s="19" t="n">
-        <v>0.975060755819509</v>
+        <v>0.974941244351935</v>
       </c>
     </row>
     <row r="81">
@@ -6312,46 +6312,46 @@
         <v>3869.93013865163</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1.08365440476456</v>
+        <v>1.08365343917505</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>0.0221851017823451</v>
+        <v>0.0220956203995741</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>3362.19039958411</v>
+        <v>3362.17979282867</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>3480.1440692026</v>
+        <v>3480.57455624382</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>3401.02869960795</v>
+        <v>3400.99771081788</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>3571.18479991084</v>
+        <v>3571.18798201543</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>3366.8269616273</v>
+        <v>3366.79795843734</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>3344.67233325523</v>
+        <v>3344.65721675468</v>
       </c>
       <c r="N81" s="14" t="n">
-        <v>3344.67233325523</v>
+        <v>3344.65721675468</v>
       </c>
       <c r="O81" s="15" t="n">
-        <v>-0.0132911178311058</v>
+        <v>-0.0132931439098025</v>
       </c>
       <c r="P81" s="16" t="n">
-        <v>-0.00694441956176473</v>
+        <v>-0.00694983229999813</v>
       </c>
       <c r="Q81" s="17" t="n">
-        <v>-0.0132031809487885</v>
+        <v>-0.0132051802747761</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>0.994789686410667</v>
+        <v>0.994788328657688</v>
       </c>
       <c r="S81" s="19" t="n">
-        <v>0.961072951793514</v>
+        <v>0.960949740540593</v>
       </c>
     </row>
     <row r="82">
@@ -6371,46 +6371,46 @@
         <v>3413.56946580066</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>1.04104182718984</v>
+        <v>1.04104195247535</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>3322.86609770666</v>
+        <v>3322.86122229199</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>3483.39322001008</v>
+        <v>3483.82799954664</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>3386.96006892819</v>
+        <v>3386.92656940777</v>
       </c>
       <c r="K82" s="11" t="n">
-        <v>3278.99357801517</v>
+        <v>3278.99318340054</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>3278.99357801517</v>
+        <v>3278.99318340054</v>
       </c>
       <c r="M82" s="13" t="n">
-        <v>3315.68672547236</v>
+        <v>3315.67935461701</v>
       </c>
       <c r="N82" s="14" t="n">
-        <v>3315.68672547236</v>
+        <v>3315.67935461701</v>
       </c>
       <c r="O82" s="15" t="n">
-        <v>-0.00870397241973668</v>
+        <v>-0.00870167586133361</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>-0.00796749735669433</v>
+        <v>-0.00796975057544558</v>
       </c>
       <c r="Q82" s="17" t="n">
-        <v>-0.00866620251397188</v>
+        <v>-0.00866392585539477</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>0.997839403688505</v>
+        <v>0.99783864952686</v>
       </c>
       <c r="S82" s="19" t="n">
-        <v>0.951855422587855</v>
+        <v>0.951734515897021</v>
       </c>
     </row>
     <row r="83">
@@ -6430,46 +6430,46 @@
         <v>3098.85650879477</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>0.92837594676369</v>
+        <v>0.928375860822446</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>3316.37818758131</v>
+        <v>3316.3782545089</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>3486.23198338717</v>
+        <v>3486.65997213614</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>3377.48356087041</v>
+        <v>3377.44918095655</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>3337.93278423182</v>
+        <v>3337.93309322961</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>3337.93278423182</v>
+        <v>3337.93309322961</v>
       </c>
       <c r="M83" s="13" t="n">
-        <v>3330.61200987115</v>
+        <v>3330.61102290117</v>
       </c>
       <c r="N83" s="14" t="n">
-        <v>3330.61200987115</v>
+        <v>3330.61102290117</v>
       </c>
       <c r="O83" s="15" t="n">
-        <v>0.00449131466471476</v>
+        <v>0.00449324135948639</v>
       </c>
       <c r="P83" s="16" t="n">
-        <v>-0.0189489156513396</v>
+        <v>-0.018948897952993</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>0.00450141573512375</v>
+        <v>0.00450335110461397</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>1.00429197802082</v>
+        <v>1.00429166014851</v>
       </c>
       <c r="S83" s="19" t="n">
-        <v>0.955361555324605</v>
+        <v>0.95524400128431</v>
       </c>
     </row>
     <row r="84">
@@ -6489,46 +6489,46 @@
         <v>3199.75362495821</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>0.9501615923499</v>
+        <v>0.950162769268136</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>3392.20269081218</v>
+        <v>3392.20046476105</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>3488.90194987812</v>
+        <v>3489.30945910447</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>3373.27783004273</v>
+        <v>3373.24491595421</v>
       </c>
       <c r="K84" s="11" t="n">
-        <v>3367.58889300578</v>
+        <v>3367.58472174491</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>3367.58889300578</v>
+        <v>3367.58472174491</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>3378.01401985931</v>
+        <v>3378.01223530857</v>
       </c>
       <c r="N84" s="14" t="n">
-        <v>3378.01401985931</v>
+        <v>3378.01223530857</v>
       </c>
       <c r="O84" s="15" t="n">
-        <v>0.0141318948664604</v>
+        <v>0.0141316629152885</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>-0.00336620231396878</v>
+        <v>-0.00336424370407729</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>0.0142322221404576</v>
+        <v>0.0142319868881324</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>0.995817269117998</v>
+        <v>0.995817396524801</v>
       </c>
       <c r="S84" s="19" t="n">
-        <v>0.968216954327797</v>
+        <v>0.968103366840824</v>
       </c>
     </row>
     <row r="85">
@@ -6548,46 +6548,46 @@
         <v>3684.19222817274</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1.07131451147546</v>
+        <v>1.07131423256144</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>3391.14491732455</v>
+        <v>3391.14493291041</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>3491.55202302774</v>
+        <v>3491.92249124446</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>3374.82377717008</v>
+        <v>3374.79556445208</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>3438.94550919385</v>
+        <v>3438.94640451484</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>3438.94550919385</v>
+        <v>3438.94640451484</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>3383.31241615884</v>
+        <v>3383.31275789184</v>
       </c>
       <c r="N85" s="14" t="n">
-        <v>3383.31241615884</v>
+        <v>3383.31275789184</v>
       </c>
       <c r="O85" s="15" t="n">
-        <v>0.00156726566427836</v>
+        <v>0.00156789495386156</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>0.0115527259634418</v>
+        <v>0.0115573999462544</v>
       </c>
       <c r="Q85" s="17" t="n">
-        <v>0.00156849446697915</v>
+        <v>0.00156912474379789</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>0.997690307740698</v>
+        <v>0.99769040392743</v>
       </c>
       <c r="S85" s="19" t="n">
-        <v>0.96899957206565</v>
+        <v>0.968896865945639</v>
       </c>
     </row>
     <row r="86">
@@ -6607,46 +6607,46 @@
         <v>3473.96328435329</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>1.05663216863889</v>
+        <v>1.0566309642424</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>3321.50849358518</v>
+        <v>3321.51341393432</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>3494.25528572027</v>
+        <v>3494.5690213881</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>3382.5738582922</v>
+        <v>3382.55461553044</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>3287.76975324186</v>
+        <v>3287.77350079278</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>3287.76975324186</v>
+        <v>3287.77350079278</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>3328.82807453996</v>
+        <v>3328.83132349347</v>
       </c>
       <c r="N86" s="14" t="n">
-        <v>3328.82807453996</v>
+        <v>3328.83132349347</v>
       </c>
       <c r="O86" s="15" t="n">
-        <v>-0.0162349219014396</v>
+        <v>-0.0162340469021641</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>0.00396338682018271</v>
+        <v>0.00396659853678138</v>
       </c>
       <c r="Q86" s="17" t="n">
-        <v>-0.0161038458519706</v>
+        <v>-0.0161029849431719</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>1.00220369177707</v>
+        <v>1.00220318530958</v>
       </c>
       <c r="S86" s="19" t="n">
-        <v>0.952657376850411</v>
+        <v>0.952572778823297</v>
       </c>
     </row>
     <row r="87">
@@ -6666,46 +6666,46 @@
         <v>3047.37400305265</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>0.92321522523317</v>
+        <v>0.923213937143551</v>
       </c>
       <c r="G87" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>3320.95694275611</v>
+        <v>3320.9573753931</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>3497.05194176882</v>
+        <v>3497.28589231317</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>3397.30113810897</v>
+        <v>3397.29631246991</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>3300.82728248226</v>
+        <v>3300.83188787347</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>3300.82728248226</v>
+        <v>3300.83188787347</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>3323.70464027785</v>
+        <v>3323.70480896358</v>
       </c>
       <c r="N87" s="14" t="n">
-        <v>3323.70464027785</v>
+        <v>3323.70480896358</v>
       </c>
       <c r="O87" s="15" t="n">
-        <v>-0.00154029615326543</v>
+        <v>-0.00154122140567001</v>
       </c>
       <c r="P87" s="16" t="n">
-        <v>-0.00207390400707774</v>
+        <v>-0.00207355764155681</v>
       </c>
       <c r="Q87" s="17" t="n">
-        <v>-0.001539110505973</v>
+        <v>-0.0015400343338845</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>1.00082738125459</v>
+        <v>1.00082730166633</v>
       </c>
       <c r="S87" s="19" t="n">
-        <v>0.950430447022962</v>
+        <v>0.950366916318993</v>
       </c>
     </row>
     <row r="88">
@@ -6725,46 +6725,46 @@
         <v>3228.33181776595</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>0.948005307899961</v>
+        <v>0.948008727460259</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>3341.65290941161</v>
+        <v>3341.64430628085</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>3499.85314152869</v>
+        <v>3499.98069959707</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>3419.304660795</v>
+        <v>3419.32099297739</v>
       </c>
       <c r="K88" s="11" t="n">
-        <v>3405.39424290504</v>
+        <v>3405.38195931459</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>3405.39424290504</v>
+        <v>3405.38195931459</v>
       </c>
       <c r="M88" s="13" t="n">
-        <v>3341.55393674192</v>
+        <v>3341.54748557253</v>
       </c>
       <c r="N88" s="14" t="n">
-        <v>3341.55393674192</v>
+        <v>3341.54748557253</v>
       </c>
       <c r="O88" s="15" t="n">
-        <v>0.00535593298491406</v>
+        <v>0.00535395164109569</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>-0.0107933486667121</v>
+        <v>-0.0107947358375117</v>
       </c>
       <c r="Q88" s="17" t="n">
-        <v>0.00537030163503904</v>
+        <v>0.00536830965278012</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>0.999970382121552</v>
+        <v>0.999971026028073</v>
       </c>
       <c r="S88" s="19" t="n">
-        <v>0.954769757934009</v>
+        <v>0.954733117801828</v>
       </c>
     </row>
     <row r="89">
@@ -6784,46 +6784,46 @@
         <v>3463.84324480454</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>1.06429154658028</v>
+        <v>1.06429345727511</v>
       </c>
       <c r="G89" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>3332.13201839874</v>
+        <v>3332.12799874782</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>3502.44739494312</v>
+        <v>3502.43825506444</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>3448.40110124676</v>
+        <v>3448.44667263683</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>3254.59997867536</v>
+        <v>3254.59413578747</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>3254.59997867536</v>
+        <v>3254.59413578747</v>
       </c>
       <c r="M89" s="13" t="n">
-        <v>3321.0660725907</v>
+        <v>3321.06380016145</v>
       </c>
       <c r="N89" s="14" t="n">
-        <v>3321.0660725907</v>
+        <v>3321.06380016145</v>
       </c>
       <c r="O89" s="15" t="n">
-        <v>-0.00615011172782469</v>
+        <v>-0.00614886538348732</v>
       </c>
       <c r="P89" s="16" t="n">
-        <v>-0.0183980478039348</v>
+        <v>-0.0183988186091274</v>
       </c>
       <c r="Q89" s="17" t="n">
-        <v>-0.00613123850133079</v>
+        <v>-0.00612999979785589</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>0.996679019394508</v>
+        <v>0.996679539744412</v>
       </c>
       <c r="S89" s="19" t="n">
-        <v>0.948212977412793</v>
+        <v>0.948214803033079</v>
       </c>
     </row>
     <row r="90">
@@ -6843,46 +6843,46 @@
         <v>3610.11150456841</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>1.07135458606683</v>
+        <v>1.07134985524464</v>
       </c>
       <c r="G90" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>3284.24060255633</v>
+        <v>3284.25452394873</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>3504.56417514374</v>
+        <v>3504.38424632723</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>3484.33758227129</v>
+        <v>3484.42167186385</v>
       </c>
       <c r="K90" s="11" t="n">
-        <v>3369.67009010704</v>
+        <v>3369.68496975626</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>3369.67009010704</v>
+        <v>3369.68496975626</v>
       </c>
       <c r="M90" s="13" t="n">
-        <v>3302.4644488522</v>
+        <v>3302.47442930985</v>
       </c>
       <c r="N90" s="14" t="n">
-        <v>3302.4644488522</v>
+        <v>3302.47442930985</v>
       </c>
       <c r="O90" s="15" t="n">
-        <v>-0.00561684515030083</v>
+        <v>-0.00561313878353098</v>
       </c>
       <c r="P90" s="16" t="n">
-        <v>-0.00791979191998471</v>
+        <v>-0.00791776200782812</v>
       </c>
       <c r="Q90" s="17" t="n">
-        <v>-0.00560110016841442</v>
+        <v>-0.00559741455454599</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>1.00554887674237</v>
+        <v>1.0055476532736</v>
       </c>
       <c r="S90" s="19" t="n">
-        <v>0.942332422466409</v>
+        <v>0.942383653496617</v>
       </c>
     </row>
     <row r="91">
@@ -6902,46 +6902,46 @@
         <v>2954.63346329572</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>0.918752840478085</v>
+        <v>0.918748267925671</v>
       </c>
       <c r="G91" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>3303.66221518779</v>
+        <v>3303.67326533652</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>3505.77805062699</v>
+        <v>3505.38945842286</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v>3525.89222106276</v>
+        <v>3526.02504838981</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>3215.91763651935</v>
+        <v>3215.9336419394</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>3215.91763651935</v>
+        <v>3215.9336419394</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>3305.90732485032</v>
+        <v>3305.91322406491</v>
       </c>
       <c r="N91" s="14" t="n">
-        <v>3305.90732485032</v>
+        <v>3305.91322406491</v>
       </c>
       <c r="O91" s="15" t="n">
-        <v>0.00104197415869556</v>
+        <v>0.00104073648394179</v>
       </c>
       <c r="P91" s="16" t="n">
-        <v>-0.00535466214772962</v>
+        <v>-0.00535293773703771</v>
       </c>
       <c r="Q91" s="17" t="n">
-        <v>0.00104251720236537</v>
+        <v>0.00104127823808109</v>
       </c>
       <c r="R91" s="18" t="n">
-        <v>1.00067958208688</v>
+        <v>1.00067802066018</v>
       </c>
       <c r="S91" s="19" t="n">
-        <v>0.942988197515551</v>
+        <v>0.943094415977476</v>
       </c>
     </row>
     <row r="92">
@@ -6961,46 +6961,46 @@
         <v>3221.79961592558</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>0.941461991423614</v>
+        <v>0.941468399788101</v>
       </c>
       <c r="G92" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>3343.13084423546</v>
+        <v>3343.09834238811</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>3505.57928108614</v>
+        <v>3504.94048934087</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v>3571.26979735453</v>
+        <v>3571.46217643555</v>
       </c>
       <c r="K92" s="11" t="n">
-        <v>3422.12393625556</v>
+        <v>3422.10064262456</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>3422.12393625556</v>
+        <v>3422.10064262456</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>3370.55955537268</v>
+        <v>3370.53782004135</v>
       </c>
       <c r="N92" s="14" t="n">
-        <v>3370.55955537268</v>
+        <v>3370.53782004135</v>
       </c>
       <c r="O92" s="15" t="n">
-        <v>0.0193678041558144</v>
+        <v>0.0193595711076762</v>
       </c>
       <c r="P92" s="16" t="n">
-        <v>0.00868027845123898</v>
+        <v>0.00867572123214866</v>
       </c>
       <c r="Q92" s="17" t="n">
-        <v>0.0195565768091461</v>
+        <v>0.0195481827853239</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>1.00820449824287</v>
+        <v>1.00820779852789</v>
       </c>
       <c r="S92" s="19" t="n">
-        <v>0.961484332577515</v>
+        <v>0.96165336623881</v>
       </c>
     </row>
     <row r="93">
@@ -7020,46 +7020,46 @@
         <v>3638.1623004355</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1.06314582013072</v>
+        <v>1.06316332979257</v>
       </c>
       <c r="G93" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>3486.21379474576</v>
+        <v>3486.19604906964</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>3503.2769634557</v>
+        <v>3502.34302718551</v>
       </c>
       <c r="J93" s="10" t="n">
-        <v>3617.12521795723</v>
+        <v>3617.38797318966</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>3422.07271246024</v>
+        <v>3422.01635297686</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>3422.07271246024</v>
+        <v>3422.01635297686</v>
       </c>
       <c r="M93" s="13" t="n">
-        <v>3497.90693281288</v>
+        <v>3497.89514791856</v>
       </c>
       <c r="N93" s="14" t="n">
-        <v>3497.90693281288</v>
+        <v>3497.89514791856</v>
       </c>
       <c r="O93" s="15" t="n">
-        <v>0.037085999663186</v>
+        <v>0.0370890791333275</v>
       </c>
       <c r="P93" s="16" t="n">
-        <v>0.0532482210100178</v>
+        <v>0.0532453931624313</v>
       </c>
       <c r="Q93" s="17" t="n">
-        <v>0.0377822659259084</v>
+        <v>0.0377854617503304</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>1.00335410814011</v>
+        <v>1.00335583503746</v>
       </c>
       <c r="S93" s="19" t="n">
-        <v>0.998467140708874</v>
+        <v>0.998730027518028</v>
       </c>
     </row>
     <row r="94">
@@ -7079,46 +7079,46 @@
         <v>4037.4781476365</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>1.08378248387274</v>
+        <v>1.08375662952114</v>
       </c>
       <c r="G94" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>3715.3642805585</v>
+        <v>3715.4243105474</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>3498.12803507961</v>
+        <v>3496.85098515684</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v>3659.367660376</v>
+        <v>3659.71054817166</v>
       </c>
       <c r="K94" s="11" t="n">
-        <v>3725.35837007548</v>
+        <v>3725.44724309596</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>3725.35837007548</v>
+        <v>3725.44724309596</v>
       </c>
       <c r="M94" s="13" t="n">
-        <v>3710.20607816769</v>
+        <v>3710.2510712467</v>
       </c>
       <c r="N94" s="14" t="n">
-        <v>3710.20607816769</v>
+        <v>3710.2510712467</v>
       </c>
       <c r="O94" s="15" t="n">
-        <v>0.058922651338363</v>
+        <v>0.0589381472389278</v>
       </c>
       <c r="P94" s="16" t="n">
-        <v>0.123465864850477</v>
+        <v>0.123476093658072</v>
       </c>
       <c r="Q94" s="17" t="n">
-        <v>0.0606931943681195</v>
+        <v>0.0607096308917383</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>0.998611656354182</v>
+        <v>0.998607631627425</v>
       </c>
       <c r="S94" s="19" t="n">
-        <v>1.06062615231956</v>
+        <v>1.06102635971498</v>
       </c>
     </row>
     <row r="95">
@@ -7138,46 +7138,46 @@
         <v>3625.34060687029</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>0.913636279600601</v>
+        <v>0.913622790484195</v>
       </c>
       <c r="G95" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H95" s="8" t="n">
-        <v>3927.96523573611</v>
+        <v>3928.008760828</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>3489.33868064497</v>
+        <v>3487.66807228352</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v>3692.9310395885</v>
+        <v>3693.36115280002</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>3968.03486005954</v>
+        <v>3968.09344581801</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>3968.03486005954</v>
+        <v>3968.09344581801</v>
       </c>
       <c r="M95" s="13" t="n">
-        <v>3895.92355115147</v>
+        <v>3895.94800609311</v>
       </c>
       <c r="N95" s="14" t="n">
-        <v>3895.92355115147</v>
+        <v>3895.94800609311</v>
       </c>
       <c r="O95" s="15" t="n">
-        <v>0.0488433414407701</v>
+        <v>0.0488374917125554</v>
       </c>
       <c r="P95" s="16" t="n">
-        <v>0.178473311053225</v>
+        <v>0.17847860546766</v>
       </c>
       <c r="Q95" s="17" t="n">
-        <v>0.0500558376195379</v>
+        <v>0.0500496950962437</v>
       </c>
       <c r="R95" s="18" t="n">
-        <v>0.99184267612831</v>
+        <v>0.991837911601771</v>
       </c>
       <c r="S95" s="19" t="n">
-        <v>1.11652204263283</v>
+        <v>1.11706387343858</v>
       </c>
     </row>
     <row r="96">
@@ -7197,46 +7197,46 @@
         <v>3659.99110295258</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>0.93313176520709</v>
+        <v>0.933157513270865</v>
       </c>
       <c r="G96" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>3929.85900583045</v>
+        <v>3929.74218136607</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>3476.25710379821</v>
+        <v>3474.14087025543</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>3713.07922412087</v>
+        <v>3713.59972196782</v>
       </c>
       <c r="K96" s="11" t="n">
-        <v>3922.26611441131</v>
+        <v>3922.15788964045</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>3922.26611441131</v>
+        <v>3922.15788964045</v>
       </c>
       <c r="M96" s="13" t="n">
-        <v>3929.6233189375</v>
+        <v>3929.54199045825</v>
       </c>
       <c r="N96" s="14" t="n">
-        <v>3929.6233189375</v>
+        <v>3929.54199045825</v>
       </c>
       <c r="O96" s="15" t="n">
-        <v>0.00861281049551458</v>
+        <v>0.00858583698892108</v>
       </c>
       <c r="P96" s="16" t="n">
-        <v>0.165866751315423</v>
+        <v>0.165850140322725</v>
       </c>
       <c r="Q96" s="17" t="n">
-        <v>0.00865000746127853</v>
+        <v>0.00862280100058022</v>
       </c>
       <c r="R96" s="18" t="n">
-        <v>0.999940026628793</v>
+        <v>0.99994905749574</v>
       </c>
       <c r="S96" s="19" t="n">
-        <v>1.1304179183536</v>
+        <v>1.13108308995235</v>
       </c>
     </row>
     <row r="97">
@@ -7256,46 +7256,46 @@
         <v>4183.39210452291</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>1.07103716362791</v>
+        <v>1.0710830818037</v>
       </c>
       <c r="G97" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H97" s="8" t="n">
-        <v>3977.8671107608</v>
+        <v>3977.79064053321</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>3458.53069329795</v>
+        <v>3455.91622662093</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>3716.45160160164</v>
+        <v>3717.05985203325</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>3905.92618686784</v>
+        <v>3905.75873673412</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>3905.92618686784</v>
+        <v>3905.75873673412</v>
       </c>
       <c r="M97" s="13" t="n">
-        <v>3966.89991737741</v>
+        <v>3966.84967055264</v>
       </c>
       <c r="N97" s="14" t="n">
-        <v>3966.89991737741</v>
+        <v>3966.84967055264</v>
       </c>
       <c r="O97" s="15" t="n">
-        <v>0.00944133873185516</v>
+        <v>0.00944936859709715</v>
       </c>
       <c r="P97" s="16" t="n">
-        <v>0.134078176913467</v>
+        <v>0.134067632905788</v>
       </c>
       <c r="Q97" s="17" t="n">
-        <v>0.00948604876713399</v>
+        <v>0.00949415483661453</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>0.997242946262905</v>
+        <v>0.997249485714738</v>
       </c>
       <c r="S97" s="19" t="n">
-        <v>1.14698994144091</v>
+        <v>1.14784312188935</v>
       </c>
     </row>
     <row r="98">
@@ -7315,46 +7315,46 @@
         <v>4473.66539441506</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>1.08229968835621</v>
+        <v>1.08223629137013</v>
       </c>
       <c r="G98" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>4033.07148730938</v>
+        <v>4033.26368927765</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>3436.08559353441</v>
+        <v>3432.92099956547</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>3700.73349411075</v>
+        <v>3701.41793019284</v>
       </c>
       <c r="K98" s="11" t="n">
-        <v>4133.48118136265</v>
+        <v>4133.72331910189</v>
       </c>
       <c r="L98" s="12" t="n">
-        <v>4133.48118136265</v>
+        <v>4133.72331910189</v>
       </c>
       <c r="M98" s="13" t="n">
-        <v>4003.1297207915</v>
+        <v>4003.2696039385</v>
       </c>
       <c r="N98" s="14" t="n">
-        <v>4003.1297207915</v>
+        <v>4003.2696039385</v>
       </c>
       <c r="O98" s="15" t="n">
-        <v>0.00909157295808076</v>
+        <v>0.00913918239565979</v>
       </c>
       <c r="P98" s="16" t="n">
-        <v>0.0789507742838031</v>
+        <v>0.0789753919788898</v>
       </c>
       <c r="Q98" s="17" t="n">
-        <v>0.00913302683926531</v>
+        <v>0.0091810722388137</v>
       </c>
       <c r="R98" s="18" t="n">
-        <v>0.992575939550762</v>
+        <v>0.992563321505884</v>
       </c>
       <c r="S98" s="19" t="n">
-        <v>1.16502619385387</v>
+        <v>1.16614090578992</v>
       </c>
     </row>
     <row r="99">
@@ -7374,46 +7374,46 @@
         <v>3517.77670169052</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>0.916175880509091</v>
+        <v>0.916117971687646</v>
       </c>
       <c r="G99" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H99" s="8" t="n">
-        <v>3869.24644741629</v>
+        <v>3869.39006863881</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>3409.12757108129</v>
+        <v>3405.36319884331</v>
       </c>
       <c r="J99" s="10" t="n">
-        <v>3664.5575966545</v>
+        <v>3665.29383806663</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>3839.63033357285</v>
+        <v>3839.8730408161</v>
       </c>
       <c r="L99" s="12" t="n">
-        <v>3839.63033357285</v>
+        <v>3839.8730408161</v>
       </c>
       <c r="M99" s="13" t="n">
-        <v>3859.82478310238</v>
+        <v>3859.91579726282</v>
       </c>
       <c r="N99" s="14" t="n">
-        <v>3859.82478310238</v>
+        <v>3859.91579726282</v>
       </c>
       <c r="O99" s="15" t="n">
-        <v>-0.0364546959110425</v>
+        <v>-0.036466059156076</v>
       </c>
       <c r="P99" s="16" t="n">
-        <v>-0.0092657793653117</v>
+        <v>-0.00924863698743694</v>
       </c>
       <c r="Q99" s="17" t="n">
-        <v>-0.0357982248101579</v>
+        <v>-0.0358091812089408</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>0.997564987280611</v>
+        <v>0.99755148196281</v>
       </c>
       <c r="S99" s="19" t="n">
-        <v>1.13220309378981</v>
+        <v>1.13348138564894</v>
       </c>
     </row>
     <row r="100">
@@ -7433,46 +7433,46 @@
         <v>3357.72554729946</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>0.925871366269303</v>
+        <v>0.925964177126254</v>
       </c>
       <c r="G100" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>3667.74812196973</v>
+        <v>3667.42615537273</v>
       </c>
       <c r="I100" s="9" t="n">
-        <v>3378.29826475469</v>
+        <v>3373.88883565847</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>3608.72034267545</v>
+        <v>3609.46898421921</v>
       </c>
       <c r="K100" s="11" t="n">
-        <v>3626.55728390117</v>
+        <v>3626.19378831719</v>
       </c>
       <c r="L100" s="12" t="n">
-        <v>3626.55728390117</v>
+        <v>3626.19378831719</v>
       </c>
       <c r="M100" s="13" t="n">
-        <v>3696.46182735014</v>
+        <v>3696.23456450144</v>
       </c>
       <c r="N100" s="14" t="n">
-        <v>3696.46182735014</v>
+        <v>3696.23456450144</v>
       </c>
       <c r="O100" s="15" t="n">
-        <v>-0.0432456902069874</v>
+        <v>-0.0433307528711487</v>
       </c>
       <c r="P100" s="16" t="n">
-        <v>-0.0593343108647891</v>
+        <v>-0.0593726766435712</v>
       </c>
       <c r="Q100" s="17" t="n">
-        <v>-0.0423239304715108</v>
+        <v>-0.042405389484779</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>1.00782870154262</v>
+        <v>1.00785521177748</v>
       </c>
       <c r="S100" s="19" t="n">
-        <v>1.09417864784611</v>
+        <v>1.09554130101624</v>
       </c>
     </row>
     <row r="101">
@@ -7492,46 +7492,46 @@
         <v>3992.99553442729</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>1.08120357717409</v>
+        <v>1.08132794765883</v>
       </c>
       <c r="G101" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H101" s="8" t="n">
-        <v>3660.601032298</v>
+        <v>3660.38108587428</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>3344.50837759728</v>
+        <v>3339.41548986616</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v>3534.89352930072</v>
+        <v>3535.59767322891</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>3693.10240802538</v>
+        <v>3692.67764055527</v>
       </c>
       <c r="L101" s="12" t="n">
-        <v>3693.10240802538</v>
+        <v>3692.67764055527</v>
       </c>
       <c r="M101" s="13" t="n">
-        <v>3672.47204911272</v>
+        <v>3672.33004388321</v>
       </c>
       <c r="N101" s="14" t="n">
-        <v>3672.47204911272</v>
+        <v>3672.33004388321</v>
       </c>
       <c r="O101" s="15" t="n">
-        <v>-0.00651108108493959</v>
+        <v>-0.00648826623606423</v>
       </c>
       <c r="P101" s="16" t="n">
-        <v>-0.0742211486039567</v>
+        <v>-0.0742452200434424</v>
       </c>
       <c r="Q101" s="17" t="n">
-        <v>-0.00648992992702413</v>
+        <v>-0.00646726288634769</v>
       </c>
       <c r="R101" s="18" t="n">
-        <v>1.00324291467712</v>
+        <v>1.00326440272982</v>
       </c>
       <c r="S101" s="19" t="n">
-        <v>1.09806035281964</v>
+        <v>1.09969246265621</v>
       </c>
     </row>
     <row r="102">
@@ -7551,46 +7551,46 @@
         <v>3941.5912142825</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>1.07192168852609</v>
+        <v>1.07173369428551</v>
       </c>
       <c r="G102" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>3674.58176927484</v>
+        <v>3675.09761104776</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>3308.82377453867</v>
+        <v>3303.01843191701</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v>3444.83813836361</v>
+        <v>3445.41783369457</v>
       </c>
       <c r="K102" s="11" t="n">
-        <v>3677.12609649895</v>
+        <v>3677.77110610508</v>
       </c>
       <c r="L102" s="12" t="n">
-        <v>3677.12609649895</v>
+        <v>3677.77110610508</v>
       </c>
       <c r="M102" s="13" t="n">
-        <v>3676.62028115357</v>
+        <v>3676.99721560962</v>
       </c>
       <c r="N102" s="14" t="n">
-        <v>3676.62028115357</v>
+        <v>3676.99721560962</v>
       </c>
       <c r="O102" s="15" t="n">
-        <v>0.00112891015515632</v>
+        <v>0.00127009512272908</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>-0.0815635421310725</v>
+        <v>-0.0815014776941058</v>
       </c>
       <c r="Q102" s="17" t="n">
-        <v>0.00112954761408091</v>
+        <v>0.00127090203512181</v>
       </c>
       <c r="R102" s="18" t="n">
-        <v>1.00055476024395</v>
+        <v>1.0005168854716</v>
       </c>
       <c r="S102" s="19" t="n">
-        <v>1.11115626931996</v>
+        <v>1.1132233414379</v>
       </c>
     </row>
     <row r="103">
@@ -7610,46 +7610,46 @@
         <v>3374.51907473218</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>0.922219839345833</v>
+        <v>0.922057940217835</v>
       </c>
       <c r="G103" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H103" s="8" t="n">
-        <v>3687.85354894499</v>
+        <v>3688.29399315392</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>3272.52819177751</v>
+        <v>3265.99372110583</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>3341.10619609099</v>
+        <v>3341.45279405164</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>3659.12652359102</v>
+        <v>3659.76900967303</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>3659.12652359102</v>
+        <v>3659.76900967303</v>
       </c>
       <c r="M103" s="13" t="n">
-        <v>3687.40808021881</v>
+        <v>3687.67143947789</v>
       </c>
       <c r="N103" s="14" t="n">
-        <v>3687.40808021881</v>
+        <v>3687.67143947789</v>
       </c>
       <c r="O103" s="15" t="n">
-        <v>0.00292986562593904</v>
+        <v>0.00289876757331062</v>
       </c>
       <c r="P103" s="16" t="n">
-        <v>-0.0446695672918564</v>
+        <v>-0.0446238640508874</v>
       </c>
       <c r="Q103" s="17" t="n">
-        <v>0.00293416187702022</v>
+        <v>0.00290297306262954</v>
       </c>
       <c r="R103" s="18" t="n">
-        <v>0.999879206503115</v>
+        <v>0.999831208228742</v>
       </c>
       <c r="S103" s="19" t="n">
-        <v>1.12677656665685</v>
+        <v>1.1291116133038</v>
       </c>
     </row>
     <row r="104">
@@ -7669,46 +7669,46 @@
         <v>3469.76766476378</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>0.924223141327113</v>
+        <v>0.924438979759211</v>
       </c>
       <c r="G104" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>3757.69336524073</v>
+        <v>3756.85171414265</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>3237.13555446365</v>
+        <v>3229.87163714881</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v>3227.41116850045</v>
+        <v>3227.38764909763</v>
       </c>
       <c r="K104" s="11" t="n">
-        <v>3754.25317719427</v>
+        <v>3753.37663246043</v>
       </c>
       <c r="L104" s="12" t="n">
-        <v>3754.25317719427</v>
+        <v>3753.37663246043</v>
       </c>
       <c r="M104" s="13" t="n">
-        <v>3713.5134242329</v>
+        <v>3712.83460547591</v>
       </c>
       <c r="N104" s="14" t="n">
-        <v>3713.5134242329</v>
+        <v>3712.83460547591</v>
       </c>
       <c r="O104" s="15" t="n">
-        <v>0.00705464914497969</v>
+        <v>0.00680041684150922</v>
       </c>
       <c r="P104" s="16" t="n">
-        <v>0.00461295089174008</v>
+        <v>0.00449106805447275</v>
       </c>
       <c r="Q104" s="17" t="n">
-        <v>0.00707959180165818</v>
+        <v>0.00682359218032191</v>
       </c>
       <c r="R104" s="18" t="n">
-        <v>0.988242803040689</v>
+        <v>0.98828351182959</v>
       </c>
       <c r="S104" s="19" t="n">
-        <v>1.14716030940143</v>
+        <v>1.14953008124913</v>
       </c>
     </row>
     <row r="105">
@@ -7728,46 +7728,46 @@
         <v>4016.542850834</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1.08955082669477</v>
+        <v>1.09002530662661</v>
       </c>
       <c r="G105" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H105" s="8" t="n">
-        <v>3640.96250904559</v>
+        <v>3639.85081555179</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>3204.40141170435</v>
+        <v>3196.42856931748</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>3109.05662324705</v>
+        <v>3108.49907470816</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>3686.42081895203</v>
+        <v>3684.81614730975</v>
       </c>
       <c r="L105" s="12" t="n">
-        <v>3686.42081895203</v>
+        <v>3684.81614730975</v>
       </c>
       <c r="M105" s="13" t="n">
-        <v>3561.52795782527</v>
+        <v>3560.45939336006</v>
       </c>
       <c r="N105" s="14" t="n">
-        <v>3561.52795782527</v>
+        <v>3560.45939336006</v>
       </c>
       <c r="O105" s="15" t="n">
-        <v>-0.0417887886823625</v>
+        <v>-0.04190604987126</v>
       </c>
       <c r="P105" s="16" t="n">
-        <v>-0.0302096489241503</v>
+        <v>-0.0304631253689952</v>
       </c>
       <c r="Q105" s="17" t="n">
-        <v>-0.0409276738885158</v>
+        <v>-0.0410401292562604</v>
       </c>
       <c r="R105" s="18" t="n">
-        <v>0.978183090041994</v>
+        <v>0.978188275779734</v>
       </c>
       <c r="S105" s="19" t="n">
-        <v>1.11144875445894</v>
+        <v>1.11388673832318</v>
       </c>
     </row>
     <row r="106">
@@ -7787,46 +7787,46 @@
         <v>3685.04709961106</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>1.05417424529402</v>
+        <v>1.05350817248036</v>
       </c>
       <c r="G106" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>3119.01701620274</v>
+        <v>3118.82864636032</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>3176.40451112108</v>
+        <v>3167.76809750545</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>2993.98033802933</v>
+        <v>2992.69369167566</v>
       </c>
       <c r="K106" s="11" t="n">
-        <v>3495.67172226188</v>
+        <v>3497.88183506451</v>
       </c>
       <c r="L106" s="12" t="n">
-        <v>3119.01701620274</v>
+        <v>3118.82864636032</v>
       </c>
       <c r="M106" s="13" t="n">
-        <v>3084.19139300264</v>
+        <v>3083.68613200683</v>
       </c>
       <c r="N106" s="14" t="n">
-        <v>3084.19139300264</v>
+        <v>3083.68613200683</v>
       </c>
       <c r="O106" s="15" t="n">
-        <v>-0.143900140656246</v>
+        <v>-0.143763902115243</v>
       </c>
       <c r="P106" s="16" t="n">
-        <v>-0.161134096764828</v>
+        <v>-0.161357501464526</v>
       </c>
       <c r="Q106" s="17" t="n">
-        <v>-0.134025780641097</v>
+        <v>-0.133907793539893</v>
       </c>
       <c r="R106" s="18" t="n">
-        <v>0.988834423467655</v>
+        <v>0.988732143269717</v>
       </c>
       <c r="S106" s="19" t="n">
-        <v>0.970969340398686</v>
+        <v>0.973457032550825</v>
       </c>
     </row>
     <row r="107">
@@ -7846,46 +7846,46 @@
         <v>1880.07334156122</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>0.931357242143957</v>
+        <v>0.931102172261312</v>
       </c>
       <c r="G107" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="8" t="n">
-        <v>2412.31072065306</v>
+        <v>2412.27108799693</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>3155.52486246481</v>
+        <v>3146.29904384257</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>2893.00691152436</v>
+        <v>2890.75970615557</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>2018.63823728191</v>
+        <v>2019.19123117842</v>
       </c>
       <c r="L107" s="12" t="n">
-        <v>2412.31072065306</v>
+        <v>2412.27108799693</v>
       </c>
       <c r="M107" s="13" t="n">
-        <v>2470.518103819</v>
+        <v>2470.18662933225</v>
       </c>
       <c r="N107" s="14" t="n">
-        <v>2470.518103819</v>
+        <v>2470.18662933225</v>
       </c>
       <c r="O107" s="15" t="n">
-        <v>-0.221861626488533</v>
+        <v>-0.221831971282425</v>
       </c>
       <c r="P107" s="16" t="n">
-        <v>-0.330012287744295</v>
+        <v>-0.33015002288762</v>
       </c>
       <c r="Q107" s="17" t="n">
-        <v>-0.198973802525981</v>
+        <v>-0.19895004757677</v>
       </c>
       <c r="R107" s="18" t="n">
-        <v>1.02412930584257</v>
+        <v>1.02400872009099</v>
       </c>
       <c r="S107" s="19" t="n">
-        <v>0.782918281901685</v>
+        <v>0.785108660973119</v>
       </c>
     </row>
     <row r="108">
@@ -7905,46 +7905,46 @@
         <v>1803.44547006555</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>0.930362090923597</v>
+        <v>0.930870287442628</v>
       </c>
       <c r="G108" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>1985.14039905338</v>
+        <v>1983.87556870349</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>3144.10660830222</v>
+        <v>3134.39964330174</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>2817.58612580007</v>
+        <v>2814.11599907675</v>
       </c>
       <c r="K108" s="11" t="n">
-        <v>1938.43395776715</v>
+        <v>1937.3756949748</v>
       </c>
       <c r="L108" s="12" t="n">
-        <v>1938.43395776715</v>
+        <v>1937.3756949748</v>
       </c>
       <c r="M108" s="13" t="n">
-        <v>2059.38362983858</v>
+        <v>2058.47304949502</v>
       </c>
       <c r="N108" s="14" t="n">
-        <v>2059.38362983858</v>
+        <v>2058.47304949502</v>
       </c>
       <c r="O108" s="15" t="n">
-        <v>-0.18202115806142</v>
+        <v>-0.18232923638012</v>
       </c>
       <c r="P108" s="16" t="n">
-        <v>-0.445435253741143</v>
+        <v>-0.44557911455063</v>
       </c>
       <c r="Q108" s="17" t="n">
-        <v>-0.16641629678604</v>
+        <v>-0.166673066297232</v>
       </c>
       <c r="R108" s="18" t="n">
-        <v>1.03739948611222</v>
+        <v>1.03760189498189</v>
       </c>
       <c r="S108" s="19" t="n">
-        <v>0.654998028502162</v>
+        <v>0.656735988945764</v>
       </c>
     </row>
     <row r="109">
@@ -7964,46 +7964,46 @@
         <v>2123.17169555586</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>1.08972478482975</v>
+        <v>1.09055663751311</v>
       </c>
       <c r="G109" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H109" s="8" t="n">
-        <v>1881.10674569218</v>
+        <v>1880.60698461145</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>3144.02938236133</v>
+        <v>3133.98936338342</v>
       </c>
       <c r="J109" s="10" t="n">
-        <v>2776.76428197004</v>
+        <v>2771.78900827728</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>1948.35588316693</v>
+        <v>1946.86972003354</v>
       </c>
       <c r="L109" s="12" t="n">
-        <v>1948.35588316693</v>
+        <v>1946.86972003354</v>
       </c>
       <c r="M109" s="13" t="n">
-        <v>1946.21401693398</v>
+        <v>1945.85861549253</v>
       </c>
       <c r="N109" s="14" t="n">
-        <v>1946.21401693398</v>
+        <v>1945.85861549253</v>
       </c>
       <c r="O109" s="15" t="n">
-        <v>-0.0565207736272218</v>
+        <v>-0.0562611426243757</v>
       </c>
       <c r="P109" s="16" t="n">
-        <v>-0.453545208691169</v>
+        <v>-0.453481025757132</v>
       </c>
       <c r="Q109" s="17" t="n">
-        <v>-0.0549531477597847</v>
+        <v>-0.0547077524430634</v>
       </c>
       <c r="R109" s="18" t="n">
-        <v>1.03461115186094</v>
+        <v>1.03469711184475</v>
       </c>
       <c r="S109" s="19" t="n">
-        <v>0.619019029482564</v>
+        <v>0.620888710800153</v>
       </c>
     </row>
     <row r="110">
@@ -8023,46 +8023,46 @@
         <v>1981.82749195669</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>1.03943534361272</v>
+        <v>1.03825551871355</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>0.667347090440055</v>
+        <v>0.663418976476775</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>2036.11824257747</v>
+        <v>2038.08804764767</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>3156.41927296357</v>
+        <v>3146.2395316204</v>
       </c>
       <c r="J110" s="10" t="n">
-        <v>2775.19192030767</v>
+        <v>2768.4214700747</v>
       </c>
       <c r="K110" s="11" t="n">
-        <v>1906.63854575941</v>
+        <v>1908.80516042166</v>
       </c>
       <c r="L110" s="12" t="n">
-        <v>1949.71034363488</v>
+        <v>1952.31932692823</v>
       </c>
       <c r="M110" s="13" t="n">
-        <v>2060.44947007172</v>
+        <v>2061.84781473778</v>
       </c>
       <c r="N110" s="14" t="n">
-        <v>2060.44947007172</v>
+        <v>2061.84781473778</v>
       </c>
       <c r="O110" s="15" t="n">
-        <v>0.0570381927707018</v>
+        <v>0.0578992509701197</v>
       </c>
       <c r="P110" s="16" t="n">
-        <v>-0.331932034196572</v>
+        <v>-0.331369106169065</v>
       </c>
       <c r="Q110" s="17" t="n">
-        <v>0.0586962441662526</v>
+        <v>0.0596082358305876</v>
       </c>
       <c r="R110" s="18" t="n">
-        <v>1.01194981066691</v>
+        <v>1.01165787077626</v>
       </c>
       <c r="S110" s="19" t="n">
-        <v>0.652780664381496</v>
+        <v>0.655337203037392</v>
       </c>
     </row>
     <row r="111">
@@ -8082,46 +8082,46 @@
         <v>2244.76524089118</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>0.937654661491575</v>
+        <v>0.936926113913071</v>
       </c>
       <c r="G111" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H111" s="8" t="n">
-        <v>2323.25847300991</v>
+        <v>2324.07756741393</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>3181.65507249338</v>
+        <v>3171.57952576834</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>2813.37753909236</v>
+        <v>2804.53152434536</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>2394.02130985017</v>
+        <v>2395.88288506115</v>
       </c>
       <c r="L111" s="12" t="n">
-        <v>2394.02130985017</v>
+        <v>2395.88288506115</v>
       </c>
       <c r="M111" s="13" t="n">
-        <v>2325.79494405394</v>
+        <v>2326.32941415729</v>
       </c>
       <c r="N111" s="14" t="n">
-        <v>2325.79494405394</v>
+        <v>2326.32941415729</v>
       </c>
       <c r="O111" s="15" t="n">
-        <v>0.121137743665123</v>
+        <v>0.120689088479285</v>
       </c>
       <c r="P111" s="16" t="n">
-        <v>-0.0585800846961405</v>
+        <v>-0.0582373871944419</v>
       </c>
       <c r="Q111" s="17" t="n">
-        <v>0.128780384006693</v>
+        <v>0.128274064423683</v>
       </c>
       <c r="R111" s="18" t="n">
-        <v>1.00109177307368</v>
+        <v>1.00096892064832</v>
       </c>
       <c r="S111" s="19" t="n">
-        <v>0.731001598558347</v>
+        <v>0.733492379824125</v>
       </c>
     </row>
     <row r="112">
@@ -8141,46 +8141,46 @@
         <v>2416.28398981369</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>0.941864323582329</v>
+        <v>0.943406712825488</v>
       </c>
       <c r="G112" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>2568.54222444784</v>
+        <v>2565.62030535546</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>3219.36138025441</v>
+        <v>3209.69252345501</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>2887.70222872016</v>
+        <v>2876.55680024988</v>
       </c>
       <c r="K112" s="11" t="n">
-        <v>2565.42681288053</v>
+        <v>2561.23255957864</v>
       </c>
       <c r="L112" s="12" t="n">
-        <v>2565.42681288053</v>
+        <v>2561.23255957864</v>
       </c>
       <c r="M112" s="13" t="n">
-        <v>2560.40028078374</v>
+        <v>2558.33741402334</v>
       </c>
       <c r="N112" s="14" t="n">
-        <v>2560.40028078374</v>
+        <v>2558.33741402334</v>
       </c>
       <c r="O112" s="15" t="n">
-        <v>0.0961017139277385</v>
+        <v>0.095065933197357</v>
       </c>
       <c r="P112" s="16" t="n">
-        <v>0.243284759423105</v>
+        <v>0.242832600917925</v>
       </c>
       <c r="Q112" s="17" t="n">
-        <v>0.100871032216139</v>
+        <v>0.099731361540687</v>
       </c>
       <c r="R112" s="18" t="n">
-        <v>0.996830130497132</v>
+        <v>0.997161352630039</v>
       </c>
       <c r="S112" s="19" t="n">
-        <v>0.79531310044522</v>
+        <v>0.797066197253521</v>
       </c>
     </row>
     <row r="113">
@@ -8200,46 +8200,46 @@
         <v>2945.85895499108</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>1.08434150210634</v>
+        <v>1.08503026248868</v>
       </c>
       <c r="G113" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H113" s="8" t="n">
-        <v>2732.73459126095</v>
+        <v>2731.96674199351</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>3268.67052444861</v>
+        <v>3259.77689190772</v>
       </c>
       <c r="J113" s="10" t="n">
-        <v>2992.45029844088</v>
+        <v>2978.89168375243</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>2716.7261875237</v>
+        <v>2715.00165187496</v>
       </c>
       <c r="L113" s="12" t="n">
-        <v>2716.7261875237</v>
+        <v>2715.00165187496</v>
       </c>
       <c r="M113" s="13" t="n">
-        <v>2763.98357580784</v>
+        <v>2763.51053350517</v>
       </c>
       <c r="N113" s="14" t="n">
-        <v>2763.98357580784</v>
+        <v>2763.51053350517</v>
       </c>
       <c r="O113" s="15" t="n">
-        <v>0.076509357755649</v>
+        <v>0.0771442040758122</v>
       </c>
       <c r="P113" s="16" t="n">
-        <v>0.420184805863314</v>
+        <v>0.420201093492951</v>
       </c>
       <c r="Q113" s="17" t="n">
-        <v>0.0795122921021501</v>
+        <v>0.0801978340922425</v>
       </c>
       <c r="R113" s="18" t="n">
-        <v>1.01143506019458</v>
+        <v>1.01154618430261</v>
       </c>
       <c r="S113" s="19" t="n">
-        <v>0.845598709057436</v>
+        <v>0.847760636737282</v>
       </c>
     </row>
     <row r="114">
@@ -8259,46 +8259,46 @@
         <v>3141.23369626134</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>1.02753584014123</v>
+        <v>1.02560639447545</v>
       </c>
       <c r="G114" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>3083.33816008347</v>
+        <v>3087.60699688758</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>3328.30612417336</v>
+        <v>3320.62571087636</v>
       </c>
       <c r="J114" s="10" t="n">
-        <v>3120.29468042513</v>
+        <v>3104.35393961385</v>
       </c>
       <c r="K114" s="11" t="n">
-        <v>3057.05511530341</v>
+        <v>3062.80627069211</v>
       </c>
       <c r="L114" s="12" t="n">
-        <v>3057.05511530341</v>
+        <v>3062.80627069211</v>
       </c>
       <c r="M114" s="13" t="n">
-        <v>3102.09162076786</v>
+        <v>3104.95708696134</v>
       </c>
       <c r="N114" s="14" t="n">
-        <v>3102.09162076786</v>
+        <v>3104.95708696134</v>
       </c>
       <c r="O114" s="15" t="n">
-        <v>0.115403636643705</v>
+        <v>0.116498090727893</v>
       </c>
       <c r="P114" s="16" t="n">
-        <v>0.505541225750075</v>
+        <v>0.50590992447045</v>
       </c>
       <c r="Q114" s="17" t="n">
-        <v>0.122326358202474</v>
+        <v>0.123555365292237</v>
       </c>
       <c r="R114" s="18" t="n">
-        <v>1.00608219394394</v>
+        <v>1.00561926763712</v>
       </c>
       <c r="S114" s="19" t="n">
-        <v>0.932033143897879</v>
+        <v>0.935051811708674</v>
       </c>
     </row>
     <row r="115">
@@ -8318,46 +8318,46 @@
         <v>3374.61116034377</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>0.943279608860394</v>
+        <v>0.942835777518301</v>
       </c>
       <c r="G115" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>3563.77099972505</v>
+        <v>3563.27087167927</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>3396.64683331542</v>
+        <v>3390.69157558579</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>3262.52968628896</v>
+        <v>3244.44188243559</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>3577.53006494092</v>
+        <v>3579.21415458618</v>
       </c>
       <c r="L115" s="12" t="n">
-        <v>3577.53006494092</v>
+        <v>3579.21415458618</v>
       </c>
       <c r="M115" s="13" t="n">
-        <v>3530.85817797741</v>
+        <v>3530.56633773371</v>
       </c>
       <c r="N115" s="14" t="n">
-        <v>3530.85817797741</v>
+        <v>3530.56633773371</v>
       </c>
       <c r="O115" s="15" t="n">
-        <v>0.129464350958326</v>
+        <v>0.128458399029833</v>
       </c>
       <c r="P115" s="16" t="n">
-        <v>0.518129612846699</v>
+        <v>0.51765537427667</v>
       </c>
       <c r="Q115" s="17" t="n">
-        <v>0.138218534339556</v>
+        <v>0.137074116920852</v>
       </c>
       <c r="R115" s="18" t="n">
-        <v>0.990764608121516</v>
+        <v>0.990821765977575</v>
       </c>
       <c r="S115" s="19" t="n">
-        <v>1.03951289352358</v>
+        <v>1.04125257606887</v>
       </c>
     </row>
     <row r="116">
@@ -8377,46 +8377,46 @@
         <v>3733.26985008941</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>0.954478863413738</v>
+        <v>0.956995745271982</v>
       </c>
       <c r="G116" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>3850.24228817767</v>
+        <v>3849.17242322115</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>3471.90177388102</v>
+        <v>3468.26594411076</v>
       </c>
       <c r="J116" s="10" t="n">
-        <v>3410.1334298228</v>
+        <v>3390.44608847447</v>
       </c>
       <c r="K116" s="11" t="n">
-        <v>3911.31746672441</v>
+        <v>3901.03077107036</v>
       </c>
       <c r="L116" s="12" t="n">
-        <v>3911.31746672441</v>
+        <v>3901.03077107036</v>
       </c>
       <c r="M116" s="13" t="n">
-        <v>3819.7835284251</v>
+        <v>3815.86740337451</v>
       </c>
       <c r="N116" s="14" t="n">
-        <v>3819.7835284251</v>
+        <v>3815.86740337451</v>
       </c>
       <c r="O116" s="15" t="n">
-        <v>0.0786528017538535</v>
+        <v>0.0777097117435601</v>
       </c>
       <c r="P116" s="16" t="n">
-        <v>0.491869672524746</v>
+        <v>0.491541882809555</v>
       </c>
       <c r="Q116" s="17" t="n">
-        <v>0.0818286478482091</v>
+        <v>0.0808088670057212</v>
       </c>
       <c r="R116" s="18" t="n">
-        <v>0.99208913167722</v>
+        <v>0.991347485593079</v>
       </c>
       <c r="S116" s="19" t="n">
-        <v>1.10019919260423</v>
+        <v>1.10022341563916</v>
       </c>
     </row>
     <row r="117">
@@ -8436,46 +8436,46 @@
         <v>4166.74891556592</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1.07418976323358</v>
+        <v>1.07329747171194</v>
       </c>
       <c r="G117" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H117" s="8" t="n">
-        <v>3965.66517602769</v>
+        <v>3954.05947167177</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>3552.39311989618</v>
+        <v>3551.75810113791</v>
       </c>
       <c r="J117" s="10" t="n">
-        <v>3555.65902671033</v>
+        <v>3535.33099534809</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>3878.96911531066</v>
+        <v>3882.19391677113</v>
       </c>
       <c r="L117" s="12" t="n">
-        <v>3878.96911531066</v>
+        <v>3882.19391677113</v>
       </c>
       <c r="M117" s="13" t="n">
-        <v>3950.51956691797</v>
+        <v>3937.08032543277</v>
       </c>
       <c r="N117" s="14" t="n">
-        <v>3950.51956691797</v>
+        <v>3937.08032543277</v>
       </c>
       <c r="O117" s="15" t="n">
-        <v>0.0336533531302897</v>
+        <v>0.0312714090152356</v>
       </c>
       <c r="P117" s="16" t="n">
-        <v>0.429284747382531</v>
+        <v>0.424666299512556</v>
       </c>
       <c r="Q117" s="17" t="n">
-        <v>0.0342260333655027</v>
+        <v>0.0317654963458824</v>
       </c>
       <c r="R117" s="18" t="n">
-        <v>0.996180814961063</v>
+        <v>0.995705895078048</v>
       </c>
       <c r="S117" s="19" t="n">
-        <v>1.11207274464979</v>
+        <v>1.10848774418827</v>
       </c>
     </row>
     <row r="118">
@@ -8483,58 +8483,58 @@
         <v>169</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>4233.78150541524</v>
+        <v>4176.79388293553</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>4233.78150541524</v>
+        <v>4176.79388293553</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>4233.78150541524</v>
+        <v>4176.79388293553</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>4233.78150541524</v>
+        <v>4176.79388293553</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>1.02442856749137</v>
+        <v>1.02299618501399</v>
       </c>
       <c r="G118" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>4079.73788972205</v>
+        <v>4040.57132655491</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>3636.71768019492</v>
+        <v>3639.8478093707</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>3694.16551281975</v>
+        <v>3674.61396408701</v>
       </c>
       <c r="K118" s="11" t="n">
-        <v>4132.82257032617</v>
+        <v>4082.90269711847</v>
       </c>
       <c r="L118" s="12" t="n">
-        <v>4132.82257032617</v>
+        <v>4082.90269711847</v>
       </c>
       <c r="M118" s="13" t="n">
-        <v>4072.27796701784</v>
+        <v>4033.15377854736</v>
       </c>
       <c r="N118" s="14" t="n">
-        <v>4072.27796701784</v>
+        <v>4033.15377854736</v>
       </c>
       <c r="O118" s="15" t="n">
-        <v>0.0303554337469663</v>
+        <v>0.0241092307739148</v>
       </c>
       <c r="P118" s="16" t="n">
-        <v>0.312752318388915</v>
+        <v>0.298940264096983</v>
       </c>
       <c r="Q118" s="17" t="n">
-        <v>0.0308208573675937</v>
+        <v>0.0244022080255699</v>
       </c>
       <c r="R118" s="18" t="n">
-        <v>0.998171470102772</v>
+        <v>0.99816423287499</v>
       </c>
       <c r="S118" s="19" t="n">
-        <v>1.11976741807452</v>
+        <v>1.10805560830431</v>
       </c>
     </row>
     <row r="119">
@@ -8542,58 +8542,58 @@
         <v>170</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>3910.97166063794</v>
+        <v>3855.30333176018</v>
       </c>
       <c r="C119" s="3" t="n">
-        <v>3910.97166063794</v>
+        <v>3855.30333176018</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>3910.97166063794</v>
+        <v>3855.30333176018</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>3910.97166063794</v>
+        <v>3855.30333176018</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>0.943653978521264</v>
+        <v>0.943859476026463</v>
       </c>
       <c r="G119" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H119" s="8" t="n">
-        <v>4149.46179489071</v>
+        <v>4085.141222728</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>3723.6763736084</v>
+        <v>3731.42135389738</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>3822.32847446226</v>
+        <v>3805.54667032892</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>4144.49761210837</v>
+        <v>4084.61580318137</v>
       </c>
       <c r="L119" s="12" t="n">
-        <v>4144.49761210837</v>
+        <v>4084.61580318137</v>
       </c>
       <c r="M119" s="13" t="n">
-        <v>4132.59865213177</v>
+        <v>4074.35979524872</v>
       </c>
       <c r="N119" s="14" t="n">
-        <v>4132.59865213177</v>
+        <v>4074.35979524872</v>
       </c>
       <c r="O119" s="15" t="n">
-        <v>0.0147038827537903</v>
+        <v>0.010164983661921</v>
       </c>
       <c r="P119" s="16" t="n">
-        <v>0.17042329196554</v>
+        <v>0.154024427101992</v>
       </c>
       <c r="Q119" s="17" t="n">
-        <v>0.0148125166313504</v>
+        <v>0.0102168226067987</v>
       </c>
       <c r="R119" s="18" t="n">
-        <v>0.995936065062775</v>
+        <v>0.997360818906505</v>
       </c>
       <c r="S119" s="19" t="n">
-        <v>1.10981681475372</v>
+        <v>1.09190557935601</v>
       </c>
     </row>
     <row r="120">
@@ -8601,58 +8601,58 @@
         <v>171</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>3961.64730583922</v>
+        <v>3912.69231011997</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>3961.64730583922</v>
+        <v>3912.69231011997</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>3961.64730583922</v>
+        <v>3912.69231011997</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>3961.64730583922</v>
+        <v>3912.69231011997</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>0.964238344614886</v>
+        <v>0.967218152547455</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>4132.77669493217</v>
+        <v>4075.44206905146</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>3812.38018452413</v>
+        <v>3825.64192911104</v>
       </c>
       <c r="J120" s="10" t="n">
-        <v>3939.01678323659</v>
+        <v>3927.42223337666</v>
       </c>
       <c r="K120" s="11" t="n">
-        <v>4108.57681398419</v>
+        <v>4045.30487751366</v>
       </c>
       <c r="L120" s="12" t="n">
-        <v>4108.57681398419</v>
+        <v>4045.30487751366</v>
       </c>
       <c r="M120" s="13" t="n">
-        <v>4128.42163691375</v>
+        <v>4072.7528517631</v>
       </c>
       <c r="N120" s="14" t="n">
-        <v>4128.42163691375</v>
+        <v>4072.7528517631</v>
       </c>
       <c r="O120" s="15" t="n">
-        <v>-0.0010112590038134</v>
+        <v>-0.000394481720354239</v>
       </c>
       <c r="P120" s="16" t="n">
-        <v>0.0807998951228273</v>
+        <v>0.0673203288356985</v>
       </c>
       <c r="Q120" s="17" t="n">
-        <v>-0.00101074785374322</v>
+        <v>-0.00039440392267065</v>
       </c>
       <c r="R120" s="18" t="n">
-        <v>0.998946215017191</v>
+        <v>0.999340140960712</v>
       </c>
       <c r="S120" s="19" t="n">
-        <v>1.0828987239186</v>
+        <v>1.06459332243608</v>
       </c>
     </row>
     <row r="121">
@@ -8660,58 +8660,58 @@
         <v>172</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>4425.94559335052</v>
+        <v>4375.68794227454</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>4425.94559335052</v>
+        <v>4375.68794227454</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>4425.94559335052</v>
+        <v>4375.68794227454</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>4425.94559335052</v>
+        <v>4375.68794227454</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>1.06597012440437</v>
+        <v>1.06314762307272</v>
       </c>
       <c r="G121" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>4118.86179972859</v>
+        <v>4075.4122208133</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>3902.20311060365</v>
+        <v>3921.89347593557</v>
       </c>
       <c r="J121" s="10" t="n">
-        <v>4044.71015642969</v>
+        <v>4040.92911819732</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>4152.03530757824</v>
+        <v>4115.78584884372</v>
       </c>
       <c r="L121" s="12" t="n">
-        <v>4152.03530757824</v>
+        <v>4115.78584884372</v>
       </c>
       <c r="M121" s="13" t="n">
-        <v>4121.22908066251</v>
+        <v>4078.32784361086</v>
       </c>
       <c r="N121" s="14" t="n">
-        <v>4121.22908066251</v>
+        <v>4078.32784361086</v>
       </c>
       <c r="O121" s="15" t="n">
-        <v>-0.00174372426662301</v>
+        <v>0.00136791498586075</v>
       </c>
       <c r="P121" s="16" t="n">
-        <v>0.0432119144970378</v>
+        <v>0.0358762093995533</v>
       </c>
       <c r="Q121" s="17" t="n">
-        <v>-0.0017422048627328</v>
+        <v>0.00136885100831607</v>
       </c>
       <c r="R121" s="18" t="n">
-        <v>1.00057474153031</v>
+        <v>1.00071541788648</v>
       </c>
       <c r="S121" s="19" t="n">
-        <v>1.05612879797663</v>
+        <v>1.03988745962509</v>
       </c>
     </row>
     <row r="122">
@@ -8719,58 +8719,58 @@
         <v>173</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>4179.49876291989</v>
+        <v>4139.45294223971</v>
       </c>
       <c r="C122" s="3" t="n">
-        <v>4179.49876291989</v>
+        <v>4139.45294223971</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>4179.49876291989</v>
+        <v>4139.45294223971</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>4179.49876291989</v>
+        <v>4139.45294223971</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>1.02633172617394</v>
+        <v>1.02552206293948</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>4086.48423115742</v>
+        <v>4045.71770150933</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>3992.70427240193</v>
+        <v>4019.69722463762</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>4140.73611148227</v>
+        <v>4147.3452029787</v>
       </c>
       <c r="K122" s="11" t="n">
-        <v>4072.26889350935</v>
+        <v>4036.43479924234</v>
       </c>
       <c r="L122" s="12" t="n">
-        <v>4072.26889350935</v>
+        <v>4036.43479924234</v>
       </c>
       <c r="M122" s="13" t="n">
-        <v>4103.75951252214</v>
+        <v>4071.53340520224</v>
       </c>
       <c r="N122" s="14" t="n">
-        <v>4103.75951252214</v>
+        <v>4071.53340520224</v>
       </c>
       <c r="O122" s="15" t="n">
-        <v>-0.00424793158365897</v>
+        <v>-0.00166737562157574</v>
       </c>
       <c r="P122" s="16" t="n">
-        <v>0.00773069661729209</v>
+        <v>0.00951603354650632</v>
       </c>
       <c r="Q122" s="17" t="n">
-        <v>-0.00423892188433284</v>
+        <v>-0.0016659863231121</v>
       </c>
       <c r="R122" s="18" t="n">
-        <v>1.00422741906918</v>
+        <v>1.00638099481911</v>
       </c>
       <c r="S122" s="19" t="n">
-        <v>1.02781454186022</v>
+        <v>1.01289554353669</v>
       </c>
     </row>
     <row r="123">
@@ -8778,58 +8778,58 @@
         <v>174</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>3874.20337444698</v>
+        <v>3860.80585126077</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>3874.20337444698</v>
+        <v>3860.80585126077</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>3874.20337444698</v>
+        <v>3860.80585126077</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>3874.20337444698</v>
+        <v>3860.80585126077</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>0.940691110963825</v>
+        <v>0.942239516063428</v>
       </c>
       <c r="G123" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>4148.17122213313</v>
+        <v>4157.90972556409</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>4083.59893559706</v>
+        <v>4118.69558821689</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>4228.95879159077</v>
+        <v>4248.32264956182</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>4118.46495549161</v>
+        <v>4097.47817348054</v>
       </c>
       <c r="L123" s="12" t="n">
-        <v>4118.46495549161</v>
+        <v>4097.47817348054</v>
       </c>
       <c r="M123" s="13" t="n">
-        <v>4153.6105842369</v>
+        <v>4173.39440546451</v>
       </c>
       <c r="N123" s="14" t="n">
-        <v>4153.6105842369</v>
+        <v>4173.39440546451</v>
       </c>
       <c r="O123" s="15" t="n">
-        <v>0.0120744684541691</v>
+        <v>0.0247100242600516</v>
       </c>
       <c r="P123" s="16" t="n">
-        <v>0.00508443569623984</v>
+        <v>0.0243067905616194</v>
       </c>
       <c r="Q123" s="17" t="n">
-        <v>0.0121476591312557</v>
+        <v>0.0250178471167957</v>
       </c>
       <c r="R123" s="18" t="n">
-        <v>1.00131126749898</v>
+        <v>1.00372415009523</v>
       </c>
       <c r="S123" s="19" t="n">
-        <v>1.01714459469307</v>
+        <v>1.01328061666031</v>
       </c>
     </row>
     <row r="124">
@@ -8837,58 +8837,58 @@
         <v>175</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>4430.14508587482</v>
+        <v>4384.27601900521</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>4430.14508587482</v>
+        <v>4384.27601900521</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>4430.14508587482</v>
+        <v>4384.27601900521</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>4430.14508587482</v>
+        <v>4384.27601900521</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>0.96927998880952</v>
+        <v>0.972080436304043</v>
       </c>
       <c r="G124" s="7" t="n">
-        <v>0</v>
+        <v>0.613221075326813</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>4305.24353245505</v>
+        <v>4386.06503172968</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>4174.65209375531</v>
+        <v>4218.54144065723</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>4310.90000386176</v>
+        <v>4344.95906776901</v>
       </c>
       <c r="K124" s="11" t="n">
-        <v>4570.55251013277</v>
+        <v>4510.19880173159</v>
       </c>
       <c r="L124" s="12" t="n">
-        <v>4305.24353245505</v>
+        <v>4462.18647565462</v>
       </c>
       <c r="M124" s="13" t="n">
-        <v>4283.86939037307</v>
+        <v>4373.69693994089</v>
       </c>
       <c r="N124" s="14" t="n">
-        <v>4283.86939037307</v>
+        <v>4373.69693994089</v>
       </c>
       <c r="O124" s="15" t="n">
-        <v>0.0308786880536441</v>
+        <v>0.0468789223525102</v>
       </c>
       <c r="P124" s="16" t="n">
-        <v>0.0376530711081946</v>
+        <v>0.0738920575667905</v>
       </c>
       <c r="Q124" s="17" t="n">
-        <v>0.0313603799620752</v>
+        <v>0.0479951126148317</v>
       </c>
       <c r="R124" s="18" t="n">
-        <v>0.995035323339818</v>
+        <v>0.997180139441774</v>
       </c>
       <c r="S124" s="19" t="n">
-        <v>1.02616201162754</v>
+        <v>1.03677941806813</v>
       </c>
     </row>
     <row r="125">
@@ -8896,58 +8896,58 @@
         <v>176</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>4683.00158498928</v>
+        <v>4731.06809231028</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>4683.00158498928</v>
+        <v>4731.06809231028</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>4683.00158498928</v>
+        <v>4731.06809231028</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>4683.00158498928</v>
+        <v>4731.06809231028</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>1.06274241266063</v>
+        <v>1.05770961638897</v>
       </c>
       <c r="G125" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>4432.961825219</v>
+        <v>4501.79416625325</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>4265.65053170538</v>
+        <v>4318.87439505826</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v>4387.52908622133</v>
+        <v>4437.5978450422</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>4406.52554109057</v>
+        <v>4472.93663497377</v>
       </c>
       <c r="L125" s="12" t="n">
-        <v>4406.52554109057</v>
+        <v>4472.93663497377</v>
       </c>
       <c r="M125" s="13" t="n">
-        <v>4406.66588424604</v>
+        <v>4480.22939570274</v>
       </c>
       <c r="N125" s="14" t="n">
-        <v>4406.66588424604</v>
+        <v>4480.22939570274</v>
       </c>
       <c r="O125" s="15" t="n">
-        <v>0.0282617038555527</v>
+        <v>0.0240656163674013</v>
       </c>
       <c r="P125" s="16" t="n">
-        <v>0.0692601158530239</v>
+        <v>0.0985456705550307</v>
       </c>
       <c r="Q125" s="17" t="n">
-        <v>0.028664854756993</v>
+        <v>0.024357530305539</v>
       </c>
       <c r="R125" s="18" t="n">
-        <v>0.994068087655671</v>
+        <v>0.995209738661052</v>
       </c>
       <c r="S125" s="19" t="n">
-        <v>1.03305834631612</v>
+        <v>1.03736042910373</v>
       </c>
     </row>
     <row r="126">
@@ -8955,58 +8955,58 @@
         <v>177</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>4643.87571398214</v>
+        <v>4651.23302563202</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>4643.87571398214</v>
+        <v>4651.23302563202</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>4643.87571398214</v>
+        <v>4651.23302563202</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>4643.87571398214</v>
+        <v>4651.23302563202</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>1.03005672205805</v>
+        <v>1.03066243019718</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>4484.94879567994</v>
+        <v>4514.84957326482</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>4356.46265392516</v>
+        <v>4419.48634266649</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v>4459.78709423853</v>
+        <v>4527.16850586275</v>
       </c>
       <c r="K126" s="11" t="n">
-        <v>4508.36892234797</v>
+        <v>4512.85783720881</v>
       </c>
       <c r="L126" s="12" t="n">
-        <v>4508.36892234797</v>
+        <v>4512.85783720881</v>
       </c>
       <c r="M126" s="13" t="n">
-        <v>4480.98248207096</v>
+        <v>4518.2115238725</v>
       </c>
       <c r="N126" s="14" t="n">
-        <v>4480.98248207096</v>
+        <v>4518.2115238725</v>
       </c>
       <c r="O126" s="15" t="n">
-        <v>0.0167239582154094</v>
+        <v>0.00844198546882369</v>
       </c>
       <c r="P126" s="16" t="n">
-        <v>0.0919213146866362</v>
+        <v>0.109707590290072</v>
       </c>
       <c r="Q126" s="17" t="n">
-        <v>0.0168645864644748</v>
+        <v>0.00847771951279785</v>
       </c>
       <c r="R126" s="18" t="n">
-        <v>0.999115639043014</v>
+        <v>1.00074464288414</v>
       </c>
       <c r="S126" s="19" t="n">
-        <v>1.02858278333538</v>
+        <v>1.02233860986353</v>
       </c>
     </row>
     <row r="127">
@@ -9014,58 +9014,58 @@
         <v>178</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>4212.04006084719</v>
+        <v>4291.63474282149</v>
       </c>
       <c r="C127" s="3" t="n">
-        <v>4212.04006084719</v>
+        <v>4291.63474282149</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>4212.04006084719</v>
+        <v>4291.63474282149</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>4212.04006084719</v>
+        <v>4291.63474282149</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>0.935870280785125</v>
+        <v>0.938227574849177</v>
       </c>
       <c r="G127" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>4526.37383700262</v>
+        <v>4573.10395089496</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>4447.04491177342</v>
+        <v>4520.26546362836</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>4528.71006575674</v>
+        <v>4614.77726866169</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>4500.66654249732</v>
+        <v>4574.19378609863</v>
       </c>
       <c r="L127" s="12" t="n">
-        <v>4500.66654249732</v>
+        <v>4574.19378609863</v>
       </c>
       <c r="M127" s="13" t="n">
-        <v>4515.25127776335</v>
+        <v>4570.6940984847</v>
       </c>
       <c r="N127" s="14" t="n">
-        <v>4515.25127776335</v>
+        <v>4570.6940984847</v>
       </c>
       <c r="O127" s="15" t="n">
-        <v>0.00761851289301565</v>
+        <v>0.0115488398970322</v>
       </c>
       <c r="P127" s="16" t="n">
-        <v>0.0870665860923239</v>
+        <v>0.0951982138328389</v>
       </c>
       <c r="Q127" s="17" t="n">
-        <v>0.00764760760157124</v>
+        <v>0.0116157852138827</v>
       </c>
       <c r="R127" s="18" t="n">
-        <v>0.997542721913877</v>
+        <v>0.9994730379112</v>
       </c>
       <c r="S127" s="19" t="n">
-        <v>1.0153374583219</v>
+        <v>1.01115612241407</v>
       </c>
     </row>
     <row r="128">
@@ -9073,58 +9073,58 @@
         <v>179</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>4416.92558923214</v>
+        <v>4496.73564215719</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>4416.92558923214</v>
+        <v>4496.73564215719</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>4416.92558923214</v>
+        <v>4496.73564215719</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>4416.92558923214</v>
+        <v>4496.73564215719</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>0.97047493620693</v>
+        <v>0.972996969447311</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>4519.95821482252</v>
+        <v>4595.16656357479</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>4537.44869802667</v>
+        <v>4621.15829527441</v>
       </c>
       <c r="J128" s="10" t="n">
-        <v>4595.57694775991</v>
+        <v>4701.45879852676</v>
       </c>
       <c r="K128" s="11" t="n">
-        <v>4551.3031037108</v>
+        <v>4621.53098453272</v>
       </c>
       <c r="L128" s="12" t="n">
-        <v>4551.3031037108</v>
+        <v>4621.53098453272</v>
       </c>
       <c r="M128" s="13" t="n">
-        <v>4520.33179751374</v>
+        <v>4612.88855202506</v>
       </c>
       <c r="N128" s="14" t="n">
-        <v>4520.33179751374</v>
+        <v>4612.88855202506</v>
       </c>
       <c r="O128" s="15" t="n">
-        <v>0.00112455836960924</v>
+        <v>0.00918916986038651</v>
       </c>
       <c r="P128" s="16" t="n">
-        <v>0.055198323196328</v>
+        <v>0.054688657071746</v>
       </c>
       <c r="Q128" s="17" t="n">
-        <v>0.00112519092246455</v>
+        <v>0.00923151990293003</v>
       </c>
       <c r="R128" s="18" t="n">
-        <v>1.00008265180196</v>
+        <v>1.00385665855744</v>
       </c>
       <c r="S128" s="19" t="n">
-        <v>0.99622763767657</v>
+        <v>0.998210460944867</v>
       </c>
     </row>
     <row r="129">
@@ -9132,92 +9132,118 @@
         <v>180</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>4766.00149933856</v>
+        <v>4901.25392352843</v>
       </c>
       <c r="C129" s="3" t="n">
-        <v>4766.00149933856</v>
+        <v>4901.25392352843</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>4766.00149933856</v>
+        <v>4901.25392352843</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>4766.00149933856</v>
+        <v>4901.25392352843</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>1.06430182193001</v>
+        <v>1.05760428968987</v>
       </c>
       <c r="G129" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>4516.10839293417</v>
+        <v>4706.32616004992</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>4627.75891898065</v>
+        <v>4722.14508013672</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>4661.52646961568</v>
+        <v>4788.04484313288</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>4478.05444013604</v>
+        <v>4634.29845293618</v>
       </c>
       <c r="L129" s="12" t="n">
-        <v>4478.05444013604</v>
+        <v>4634.29845293618</v>
       </c>
       <c r="M129" s="13" t="n">
-        <v>4502.47066132763</v>
+        <v>4708.10501767361</v>
       </c>
       <c r="N129" s="14" t="n">
-        <v>4502.47066132763</v>
+        <v>4708.10501767361</v>
       </c>
       <c r="O129" s="15" t="n">
-        <v>-0.00395911571778157</v>
+        <v>0.0204312506269245</v>
       </c>
       <c r="P129" s="16" t="n">
-        <v>0.0217408761177216</v>
+        <v>0.0508624898067573</v>
       </c>
       <c r="Q129" s="17" t="n">
-        <v>-0.00395128875184314</v>
+        <v>0.0206413973749151</v>
       </c>
       <c r="R129" s="18" t="n">
-        <v>0.996980202771953</v>
+        <v>1.00037797159891</v>
       </c>
       <c r="S129" s="19" t="n">
-        <v>0.972926796782961</v>
+        <v>0.997026761731194</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
         <v>181</v>
       </c>
-      <c r="B130" s="2"/>
+      <c r="B130" s="2" t="n">
+        <v>5208.86949768429</v>
+      </c>
       <c r="C130" s="3" t="n">
-        <v>4664.53953058182</v>
+        <v>5208.86949768429</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>5668.23010814561</v>
+        <v>5208.86949768429</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>3838.57546663339</v>
+        <v>5208.86949768429</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>1.03070445996027</v>
-      </c>
-      <c r="G130" s="7"/>
-      <c r="H130" s="8"/>
-      <c r="I130" s="9"/>
-      <c r="J130" s="10"/>
-      <c r="K130" s="11"/>
-      <c r="L130" s="12"/>
-      <c r="M130" s="13"/>
+        <v>1.03264433851455</v>
+      </c>
+      <c r="G130" s="7" t="n">
+        <v>0.380729905133907</v>
+      </c>
+      <c r="H130" s="8" t="n">
+        <v>4879.63588411126</v>
+      </c>
+      <c r="I130" s="9" t="n">
+        <v>4823.20629367817</v>
+      </c>
+      <c r="J130" s="10" t="n">
+        <v>4874.96751108503</v>
+      </c>
+      <c r="K130" s="11" t="n">
+        <v>5044.20476964721</v>
+      </c>
+      <c r="L130" s="12" t="n">
+        <v>4942.29218028936</v>
+      </c>
+      <c r="M130" s="13" t="n">
+        <v>4839.62760450496</v>
+      </c>
       <c r="N130" s="14" t="n">
-        <v>4525.583920304</v>
-      </c>
-      <c r="O130" s="15"/>
-      <c r="P130" s="16"/>
-      <c r="Q130" s="17"/>
-      <c r="R130" s="18"/>
-      <c r="S130" s="19"/>
+        <v>4839.62760450496</v>
+      </c>
+      <c r="O130" s="15" t="n">
+        <v>0.0275522811833358</v>
+      </c>
+      <c r="P130" s="16" t="n">
+        <v>0.0711379002364587</v>
+      </c>
+      <c r="Q130" s="17" t="n">
+        <v>0.0279353553792099</v>
+      </c>
+      <c r="R130" s="18" t="n">
+        <v>0.991800970286212</v>
+      </c>
+      <c r="S130" s="19" t="n">
+        <v>1.00340464616832</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
@@ -9225,16 +9251,16 @@
       </c>
       <c r="B131" s="2"/>
       <c r="C131" s="3" t="n">
-        <v>4126.77321452653</v>
+        <v>4614.83859774665</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>5436.3547999046</v>
+        <v>5600.23630467111</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>3132.66109203037</v>
+        <v>3802.82797450687</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>0.933596509852354</v>
+        <v>0.936238958052296</v>
       </c>
       <c r="G131" s="7"/>
       <c r="H131" s="8"/>
@@ -9244,7 +9270,7 @@
       <c r="L131" s="12"/>
       <c r="M131" s="13"/>
       <c r="N131" s="14" t="n">
-        <v>4420.29631749498</v>
+        <v>4929.12472617795</v>
       </c>
       <c r="O131" s="15"/>
       <c r="P131" s="16"/>
@@ -9258,16 +9284,16 @@
       </c>
       <c r="B132" s="2"/>
       <c r="C132" s="3" t="n">
-        <v>4264.24070320446</v>
+        <v>4766.82004114845</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>5976.40789412975</v>
+        <v>6267.4831496668</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>3042.58830671957</v>
+        <v>3625.47018668931</v>
       </c>
       <c r="F132" s="6" t="n">
-        <v>0.97088695864908</v>
+        <v>0.973228093126713</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="8"/>
@@ -9277,7 +9303,7 @@
       <c r="L132" s="12"/>
       <c r="M132" s="13"/>
       <c r="N132" s="14" t="n">
-        <v>4392.10833477241</v>
+        <v>4897.9474337141</v>
       </c>
       <c r="O132" s="15"/>
       <c r="P132" s="16"/>
@@ -9291,16 +9317,16 @@
       </c>
       <c r="B133" s="2"/>
       <c r="C133" s="3" t="n">
-        <v>4882.94163916669</v>
+        <v>5469.26838078428</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>7210.39277618192</v>
+        <v>7647.29461540038</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>3306.77118315508</v>
+        <v>3911.56587073383</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>1.06553787255376</v>
+        <v>1.05757182340301</v>
       </c>
       <c r="G133" s="7"/>
       <c r="H133" s="8"/>
@@ -9310,7 +9336,7 @@
       <c r="L133" s="12"/>
       <c r="M133" s="13"/>
       <c r="N133" s="14" t="n">
-        <v>4582.60730560783</v>
+        <v>5171.5337528429</v>
       </c>
       <c r="O133" s="15"/>
       <c r="P133" s="16"/>
@@ -9323,10 +9349,18 @@
         <v>185</v>
       </c>
       <c r="B134" s="2"/>
-      <c r="C134" s="3"/>
-      <c r="D134" s="4"/>
-      <c r="E134" s="5"/>
-      <c r="F134" s="6"/>
+      <c r="C134" s="3" t="n">
+        <v>5373.61888619766</v>
+      </c>
+      <c r="D134" s="4" t="n">
+        <v>7913.46223802113</v>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>3648.94392183528</v>
+      </c>
+      <c r="F134" s="6" t="n">
+        <v>1.03368050111134</v>
+      </c>
       <c r="G134" s="7"/>
       <c r="H134" s="8"/>
       <c r="I134" s="9"/>
@@ -9334,7 +9368,9 @@
       <c r="K134" s="11"/>
       <c r="L134" s="12"/>
       <c r="M134" s="13"/>
-      <c r="N134" s="14"/>
+      <c r="N134" s="14" t="n">
+        <v>5198.52979757316</v>
+      </c>
       <c r="O134" s="15"/>
       <c r="P134" s="16"/>
       <c r="Q134" s="17"/>
@@ -9832,7 +9868,7 @@
         <v>222</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.0211556347589539</v>
+        <v>0.0237608746453161</v>
       </c>
     </row>
     <row r="6">
@@ -9840,7 +9876,7 @@
         <v>223</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.103122817401219</v>
+        <v>0.0966850156702349</v>
       </c>
     </row>
     <row r="7">
@@ -9848,7 +9884,7 @@
         <v>224</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.231147261464707</v>
+        <v>0.225545603442134</v>
       </c>
     </row>
     <row r="8">
@@ -9856,7 +9892,7 @@
         <v>225</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.384395391172474</v>
+        <v>0.379663141030601</v>
       </c>
     </row>
     <row r="9">
@@ -9864,7 +9900,7 @@
         <v>226</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.4936716467603</v>
+        <v>0.485729310418434</v>
       </c>
     </row>
     <row r="10">
@@ -9872,7 +9908,7 @@
         <v>227</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.482664456923521</v>
+        <v>0.477277529108288</v>
       </c>
     </row>
     <row r="11">
@@ -9880,7 +9916,7 @@
         <v>228</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.335607966593852</v>
+        <v>0.327026485568293</v>
       </c>
     </row>
     <row r="12">
@@ -9888,7 +9924,7 @@
         <v>229</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.139637464961147</v>
+        <v>0.133584057536211</v>
       </c>
     </row>
     <row r="13">
@@ -9896,7 +9932,7 @@
         <v>230</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.0125624053766106</v>
+        <v>0.0168978299150181</v>
       </c>
     </row>
     <row r="14">
